--- a/Financial Analysis/LHX.xlsx
+++ b/Financial Analysis/LHX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B1F300-7BF2-4A5C-9B8A-0FB20FEF4762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A4256F-A72C-4A92-AF6A-BED080EE7A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{C2D3018F-E467-4E1E-BD9F-9383343E0F25}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C2D3018F-E467-4E1E-BD9F-9383343E0F25}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>LHX</t>
   </si>
@@ -185,6 +185,36 @@
   </si>
   <si>
     <t>Net Margin</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>Discount rate</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>Net cash</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Per share</t>
+  </si>
+  <si>
+    <t>Current price</t>
+  </si>
+  <si>
+    <t>Variance</t>
+  </si>
+  <si>
+    <t>Consensus</t>
+  </si>
+  <si>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -695,7 +725,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45771</v>
+        <v>45805</v>
       </c>
       <c r="G3" s="4">
         <v>45771</v>
@@ -771,12 +801,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C127D1A-B1AA-4685-BD0F-764C53F340E2}">
-  <dimension ref="B2:AI31"/>
+  <dimension ref="B2:EO31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
     <col min="2" max="2" width="17.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="1"/>
+    <col min="3" max="36" width="8.88671875" style="1"/>
+    <col min="37" max="37" width="11.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.77734375" style="1" customWidth="1"/>
+    <col min="39" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:35" x14ac:dyDescent="0.3">
@@ -896,6 +929,50 @@
       <c r="X3" s="6">
         <v>15134</v>
       </c>
+      <c r="Y3" s="6">
+        <f>X3*1.08</f>
+        <v>16344.720000000001</v>
+      </c>
+      <c r="Z3" s="6">
+        <f>Y3*1.05</f>
+        <v>17161.956000000002</v>
+      </c>
+      <c r="AA3" s="6">
+        <f>Z3*1.04</f>
+        <v>17848.434240000002</v>
+      </c>
+      <c r="AB3" s="6">
+        <f>AA3*1.03</f>
+        <v>18383.887267200003</v>
+      </c>
+      <c r="AC3" s="6">
+        <f t="shared" ref="AC3:AI3" si="0">AB3*1.02</f>
+        <v>18751.565012544004</v>
+      </c>
+      <c r="AD3" s="6">
+        <f t="shared" si="0"/>
+        <v>19126.596312794885</v>
+      </c>
+      <c r="AE3" s="6">
+        <f t="shared" si="0"/>
+        <v>19509.128239050784</v>
+      </c>
+      <c r="AF3" s="6">
+        <f t="shared" si="0"/>
+        <v>19899.310803831799</v>
+      </c>
+      <c r="AG3" s="6">
+        <f t="shared" si="0"/>
+        <v>20297.297019908434</v>
+      </c>
+      <c r="AH3" s="6">
+        <f t="shared" si="0"/>
+        <v>20703.242960306601</v>
+      </c>
+      <c r="AI3" s="6">
+        <f t="shared" si="0"/>
+        <v>21117.307819512735</v>
+      </c>
     </row>
     <row r="4" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -916,30 +993,118 @@
       <c r="X4" s="6">
         <v>6191</v>
       </c>
+      <c r="Y4" s="6">
+        <f>X4*1.06</f>
+        <v>6562.46</v>
+      </c>
+      <c r="Z4" s="6">
+        <f>Y4*1.05</f>
+        <v>6890.5830000000005</v>
+      </c>
+      <c r="AA4" s="6">
+        <f>Z4*1.04</f>
+        <v>7166.2063200000011</v>
+      </c>
+      <c r="AB4" s="6">
+        <f>AA4*1.03</f>
+        <v>7381.1925096000014</v>
+      </c>
+      <c r="AC4" s="6">
+        <f t="shared" ref="AC4:AI4" si="1">AB4*1.03</f>
+        <v>7602.6282848880019</v>
+      </c>
+      <c r="AD4" s="6">
+        <f t="shared" si="1"/>
+        <v>7830.7071334346419</v>
+      </c>
+      <c r="AE4" s="6">
+        <f t="shared" si="1"/>
+        <v>8065.6283474376814</v>
+      </c>
+      <c r="AF4" s="6">
+        <f t="shared" si="1"/>
+        <v>8307.5971978608122</v>
+      </c>
+      <c r="AG4" s="6">
+        <f t="shared" si="1"/>
+        <v>8556.8251137966363</v>
+      </c>
+      <c r="AH4" s="6">
+        <f t="shared" si="1"/>
+        <v>8813.5298672105364</v>
+      </c>
+      <c r="AI4" s="6">
+        <f t="shared" si="1"/>
+        <v>9077.9357632268529</v>
+      </c>
     </row>
     <row r="5" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="T5" s="9">
-        <f>T3+T4</f>
+        <f t="shared" ref="T5:Y5" si="2">T3+T4</f>
         <v>18194</v>
       </c>
       <c r="U5" s="9">
-        <f>U3+U4</f>
+        <f t="shared" si="2"/>
         <v>17814</v>
       </c>
       <c r="V5" s="9">
-        <f>V3+V4</f>
+        <f t="shared" si="2"/>
         <v>17062</v>
       </c>
       <c r="W5" s="9">
-        <f>W3+W4</f>
+        <f t="shared" si="2"/>
         <v>19419</v>
       </c>
       <c r="X5" s="9">
-        <f>X3+X4</f>
+        <f t="shared" si="2"/>
         <v>21325</v>
+      </c>
+      <c r="Y5" s="9">
+        <f t="shared" si="2"/>
+        <v>22907.18</v>
+      </c>
+      <c r="Z5" s="9">
+        <f t="shared" ref="Z5:AI5" si="3">Z3+Z4</f>
+        <v>24052.539000000004</v>
+      </c>
+      <c r="AA5" s="9">
+        <f t="shared" si="3"/>
+        <v>25014.640560000003</v>
+      </c>
+      <c r="AB5" s="9">
+        <f t="shared" si="3"/>
+        <v>25765.079776800005</v>
+      </c>
+      <c r="AC5" s="9">
+        <f t="shared" si="3"/>
+        <v>26354.193297432008</v>
+      </c>
+      <c r="AD5" s="9">
+        <f t="shared" si="3"/>
+        <v>26957.303446229525</v>
+      </c>
+      <c r="AE5" s="9">
+        <f t="shared" si="3"/>
+        <v>27574.756586488467</v>
+      </c>
+      <c r="AF5" s="9">
+        <f t="shared" si="3"/>
+        <v>28206.908001692609</v>
+      </c>
+      <c r="AG5" s="9">
+        <f t="shared" si="3"/>
+        <v>28854.12213370507</v>
+      </c>
+      <c r="AH5" s="9">
+        <f t="shared" si="3"/>
+        <v>29516.772827517139</v>
+      </c>
+      <c r="AI5" s="9">
+        <f t="shared" si="3"/>
+        <v>30195.243582739589</v>
       </c>
     </row>
     <row r="6" spans="2:35" x14ac:dyDescent="0.3">
@@ -961,6 +1126,50 @@
       <c r="X6" s="6">
         <v>11019</v>
       </c>
+      <c r="Y6" s="6">
+        <f>Y3*0.73</f>
+        <v>11931.6456</v>
+      </c>
+      <c r="Z6" s="6">
+        <f t="shared" ref="Z6:AI6" si="4">Z3*0.73</f>
+        <v>12528.22788</v>
+      </c>
+      <c r="AA6" s="6">
+        <f t="shared" si="4"/>
+        <v>13029.356995200002</v>
+      </c>
+      <c r="AB6" s="6">
+        <f t="shared" si="4"/>
+        <v>13420.237705056003</v>
+      </c>
+      <c r="AC6" s="6">
+        <f t="shared" si="4"/>
+        <v>13688.642459157123</v>
+      </c>
+      <c r="AD6" s="6">
+        <f t="shared" si="4"/>
+        <v>13962.415308340265</v>
+      </c>
+      <c r="AE6" s="6">
+        <f t="shared" si="4"/>
+        <v>14241.663614507072</v>
+      </c>
+      <c r="AF6" s="6">
+        <f t="shared" si="4"/>
+        <v>14526.496886797213</v>
+      </c>
+      <c r="AG6" s="6">
+        <f t="shared" si="4"/>
+        <v>14817.026824533157</v>
+      </c>
+      <c r="AH6" s="6">
+        <f t="shared" si="4"/>
+        <v>15113.367361023818</v>
+      </c>
+      <c r="AI6" s="6">
+        <f t="shared" si="4"/>
+        <v>15415.634708244295</v>
+      </c>
     </row>
     <row r="7" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
@@ -981,30 +1190,118 @@
       <c r="X7" s="6">
         <v>4782</v>
       </c>
+      <c r="Y7" s="6">
+        <f>Y4*0.77</f>
+        <v>5053.0942000000005</v>
+      </c>
+      <c r="Z7" s="6">
+        <f t="shared" ref="Z7:AI7" si="5">Z4*0.77</f>
+        <v>5305.7489100000003</v>
+      </c>
+      <c r="AA7" s="6">
+        <f t="shared" si="5"/>
+        <v>5517.9788664000007</v>
+      </c>
+      <c r="AB7" s="6">
+        <f t="shared" si="5"/>
+        <v>5683.5182323920008</v>
+      </c>
+      <c r="AC7" s="6">
+        <f t="shared" si="5"/>
+        <v>5854.0237793637616</v>
+      </c>
+      <c r="AD7" s="6">
+        <f t="shared" si="5"/>
+        <v>6029.6444927446746</v>
+      </c>
+      <c r="AE7" s="6">
+        <f t="shared" si="5"/>
+        <v>6210.5338275270151</v>
+      </c>
+      <c r="AF7" s="6">
+        <f t="shared" si="5"/>
+        <v>6396.8498423528254</v>
+      </c>
+      <c r="AG7" s="6">
+        <f t="shared" si="5"/>
+        <v>6588.75533762341</v>
+      </c>
+      <c r="AH7" s="6">
+        <f t="shared" si="5"/>
+        <v>6786.4179977521135</v>
+      </c>
+      <c r="AI7" s="6">
+        <f t="shared" si="5"/>
+        <v>6990.0105376846768</v>
+      </c>
     </row>
     <row r="8" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="T8" s="6">
-        <f>T6+T7</f>
+        <f t="shared" ref="T8:Y8" si="6">T6+T7</f>
         <v>12886</v>
       </c>
       <c r="U8" s="6">
-        <f>U6+U7</f>
+        <f t="shared" si="6"/>
         <v>12438</v>
       </c>
       <c r="V8" s="6">
-        <f>V6+V7</f>
+        <f t="shared" si="6"/>
         <v>12135</v>
       </c>
       <c r="W8" s="6">
-        <f>W6+W7</f>
+        <f t="shared" si="6"/>
         <v>14306</v>
       </c>
       <c r="X8" s="6">
-        <f>X6+X7</f>
+        <f t="shared" si="6"/>
         <v>15801</v>
+      </c>
+      <c r="Y8" s="6">
+        <f t="shared" si="6"/>
+        <v>16984.739799999999</v>
+      </c>
+      <c r="Z8" s="6">
+        <f t="shared" ref="Z8:AI8" si="7">Z6+Z7</f>
+        <v>17833.976790000001</v>
+      </c>
+      <c r="AA8" s="6">
+        <f t="shared" si="7"/>
+        <v>18547.335861600004</v>
+      </c>
+      <c r="AB8" s="6">
+        <f t="shared" si="7"/>
+        <v>19103.755937448004</v>
+      </c>
+      <c r="AC8" s="6">
+        <f t="shared" si="7"/>
+        <v>19542.666238520884</v>
+      </c>
+      <c r="AD8" s="6">
+        <f t="shared" si="7"/>
+        <v>19992.059801084939</v>
+      </c>
+      <c r="AE8" s="6">
+        <f t="shared" si="7"/>
+        <v>20452.197442034085</v>
+      </c>
+      <c r="AF8" s="6">
+        <f t="shared" si="7"/>
+        <v>20923.346729150038</v>
+      </c>
+      <c r="AG8" s="6">
+        <f t="shared" si="7"/>
+        <v>21405.782162156567</v>
+      </c>
+      <c r="AH8" s="6">
+        <f t="shared" si="7"/>
+        <v>21899.785358775931</v>
+      </c>
+      <c r="AI8" s="6">
+        <f t="shared" si="7"/>
+        <v>22405.645245928972</v>
       </c>
     </row>
     <row r="9" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
@@ -1012,24 +1309,68 @@
         <v>18</v>
       </c>
       <c r="T9" s="9">
-        <f>T5-T8</f>
+        <f t="shared" ref="T9:Y9" si="8">T5-T8</f>
         <v>5308</v>
       </c>
       <c r="U9" s="9">
-        <f>U5-U8</f>
+        <f t="shared" si="8"/>
         <v>5376</v>
       </c>
       <c r="V9" s="9">
-        <f>V5-V8</f>
+        <f t="shared" si="8"/>
         <v>4927</v>
       </c>
       <c r="W9" s="9">
-        <f>W5-W8</f>
+        <f t="shared" si="8"/>
         <v>5113</v>
       </c>
       <c r="X9" s="9">
-        <f>X5-X8</f>
+        <f t="shared" si="8"/>
         <v>5524</v>
+      </c>
+      <c r="Y9" s="9">
+        <f t="shared" si="8"/>
+        <v>5922.4402000000009</v>
+      </c>
+      <c r="Z9" s="9">
+        <f t="shared" ref="Z9:AI9" si="9">Z5-Z8</f>
+        <v>6218.5622100000037</v>
+      </c>
+      <c r="AA9" s="9">
+        <f t="shared" si="9"/>
+        <v>6467.3046983999993</v>
+      </c>
+      <c r="AB9" s="9">
+        <f t="shared" si="9"/>
+        <v>6661.3238393520005</v>
+      </c>
+      <c r="AC9" s="9">
+        <f t="shared" si="9"/>
+        <v>6811.5270589111242</v>
+      </c>
+      <c r="AD9" s="9">
+        <f t="shared" si="9"/>
+        <v>6965.2436451445865</v>
+      </c>
+      <c r="AE9" s="9">
+        <f t="shared" si="9"/>
+        <v>7122.5591444543825</v>
+      </c>
+      <c r="AF9" s="9">
+        <f t="shared" si="9"/>
+        <v>7283.5612725425708</v>
+      </c>
+      <c r="AG9" s="9">
+        <f t="shared" si="9"/>
+        <v>7448.3399715485029</v>
+      </c>
+      <c r="AH9" s="9">
+        <f t="shared" si="9"/>
+        <v>7616.9874687412084</v>
+      </c>
+      <c r="AI9" s="9">
+        <f t="shared" si="9"/>
+        <v>7789.5983368106172</v>
       </c>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.3">
@@ -1051,6 +1392,50 @@
       <c r="X10" s="6">
         <v>3568</v>
       </c>
+      <c r="Y10" s="6">
+        <f>X10*1.05</f>
+        <v>3746.4</v>
+      </c>
+      <c r="Z10" s="6">
+        <f>Y10*1.04</f>
+        <v>3896.2560000000003</v>
+      </c>
+      <c r="AA10" s="6">
+        <f>Z10*1.03</f>
+        <v>4013.1436800000006</v>
+      </c>
+      <c r="AB10" s="6">
+        <f>AA10*1.02</f>
+        <v>4093.4065536000007</v>
+      </c>
+      <c r="AC10" s="6">
+        <f>AB10*1.01</f>
+        <v>4134.3406191360009</v>
+      </c>
+      <c r="AD10" s="6">
+        <f t="shared" ref="AD10:AI10" si="10">AC10*1.01</f>
+        <v>4175.6840253273613</v>
+      </c>
+      <c r="AE10" s="6">
+        <f t="shared" si="10"/>
+        <v>4217.4408655806346</v>
+      </c>
+      <c r="AF10" s="6">
+        <f t="shared" si="10"/>
+        <v>4259.6152742364411</v>
+      </c>
+      <c r="AG10" s="6">
+        <f t="shared" si="10"/>
+        <v>4302.2114269788053</v>
+      </c>
+      <c r="AH10" s="6">
+        <f t="shared" si="10"/>
+        <v>4345.2335412485936</v>
+      </c>
+      <c r="AI10" s="6">
+        <f t="shared" si="10"/>
+        <v>4388.6858766610794</v>
+      </c>
     </row>
     <row r="11" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
@@ -1073,30 +1458,107 @@
       <c r="X11" s="6">
         <v>38</v>
       </c>
+      <c r="Y11" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
       <c r="T12" s="9">
-        <f>T9-T10-T11</f>
+        <f t="shared" ref="T12:Y12" si="11">T9-T10-T11</f>
         <v>1175</v>
       </c>
       <c r="U12" s="9">
-        <f>U9-U10-U11</f>
+        <f t="shared" si="11"/>
         <v>2109</v>
       </c>
       <c r="V12" s="9">
-        <f>V9-V10-V11</f>
+        <f t="shared" si="11"/>
         <v>1127</v>
       </c>
       <c r="W12" s="9">
-        <f>W9-W10-W11</f>
+        <f t="shared" si="11"/>
         <v>1426</v>
       </c>
       <c r="X12" s="9">
-        <f>X9-X10-X11</f>
+        <f t="shared" si="11"/>
         <v>1918</v>
+      </c>
+      <c r="Y12" s="9">
+        <f t="shared" si="11"/>
+        <v>2176.0402000000008</v>
+      </c>
+      <c r="Z12" s="9">
+        <f t="shared" ref="Z12:AI12" si="12">Z9-Z10-Z11</f>
+        <v>2322.3062100000034</v>
+      </c>
+      <c r="AA12" s="9">
+        <f t="shared" si="12"/>
+        <v>2454.1610183999987</v>
+      </c>
+      <c r="AB12" s="9">
+        <f t="shared" si="12"/>
+        <v>2567.9172857519998</v>
+      </c>
+      <c r="AC12" s="9">
+        <f t="shared" si="12"/>
+        <v>2677.1864397751233</v>
+      </c>
+      <c r="AD12" s="9">
+        <f t="shared" si="12"/>
+        <v>2789.5596198172252</v>
+      </c>
+      <c r="AE12" s="9">
+        <f t="shared" si="12"/>
+        <v>2905.1182788737478</v>
+      </c>
+      <c r="AF12" s="9">
+        <f t="shared" si="12"/>
+        <v>3023.9459983061297</v>
+      </c>
+      <c r="AG12" s="9">
+        <f t="shared" si="12"/>
+        <v>3146.1285445696976</v>
+      </c>
+      <c r="AH12" s="9">
+        <f t="shared" si="12"/>
+        <v>3271.7539274926148</v>
+      </c>
+      <c r="AI12" s="9">
+        <f t="shared" si="12"/>
+        <v>3400.9124601495378</v>
       </c>
     </row>
     <row r="13" spans="2:35" x14ac:dyDescent="0.3">
@@ -1118,6 +1580,50 @@
       <c r="X13" s="6">
         <v>-354</v>
       </c>
+      <c r="Y13" s="6">
+        <f>X13*1.01</f>
+        <v>-357.54</v>
+      </c>
+      <c r="Z13" s="6">
+        <f t="shared" ref="Z13:AI13" si="13">Y13*1.01</f>
+        <v>-361.11540000000002</v>
+      </c>
+      <c r="AA13" s="6">
+        <f t="shared" si="13"/>
+        <v>-364.72655400000002</v>
+      </c>
+      <c r="AB13" s="6">
+        <f t="shared" si="13"/>
+        <v>-368.37381954</v>
+      </c>
+      <c r="AC13" s="6">
+        <f t="shared" si="13"/>
+        <v>-372.0575577354</v>
+      </c>
+      <c r="AD13" s="6">
+        <f t="shared" si="13"/>
+        <v>-375.77813331275399</v>
+      </c>
+      <c r="AE13" s="6">
+        <f t="shared" si="13"/>
+        <v>-379.53591464588152</v>
+      </c>
+      <c r="AF13" s="6">
+        <f t="shared" si="13"/>
+        <v>-383.33127379234031</v>
+      </c>
+      <c r="AG13" s="6">
+        <f t="shared" si="13"/>
+        <v>-387.1645865302637</v>
+      </c>
+      <c r="AH13" s="6">
+        <f t="shared" si="13"/>
+        <v>-391.03623239556634</v>
+      </c>
+      <c r="AI13" s="6">
+        <f t="shared" si="13"/>
+        <v>-394.94659471952201</v>
+      </c>
     </row>
     <row r="14" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
@@ -1138,30 +1644,118 @@
       <c r="X14" s="6">
         <v>675</v>
       </c>
+      <c r="Y14" s="6">
+        <f>X14*1.01</f>
+        <v>681.75</v>
+      </c>
+      <c r="Z14" s="6">
+        <f t="shared" ref="Z14:AI14" si="14">Y14*1.01</f>
+        <v>688.5675</v>
+      </c>
+      <c r="AA14" s="6">
+        <f t="shared" si="14"/>
+        <v>695.45317499999999</v>
+      </c>
+      <c r="AB14" s="6">
+        <f t="shared" si="14"/>
+        <v>702.40770674999999</v>
+      </c>
+      <c r="AC14" s="6">
+        <f t="shared" si="14"/>
+        <v>709.43178381749999</v>
+      </c>
+      <c r="AD14" s="6">
+        <f t="shared" si="14"/>
+        <v>716.52610165567501</v>
+      </c>
+      <c r="AE14" s="6">
+        <f t="shared" si="14"/>
+        <v>723.69136267223178</v>
+      </c>
+      <c r="AF14" s="6">
+        <f t="shared" si="14"/>
+        <v>730.92827629895407</v>
+      </c>
+      <c r="AG14" s="6">
+        <f t="shared" si="14"/>
+        <v>738.23755906194367</v>
+      </c>
+      <c r="AH14" s="6">
+        <f t="shared" si="14"/>
+        <v>745.61993465256307</v>
+      </c>
+      <c r="AI14" s="6">
+        <f t="shared" si="14"/>
+        <v>753.07613399908871</v>
+      </c>
     </row>
     <row r="15" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
       <c r="T15" s="9">
-        <f>T12-T13-T14</f>
+        <f t="shared" ref="T15:Y15" si="15">T12-T13-T14</f>
         <v>1322</v>
       </c>
       <c r="U15" s="9">
-        <f>U12-U13-U14</f>
+        <f t="shared" si="15"/>
         <v>2283</v>
       </c>
       <c r="V15" s="9">
-        <f>V12-V13-V14</f>
+        <f t="shared" si="15"/>
         <v>1273</v>
       </c>
       <c r="W15" s="9">
-        <f>W12-W13-W14</f>
+        <f t="shared" si="15"/>
         <v>1221</v>
       </c>
       <c r="X15" s="9">
-        <f>X12-X13-X14</f>
+        <f t="shared" si="15"/>
         <v>1597</v>
+      </c>
+      <c r="Y15" s="9">
+        <f t="shared" si="15"/>
+        <v>1851.8302000000008</v>
+      </c>
+      <c r="Z15" s="9">
+        <f t="shared" ref="Z15:AI15" si="16">Z12-Z13-Z14</f>
+        <v>1994.8541100000034</v>
+      </c>
+      <c r="AA15" s="9">
+        <f t="shared" si="16"/>
+        <v>2123.4343973999985</v>
+      </c>
+      <c r="AB15" s="9">
+        <f t="shared" si="16"/>
+        <v>2233.8833985419997</v>
+      </c>
+      <c r="AC15" s="9">
+        <f t="shared" si="16"/>
+        <v>2339.8122136930233</v>
+      </c>
+      <c r="AD15" s="9">
+        <f t="shared" si="16"/>
+        <v>2448.8116514743042</v>
+      </c>
+      <c r="AE15" s="9">
+        <f t="shared" si="16"/>
+        <v>2560.9628308473975</v>
+      </c>
+      <c r="AF15" s="9">
+        <f t="shared" si="16"/>
+        <v>2676.3489957995157</v>
+      </c>
+      <c r="AG15" s="9">
+        <f t="shared" si="16"/>
+        <v>2795.0555720380175</v>
+      </c>
+      <c r="AH15" s="9">
+        <f t="shared" si="16"/>
+        <v>2917.1702252356181</v>
+      </c>
+      <c r="AI15" s="9">
+        <f t="shared" si="16"/>
+        <v>3042.7829208699713</v>
       </c>
     </row>
     <row r="16" spans="2:35" x14ac:dyDescent="0.3">
@@ -1183,8 +1777,52 @@
       <c r="X16" s="6">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y16" s="6">
+        <f>Y15*0.1</f>
+        <v>185.18302000000008</v>
+      </c>
+      <c r="Z16" s="6">
+        <f t="shared" ref="Z16:AI16" si="17">Z15*0.1</f>
+        <v>199.48541100000034</v>
+      </c>
+      <c r="AA16" s="6">
+        <f t="shared" si="17"/>
+        <v>212.34343973999987</v>
+      </c>
+      <c r="AB16" s="6">
+        <f t="shared" si="17"/>
+        <v>223.38833985419998</v>
+      </c>
+      <c r="AC16" s="6">
+        <f t="shared" si="17"/>
+        <v>233.98122136930235</v>
+      </c>
+      <c r="AD16" s="6">
+        <f t="shared" si="17"/>
+        <v>244.88116514743044</v>
+      </c>
+      <c r="AE16" s="6">
+        <f t="shared" si="17"/>
+        <v>256.09628308473975</v>
+      </c>
+      <c r="AF16" s="6">
+        <f t="shared" si="17"/>
+        <v>267.63489957995159</v>
+      </c>
+      <c r="AG16" s="6">
+        <f t="shared" si="17"/>
+        <v>279.50555720380174</v>
+      </c>
+      <c r="AH16" s="6">
+        <f t="shared" si="17"/>
+        <v>291.71702252356181</v>
+      </c>
+      <c r="AI16" s="6">
+        <f t="shared" si="17"/>
+        <v>304.27829208699717</v>
+      </c>
+    </row>
+    <row r="17" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
@@ -1205,318 +1843,1423 @@
       <c r="X17" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="Y17" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="T18" s="9">
-        <f>T15-T16-T17</f>
+        <f t="shared" ref="T18:Y18" si="18">T15-T16-T17</f>
         <v>1119</v>
       </c>
       <c r="U18" s="9">
-        <f>U15-U16-U17</f>
+        <f t="shared" si="18"/>
         <v>1846</v>
       </c>
       <c r="V18" s="9">
-        <f>V15-V16-V17</f>
+        <f t="shared" si="18"/>
         <v>1062</v>
       </c>
       <c r="W18" s="9">
-        <f>W15-W16-W17</f>
+        <f t="shared" si="18"/>
         <v>1227</v>
       </c>
       <c r="X18" s="9">
-        <f>X15-X16-X17</f>
+        <f t="shared" si="18"/>
         <v>1502</v>
       </c>
-    </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y18" s="9">
+        <f t="shared" si="18"/>
+        <v>1666.6471800000006</v>
+      </c>
+      <c r="Z18" s="9">
+        <f t="shared" ref="Z18:AI18" si="19">Z15-Z16-Z17</f>
+        <v>1795.3686990000031</v>
+      </c>
+      <c r="AA18" s="9">
+        <f t="shared" si="19"/>
+        <v>1911.0909576599986</v>
+      </c>
+      <c r="AB18" s="9">
+        <f t="shared" si="19"/>
+        <v>2010.4950586877997</v>
+      </c>
+      <c r="AC18" s="9">
+        <f t="shared" si="19"/>
+        <v>2105.8309923237211</v>
+      </c>
+      <c r="AD18" s="9">
+        <f t="shared" si="19"/>
+        <v>2203.930486326874</v>
+      </c>
+      <c r="AE18" s="9">
+        <f t="shared" si="19"/>
+        <v>2304.8665477626578</v>
+      </c>
+      <c r="AF18" s="9">
+        <f t="shared" si="19"/>
+        <v>2408.714096219564</v>
+      </c>
+      <c r="AG18" s="9">
+        <f t="shared" si="19"/>
+        <v>2515.5500148342157</v>
+      </c>
+      <c r="AH18" s="9">
+        <f t="shared" si="19"/>
+        <v>2625.4532027120563</v>
+      </c>
+      <c r="AI18" s="9">
+        <f t="shared" si="19"/>
+        <v>2738.5046287829741</v>
+      </c>
+      <c r="AJ18" s="2">
+        <f>AI18*(1+$AL$23)</f>
+        <v>2711.1195824951442</v>
+      </c>
+      <c r="AK18" s="2">
+        <f t="shared" ref="AK18:CV18" si="20">AJ18*(1+$AL$23)</f>
+        <v>2684.0083866701925</v>
+      </c>
+      <c r="AL18" s="2">
+        <f t="shared" si="20"/>
+        <v>2657.1683028034904</v>
+      </c>
+      <c r="AM18" s="2">
+        <f t="shared" si="20"/>
+        <v>2630.5966197754556</v>
+      </c>
+      <c r="AN18" s="2">
+        <f t="shared" si="20"/>
+        <v>2604.2906535777011</v>
+      </c>
+      <c r="AO18" s="2">
+        <f t="shared" si="20"/>
+        <v>2578.247747041924</v>
+      </c>
+      <c r="AP18" s="2">
+        <f t="shared" si="20"/>
+        <v>2552.4652695715049</v>
+      </c>
+      <c r="AQ18" s="2">
+        <f t="shared" si="20"/>
+        <v>2526.9406168757901</v>
+      </c>
+      <c r="AR18" s="2">
+        <f t="shared" si="20"/>
+        <v>2501.6712107070321</v>
+      </c>
+      <c r="AS18" s="2">
+        <f t="shared" si="20"/>
+        <v>2476.6544985999617</v>
+      </c>
+      <c r="AT18" s="2">
+        <f t="shared" si="20"/>
+        <v>2451.8879536139621</v>
+      </c>
+      <c r="AU18" s="2">
+        <f t="shared" si="20"/>
+        <v>2427.3690740778225</v>
+      </c>
+      <c r="AV18" s="2">
+        <f t="shared" si="20"/>
+        <v>2403.095383337044</v>
+      </c>
+      <c r="AW18" s="2">
+        <f t="shared" si="20"/>
+        <v>2379.0644295036736</v>
+      </c>
+      <c r="AX18" s="2">
+        <f t="shared" si="20"/>
+        <v>2355.273785208637</v>
+      </c>
+      <c r="AY18" s="2">
+        <f t="shared" si="20"/>
+        <v>2331.7210473565506</v>
+      </c>
+      <c r="AZ18" s="2">
+        <f t="shared" si="20"/>
+        <v>2308.4038368829852</v>
+      </c>
+      <c r="BA18" s="2">
+        <f t="shared" si="20"/>
+        <v>2285.3197985141551</v>
+      </c>
+      <c r="BB18" s="2">
+        <f t="shared" si="20"/>
+        <v>2262.4666005290137</v>
+      </c>
+      <c r="BC18" s="2">
+        <f t="shared" si="20"/>
+        <v>2239.8419345237235</v>
+      </c>
+      <c r="BD18" s="2">
+        <f t="shared" si="20"/>
+        <v>2217.443515178486</v>
+      </c>
+      <c r="BE18" s="2">
+        <f t="shared" si="20"/>
+        <v>2195.269080026701</v>
+      </c>
+      <c r="BF18" s="2">
+        <f t="shared" si="20"/>
+        <v>2173.3163892264338</v>
+      </c>
+      <c r="BG18" s="2">
+        <f t="shared" si="20"/>
+        <v>2151.5832253341696</v>
+      </c>
+      <c r="BH18" s="2">
+        <f t="shared" si="20"/>
+        <v>2130.067393080828</v>
+      </c>
+      <c r="BI18" s="2">
+        <f t="shared" si="20"/>
+        <v>2108.7667191500195</v>
+      </c>
+      <c r="BJ18" s="2">
+        <f t="shared" si="20"/>
+        <v>2087.6790519585193</v>
+      </c>
+      <c r="BK18" s="2">
+        <f t="shared" si="20"/>
+        <v>2066.8022614389342</v>
+      </c>
+      <c r="BL18" s="2">
+        <f t="shared" si="20"/>
+        <v>2046.1342388245448</v>
+      </c>
+      <c r="BM18" s="2">
+        <f t="shared" si="20"/>
+        <v>2025.6728964362994</v>
+      </c>
+      <c r="BN18" s="2">
+        <f t="shared" si="20"/>
+        <v>2005.4161674719364</v>
+      </c>
+      <c r="BO18" s="2">
+        <f t="shared" si="20"/>
+        <v>1985.3620057972171</v>
+      </c>
+      <c r="BP18" s="2">
+        <f t="shared" si="20"/>
+        <v>1965.5083857392449</v>
+      </c>
+      <c r="BQ18" s="2">
+        <f t="shared" si="20"/>
+        <v>1945.8533018818525</v>
+      </c>
+      <c r="BR18" s="2">
+        <f t="shared" si="20"/>
+        <v>1926.394768863034</v>
+      </c>
+      <c r="BS18" s="2">
+        <f t="shared" si="20"/>
+        <v>1907.1308211744035</v>
+      </c>
+      <c r="BT18" s="2">
+        <f t="shared" si="20"/>
+        <v>1888.0595129626595</v>
+      </c>
+      <c r="BU18" s="2">
+        <f t="shared" si="20"/>
+        <v>1869.178917833033</v>
+      </c>
+      <c r="BV18" s="2">
+        <f t="shared" si="20"/>
+        <v>1850.4871286547027</v>
+      </c>
+      <c r="BW18" s="2">
+        <f t="shared" si="20"/>
+        <v>1831.9822573681556</v>
+      </c>
+      <c r="BX18" s="2">
+        <f t="shared" si="20"/>
+        <v>1813.6624347944739</v>
+      </c>
+      <c r="BY18" s="2">
+        <f t="shared" si="20"/>
+        <v>1795.5258104465292</v>
+      </c>
+      <c r="BZ18" s="2">
+        <f t="shared" si="20"/>
+        <v>1777.570552342064</v>
+      </c>
+      <c r="CA18" s="2">
+        <f t="shared" si="20"/>
+        <v>1759.7948468186435</v>
+      </c>
+      <c r="CB18" s="2">
+        <f t="shared" si="20"/>
+        <v>1742.1968983504571</v>
+      </c>
+      <c r="CC18" s="2">
+        <f t="shared" si="20"/>
+        <v>1724.7749293669526</v>
+      </c>
+      <c r="CD18" s="2">
+        <f t="shared" si="20"/>
+        <v>1707.527180073283</v>
+      </c>
+      <c r="CE18" s="2">
+        <f t="shared" si="20"/>
+        <v>1690.4519082725501</v>
+      </c>
+      <c r="CF18" s="2">
+        <f t="shared" si="20"/>
+        <v>1673.5473891898246</v>
+      </c>
+      <c r="CG18" s="2">
+        <f t="shared" si="20"/>
+        <v>1656.8119152979264</v>
+      </c>
+      <c r="CH18" s="2">
+        <f t="shared" si="20"/>
+        <v>1640.2437961449471</v>
+      </c>
+      <c r="CI18" s="2">
+        <f t="shared" si="20"/>
+        <v>1623.8413581834975</v>
+      </c>
+      <c r="CJ18" s="2">
+        <f t="shared" si="20"/>
+        <v>1607.6029446016626</v>
+      </c>
+      <c r="CK18" s="2">
+        <f t="shared" si="20"/>
+        <v>1591.5269151556458</v>
+      </c>
+      <c r="CL18" s="2">
+        <f t="shared" si="20"/>
+        <v>1575.6116460040894</v>
+      </c>
+      <c r="CM18" s="2">
+        <f t="shared" si="20"/>
+        <v>1559.8555295440485</v>
+      </c>
+      <c r="CN18" s="2">
+        <f t="shared" si="20"/>
+        <v>1544.256974248608</v>
+      </c>
+      <c r="CO18" s="2">
+        <f t="shared" si="20"/>
+        <v>1528.8144045061219</v>
+      </c>
+      <c r="CP18" s="2">
+        <f t="shared" si="20"/>
+        <v>1513.5262604610607</v>
+      </c>
+      <c r="CQ18" s="2">
+        <f t="shared" si="20"/>
+        <v>1498.39099785645</v>
+      </c>
+      <c r="CR18" s="2">
+        <f t="shared" si="20"/>
+        <v>1483.4070878778855</v>
+      </c>
+      <c r="CS18" s="2">
+        <f t="shared" si="20"/>
+        <v>1468.5730169991066</v>
+      </c>
+      <c r="CT18" s="2">
+        <f t="shared" si="20"/>
+        <v>1453.8872868291155</v>
+      </c>
+      <c r="CU18" s="2">
+        <f t="shared" si="20"/>
+        <v>1439.3484139608242</v>
+      </c>
+      <c r="CV18" s="2">
+        <f t="shared" si="20"/>
+        <v>1424.954929821216</v>
+      </c>
+      <c r="CW18" s="2">
+        <f t="shared" ref="CW18:EO18" si="21">CV18*(1+$AL$23)</f>
+        <v>1410.7053805230039</v>
+      </c>
+      <c r="CX18" s="2">
+        <f t="shared" si="21"/>
+        <v>1396.5983267177739</v>
+      </c>
+      <c r="CY18" s="2">
+        <f t="shared" si="21"/>
+        <v>1382.6323434505962</v>
+      </c>
+      <c r="CZ18" s="2">
+        <f t="shared" si="21"/>
+        <v>1368.8060200160903</v>
+      </c>
+      <c r="DA18" s="2">
+        <f t="shared" si="21"/>
+        <v>1355.1179598159295</v>
+      </c>
+      <c r="DB18" s="2">
+        <f t="shared" si="21"/>
+        <v>1341.5667802177702</v>
+      </c>
+      <c r="DC18" s="2">
+        <f t="shared" si="21"/>
+        <v>1328.1511124155925</v>
+      </c>
+      <c r="DD18" s="2">
+        <f t="shared" si="21"/>
+        <v>1314.8696012914365</v>
+      </c>
+      <c r="DE18" s="2">
+        <f t="shared" si="21"/>
+        <v>1301.7209052785222</v>
+      </c>
+      <c r="DF18" s="2">
+        <f t="shared" si="21"/>
+        <v>1288.7036962257368</v>
+      </c>
+      <c r="DG18" s="2">
+        <f t="shared" si="21"/>
+        <v>1275.8166592634796</v>
+      </c>
+      <c r="DH18" s="2">
+        <f t="shared" si="21"/>
+        <v>1263.0584926708448</v>
+      </c>
+      <c r="DI18" s="2">
+        <f t="shared" si="21"/>
+        <v>1250.4279077441363</v>
+      </c>
+      <c r="DJ18" s="2">
+        <f t="shared" si="21"/>
+        <v>1237.9236286666949</v>
+      </c>
+      <c r="DK18" s="2">
+        <f t="shared" si="21"/>
+        <v>1225.5443923800278</v>
+      </c>
+      <c r="DL18" s="2">
+        <f t="shared" si="21"/>
+        <v>1213.2889484562274</v>
+      </c>
+      <c r="DM18" s="2">
+        <f t="shared" si="21"/>
+        <v>1201.1560589716651</v>
+      </c>
+      <c r="DN18" s="2">
+        <f t="shared" si="21"/>
+        <v>1189.1444983819483</v>
+      </c>
+      <c r="DO18" s="2">
+        <f t="shared" si="21"/>
+        <v>1177.2530533981289</v>
+      </c>
+      <c r="DP18" s="2">
+        <f t="shared" si="21"/>
+        <v>1165.4805228641476</v>
+      </c>
+      <c r="DQ18" s="2">
+        <f t="shared" si="21"/>
+        <v>1153.8257176355062</v>
+      </c>
+      <c r="DR18" s="2">
+        <f t="shared" si="21"/>
+        <v>1142.2874604591511</v>
+      </c>
+      <c r="DS18" s="2">
+        <f t="shared" si="21"/>
+        <v>1130.8645858545597</v>
+      </c>
+      <c r="DT18" s="2">
+        <f t="shared" si="21"/>
+        <v>1119.5559399960141</v>
+      </c>
+      <c r="DU18" s="2">
+        <f t="shared" si="21"/>
+        <v>1108.360380596054</v>
+      </c>
+      <c r="DV18" s="2">
+        <f t="shared" si="21"/>
+        <v>1097.2767767900934</v>
+      </c>
+      <c r="DW18" s="2">
+        <f t="shared" si="21"/>
+        <v>1086.3040090221925</v>
+      </c>
+      <c r="DX18" s="2">
+        <f t="shared" si="21"/>
+        <v>1075.4409689319707</v>
+      </c>
+      <c r="DY18" s="2">
+        <f t="shared" si="21"/>
+        <v>1064.6865592426509</v>
+      </c>
+      <c r="DZ18" s="2">
+        <f t="shared" si="21"/>
+        <v>1054.0396936502243</v>
+      </c>
+      <c r="EA18" s="2">
+        <f t="shared" si="21"/>
+        <v>1043.4992967137221</v>
+      </c>
+      <c r="EB18" s="2">
+        <f t="shared" si="21"/>
+        <v>1033.0643037465848</v>
+      </c>
+      <c r="EC18" s="2">
+        <f t="shared" si="21"/>
+        <v>1022.7336607091189</v>
+      </c>
+      <c r="ED18" s="2">
+        <f t="shared" si="21"/>
+        <v>1012.5063241020277</v>
+      </c>
+      <c r="EE18" s="2">
+        <f t="shared" si="21"/>
+        <v>1002.3812608610075</v>
+      </c>
+      <c r="EF18" s="2">
+        <f t="shared" si="21"/>
+        <v>992.35744825239738</v>
+      </c>
+      <c r="EG18" s="2">
+        <f t="shared" si="21"/>
+        <v>982.43387376987334</v>
+      </c>
+      <c r="EH18" s="2">
+        <f t="shared" si="21"/>
+        <v>972.60953503217456</v>
+      </c>
+      <c r="EI18" s="2">
+        <f t="shared" si="21"/>
+        <v>962.88343968185279</v>
+      </c>
+      <c r="EJ18" s="2">
+        <f t="shared" si="21"/>
+        <v>953.25460528503424</v>
+      </c>
+      <c r="EK18" s="2">
+        <f t="shared" si="21"/>
+        <v>943.72205923218394</v>
+      </c>
+      <c r="EL18" s="2">
+        <f t="shared" si="21"/>
+        <v>934.28483863986207</v>
+      </c>
+      <c r="EM18" s="2">
+        <f t="shared" si="21"/>
+        <v>924.94199025346347</v>
+      </c>
+      <c r="EN18" s="2">
+        <f t="shared" si="21"/>
+        <v>915.6925703509288</v>
+      </c>
+      <c r="EO18" s="2">
+        <f t="shared" si="21"/>
+        <v>906.53564464741953</v>
+      </c>
+    </row>
+    <row r="19" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>2</v>
       </c>
       <c r="T19" s="6">
-        <f>188.3</f>
+        <f t="shared" ref="T19:Y19" si="22">188.3</f>
         <v>188.3</v>
       </c>
       <c r="U19" s="6">
-        <f>188.3</f>
+        <f t="shared" si="22"/>
         <v>188.3</v>
       </c>
       <c r="V19" s="6">
-        <f>188.3</f>
+        <f t="shared" si="22"/>
         <v>188.3</v>
       </c>
       <c r="W19" s="6">
-        <f>188.3</f>
+        <f t="shared" si="22"/>
         <v>188.3</v>
       </c>
       <c r="X19" s="6">
-        <f>188.3</f>
+        <f t="shared" si="22"/>
         <v>188.3</v>
       </c>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y19" s="6">
+        <f t="shared" si="22"/>
+        <v>188.3</v>
+      </c>
+      <c r="Z19" s="6">
+        <f t="shared" ref="Z19:AI19" si="23">188.3</f>
+        <v>188.3</v>
+      </c>
+      <c r="AA19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AB19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AC19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AD19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AE19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AF19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AG19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AH19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+      <c r="AI19" s="6">
+        <f t="shared" si="23"/>
+        <v>188.3</v>
+      </c>
+    </row>
+    <row r="20" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
       <c r="T20" s="8">
-        <f>T18/T19</f>
+        <f t="shared" ref="T20:Y20" si="24">T18/T19</f>
         <v>5.9426447158789166</v>
       </c>
       <c r="U20" s="8">
-        <f>U18/U19</f>
+        <f t="shared" si="24"/>
         <v>9.8035050451407315</v>
       </c>
       <c r="V20" s="8">
-        <f>V18/V19</f>
+        <f t="shared" si="24"/>
         <v>5.6399362719065316</v>
       </c>
       <c r="W20" s="8">
-        <f>W18/W19</f>
+        <f t="shared" si="24"/>
         <v>6.5161975570897503</v>
       </c>
       <c r="X20" s="8">
-        <f>X18/X19</f>
+        <f t="shared" si="24"/>
         <v>7.9766330323951138</v>
       </c>
-    </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y20" s="8">
+        <f t="shared" si="24"/>
+        <v>8.8510206054168901</v>
+      </c>
+      <c r="Z20" s="8">
+        <f t="shared" ref="Z20:AI20" si="25">Z18/Z19</f>
+        <v>9.534618688263425</v>
+      </c>
+      <c r="AA20" s="8">
+        <f t="shared" si="25"/>
+        <v>10.149181931279864</v>
+      </c>
+      <c r="AB20" s="8">
+        <f t="shared" si="25"/>
+        <v>10.677084751395643</v>
+      </c>
+      <c r="AC20" s="8">
+        <f t="shared" si="25"/>
+        <v>11.183382858862034</v>
+      </c>
+      <c r="AD20" s="8">
+        <f t="shared" si="25"/>
+        <v>11.704357335777344</v>
+      </c>
+      <c r="AE20" s="8">
+        <f t="shared" si="25"/>
+        <v>12.240395898898873</v>
+      </c>
+      <c r="AF20" s="8">
+        <f t="shared" si="25"/>
+        <v>12.791896421771449</v>
+      </c>
+      <c r="AG20" s="8">
+        <f t="shared" si="25"/>
+        <v>13.359267205704809</v>
+      </c>
+      <c r="AH20" s="8">
+        <f t="shared" si="25"/>
+        <v>13.942927258162804</v>
+      </c>
+      <c r="AI20" s="8">
+        <f t="shared" si="25"/>
+        <v>14.543306578773096</v>
+      </c>
+    </row>
+    <row r="22" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
       <c r="T22" s="10"/>
       <c r="U22" s="10">
-        <f t="shared" ref="U22:W24" si="0">U3/T3-1</f>
+        <f t="shared" ref="U22:W24" si="26">U3/T3-1</f>
         <v>-3.1293719166482603E-2</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>-8.0495591365156605E-2</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>0.13201620236422262</v>
       </c>
       <c r="X22" s="10">
         <f>X3/W3-1</f>
         <v>0.10515554257338988</v>
       </c>
-    </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y22" s="10">
+        <f t="shared" ref="Y22:AI24" si="27">Y3/X3-1</f>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="Z22" s="10">
+        <f t="shared" si="27"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AA22" s="10">
+        <f t="shared" si="27"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB22" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC22" s="10">
+        <f t="shared" si="27"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD22" s="10">
+        <f t="shared" si="27"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE22" s="10">
+        <f t="shared" si="27"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF22" s="10">
+        <f t="shared" si="27"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AG22" s="10">
+        <f t="shared" si="27"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH22" s="10">
+        <f t="shared" si="27"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AI22" s="10">
+        <f t="shared" si="27"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
       <c r="T23" s="10"/>
       <c r="U23" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>9.7550401040538137E-3</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>6.5908115070845819E-2</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>0.15307150050352458</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23:X24" si="1">X4/W4-1</f>
+        <f t="shared" ref="X23:X24" si="28">X4/W4-1</f>
         <v>8.1397379912663714E-2</v>
       </c>
-    </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y23" s="10">
+        <f t="shared" si="27"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="Z23" s="10">
+        <f t="shared" si="27"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AA23" s="10">
+        <f t="shared" si="27"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AI23" s="10">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AK23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL23" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="24" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
       <c r="T24" s="11"/>
       <c r="U24" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>-2.0886006375728239E-2</v>
       </c>
       <c r="V24" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>-4.2213988997417795E-2</v>
       </c>
       <c r="W24" s="11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="26"/>
         <v>0.13814324229281438</v>
       </c>
       <c r="X24" s="11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="28"/>
         <v>9.815129512333276E-2</v>
       </c>
-    </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y24" s="11">
+        <f t="shared" si="27"/>
+        <v>7.4193669402110141E-2</v>
+      </c>
+      <c r="Z24" s="11">
+        <f t="shared" si="27"/>
+        <v>5.0000000000000266E-2</v>
+      </c>
+      <c r="AA24" s="11">
+        <f t="shared" si="27"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB24" s="11">
+        <f t="shared" si="27"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC24" s="11">
+        <f t="shared" si="27"/>
+        <v>2.2864804834117569E-2</v>
+      </c>
+      <c r="AD24" s="11">
+        <f t="shared" si="27"/>
+        <v>2.2884788845207726E-2</v>
+      </c>
+      <c r="AE24" s="11">
+        <f t="shared" si="27"/>
+        <v>2.2904855505690547E-2</v>
+      </c>
+      <c r="AF24" s="11">
+        <f t="shared" si="27"/>
+        <v>2.2925004368448132E-2</v>
+      </c>
+      <c r="AG24" s="11">
+        <f t="shared" si="27"/>
+        <v>2.2945234974837581E-2</v>
+      </c>
+      <c r="AH24" s="11">
+        <f t="shared" si="27"/>
+        <v>2.2965546854673224E-2</v>
+      </c>
+      <c r="AI24" s="11">
+        <f t="shared" si="27"/>
+        <v>2.2985939526218857E-2</v>
+      </c>
+      <c r="AK24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL24" s="10">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="25" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" ref="T25:W25" si="2">(T3-T6)/T3</f>
+        <f t="shared" ref="T25:W25" si="29">(T3-T6)/T3</f>
         <v>0.3031440983727266</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0.31536941319550016</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0.3093328924526742</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="29"/>
         <v>0.29085730977070251</v>
       </c>
       <c r="X25" s="10">
         <f>(X3-X6)/X3</f>
         <v>0.27190432139553322</v>
       </c>
-    </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y25" s="10">
+        <f t="shared" ref="Y25:AI25" si="30">(Y3-Y6)/Y3</f>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="Z25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="AA25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AB25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AC25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AD25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="AE25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AF25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AG25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.26999999999999996</v>
+      </c>
+      <c r="AH25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AI25" s="10">
+        <f t="shared" si="30"/>
+        <v>0.27</v>
+      </c>
+      <c r="AK25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL25" s="6">
+        <f>NPV(AL24,Y18:EO18)</f>
+        <v>28113.120561901978</v>
+      </c>
+    </row>
+    <row r="26" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" ref="T26:W26" si="3">(T4-T7)/T4</f>
+        <f t="shared" ref="T26:W26" si="31">(T4-T7)/T4</f>
         <v>0.25818339475395619</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="31"/>
         <v>0.2634177758694719</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="31"/>
         <v>0.23867069486404835</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="3"/>
+        <f t="shared" si="31"/>
         <v>0.19737991266375546</v>
       </c>
       <c r="X26" s="10">
         <f>(X4-X7)/X4</f>
         <v>0.22758843482474561</v>
       </c>
-    </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y26" s="10">
+        <f t="shared" ref="Y26:AI26" si="32">(Y4-Y7)/Y4</f>
+        <v>0.22999999999999993</v>
+      </c>
+      <c r="Z26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.23</v>
+      </c>
+      <c r="AA26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="AB26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="AC26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="AD26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AE26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AF26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.23</v>
+      </c>
+      <c r="AG26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="AH26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AI26" s="10">
+        <f t="shared" si="32"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="AK26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL26" s="6">
+        <f>Main!D8</f>
+        <v>-11621</v>
+      </c>
+    </row>
+    <row r="27" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>49</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" ref="T27:W27" si="4">T9/T5</f>
+        <f t="shared" ref="T27:W27" si="33">T9/T5</f>
         <v>0.29174453116412002</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="33"/>
         <v>0.30178511283260356</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="33"/>
         <v>0.28877036689719843</v>
       </c>
       <c r="W27" s="10">
-        <f t="shared" si="4"/>
+        <f t="shared" si="33"/>
         <v>0.26329883104176321</v>
       </c>
       <c r="X27" s="10">
         <f>X9/X5</f>
         <v>0.25903868698710436</v>
       </c>
-    </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y27" s="10">
+        <f t="shared" ref="Y27:AI27" si="34">Y9/Y5</f>
+        <v>0.25854078066352998</v>
+      </c>
+      <c r="Z27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25854078066353003</v>
+      </c>
+      <c r="AA27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25854078066352987</v>
+      </c>
+      <c r="AB27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25854078066352992</v>
+      </c>
+      <c r="AC27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25846084461916918</v>
+      </c>
+      <c r="AD27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25838057797723846</v>
+      </c>
+      <c r="AE27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25829998252620701</v>
+      </c>
+      <c r="AF27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25821906010065004</v>
+      </c>
+      <c r="AG27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25813781258130702</v>
+      </c>
+      <c r="AH27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25805624189512477</v>
+      </c>
+      <c r="AI27" s="10">
+        <f t="shared" si="34"/>
+        <v>0.25797435001529051</v>
+      </c>
+      <c r="AK27" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL27" s="6">
+        <f>AL25+AL26</f>
+        <v>16492.120561901978</v>
+      </c>
+    </row>
+    <row r="28" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="T28" s="10"/>
       <c r="U28" s="10">
-        <f t="shared" ref="U28:W28" si="5">U10/T10-1</f>
+        <f t="shared" ref="U28:W28" si="35">U10/T10-1</f>
         <v>-1.0558069381598756E-2</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="35"/>
         <v>-8.5975609756097526E-2</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="35"/>
         <v>0.10507004669779851</v>
       </c>
       <c r="X28" s="10">
         <f>X10/W10-1</f>
         <v>7.6969514035617248E-2</v>
       </c>
-    </row>
-    <row r="29" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y28" s="10">
+        <f t="shared" ref="Y28:AI28" si="36">Y10/X10-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="Z28" s="10">
+        <f t="shared" si="36"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AA28" s="10">
+        <f t="shared" si="36"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AB28" s="10">
+        <f t="shared" si="36"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AC28" s="10">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AD28" s="10">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AE28" s="10">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AF28" s="10">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AG28" s="10">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH28" s="10">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AI28" s="10">
+        <f t="shared" si="36"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AK28" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AL28" s="5">
+        <f>AL27/AI19</f>
+        <v>87.584283387689737</v>
+      </c>
+    </row>
+    <row r="29" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>51</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" ref="T29:W29" si="6">T12/T5</f>
+        <f t="shared" ref="T29:W29" si="37">T12/T5</f>
         <v>6.4581730240738711E-2</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="37"/>
         <v>0.11839003031323678</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="37"/>
         <v>6.6053217676708478E-2</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="37"/>
         <v>7.3433235491013951E-2</v>
       </c>
       <c r="X29" s="10">
         <f>X12/X5</f>
         <v>8.9941383352872217E-2</v>
       </c>
-    </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y29" s="10">
+        <f t="shared" ref="Y29:AI29" si="38">Y12/Y5</f>
+        <v>9.4993805435675663E-2</v>
+      </c>
+      <c r="Z29" s="10">
+        <f t="shared" si="38"/>
+        <v>9.6551395675941024E-2</v>
+      </c>
+      <c r="AA29" s="10">
+        <f t="shared" si="38"/>
+        <v>9.8108985916206121E-2</v>
+      </c>
+      <c r="AB29" s="10">
+        <f t="shared" si="38"/>
+        <v>9.966657615647144E-2</v>
+      </c>
+      <c r="AC29" s="10">
+        <f t="shared" si="38"/>
+        <v>0.1015848373562621</v>
+      </c>
+      <c r="AD29" s="10">
+        <f t="shared" si="38"/>
+        <v>0.10348066249954969</v>
+      </c>
+      <c r="AE29" s="10">
+        <f t="shared" si="38"/>
+        <v>0.10535426739894579</v>
+      </c>
+      <c r="AF29" s="10">
+        <f t="shared" si="38"/>
+        <v>0.10720586595754034</v>
+      </c>
+      <c r="AG29" s="10">
+        <f t="shared" si="38"/>
+        <v>0.10903567018920471</v>
+      </c>
+      <c r="AH29" s="10">
+        <f t="shared" si="38"/>
+        <v>0.11084389023865468</v>
+      </c>
+      <c r="AI29" s="10">
+        <f t="shared" si="38"/>
+        <v>0.11263073440128135</v>
+      </c>
+      <c r="AK29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AL29" s="5">
+        <f>Main!D3</f>
+        <v>212.27</v>
+      </c>
+    </row>
+    <row r="30" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>25</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" ref="T30:W30" si="7">T16/T15</f>
+        <f t="shared" ref="T30:W30" si="39">T16/T15</f>
         <v>0.17700453857791226</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="39"/>
         <v>0.19272886552781429</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="39"/>
         <v>0.16653574234092694</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="39"/>
         <v>1.8837018837018837E-2</v>
       </c>
       <c r="X30" s="10">
         <f>X16/X15</f>
         <v>5.3224796493425174E-2</v>
       </c>
-    </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.3">
+      <c r="Y30" s="10">
+        <f t="shared" ref="Y30:AI30" si="40">Y16/Y15</f>
+        <v>0.1</v>
+      </c>
+      <c r="Z30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AA30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AB30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AC30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AD30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AE30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AF30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AG30" s="10">
+        <f t="shared" si="40"/>
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="AH30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AI30" s="10">
+        <f t="shared" si="40"/>
+        <v>0.1</v>
+      </c>
+      <c r="AK30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL30" s="11">
+        <f>AL28/AL29-1</f>
+        <v>-0.58739207901404</v>
+      </c>
+    </row>
+    <row r="31" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>52</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" ref="T31:W31" si="8">T18/T5</f>
+        <f t="shared" ref="T31:W31" si="41">T18/T5</f>
         <v>6.1503792459052437E-2</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="41"/>
         <v>0.10362636128887392</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="41"/>
         <v>6.2243582229515884E-2</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="41"/>
         <v>6.3185539935115095E-2</v>
       </c>
       <c r="X31" s="10">
         <f>X18/X5</f>
         <v>7.0433763188745599E-2</v>
+      </c>
+      <c r="Y31" s="10">
+        <f t="shared" ref="Y31:AI31" si="42">Y18/Y5</f>
+        <v>7.2756540962266011E-2</v>
+      </c>
+      <c r="Z31" s="10">
+        <f t="shared" si="42"/>
+        <v>7.4643624899641686E-2</v>
+      </c>
+      <c r="AA31" s="10">
+        <f t="shared" si="42"/>
+        <v>7.6398897400746749E-2</v>
+      </c>
+      <c r="AB31" s="10">
+        <f t="shared" si="42"/>
+        <v>7.8031780848516391E-2</v>
+      </c>
+      <c r="AC31" s="10">
+        <f t="shared" si="42"/>
+        <v>7.9904968767490842E-2</v>
+      </c>
+      <c r="AD31" s="10">
+        <f t="shared" si="42"/>
+        <v>8.1756340752811241E-2</v>
+      </c>
+      <c r="AE31" s="10">
+        <f t="shared" si="42"/>
+        <v>8.3586106754321599E-2</v>
+      </c>
+      <c r="AF31" s="10">
+        <f t="shared" si="42"/>
+        <v>8.539447485967E-2</v>
+      </c>
+      <c r="AG31" s="10">
+        <f t="shared" si="42"/>
+        <v>8.7181651314068298E-2</v>
+      </c>
+      <c r="AH31" s="10">
+        <f t="shared" si="42"/>
+        <v>8.8947840539818981E-2</v>
+      </c>
+      <c r="AI31" s="10">
+        <f t="shared" si="42"/>
+        <v>9.0693245155617053E-2</v>
+      </c>
+      <c r="AK31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL31" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LHX.xlsx
+++ b/Financial Analysis/LHX.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A4256F-A72C-4A92-AF6A-BED080EE7A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F6F2F1-31AD-4D24-9DBD-58F98712BDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C2D3018F-E467-4E1E-BD9F-9383343E0F25}"/>
   </bookViews>
@@ -718,17 +718,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>212.27</v>
+        <v>277.22000000000003</v>
       </c>
       <c r="E3" s="4">
-        <v>45771</v>
+        <v>45898</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45805</v>
+        <v>45898</v>
       </c>
       <c r="G3" s="4">
-        <v>45771</v>
+        <v>45953</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -736,11 +736,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>188.3</f>
-        <v>188.3</v>
+        <v>187.1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -749,7 +748,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>39970.441000000006</v>
+        <v>51867.862000000001</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -757,11 +756,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="6">
-        <f>615</f>
-        <v>615</v>
+        <f>482</f>
+        <v>482</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -769,11 +768,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="6">
-        <f>515+640+11081</f>
-        <v>12236</v>
+        <f>985+141+10976</f>
+        <v>12102</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -782,7 +781,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-11621</v>
+        <v>-11620</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -791,7 +790,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>51591.441000000006</v>
+        <v>63487.862000000001</v>
       </c>
     </row>
   </sheetData>
@@ -914,6 +913,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="P3" s="6"/>
       <c r="T3" s="6">
         <v>13581</v>
       </c>
@@ -978,6 +978,7 @@
       <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="P4" s="6"/>
       <c r="T4" s="6">
         <v>4613</v>
       </c>
@@ -1042,6 +1043,18 @@
       <c r="B5" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="K5" s="9">
+        <v>5211</v>
+      </c>
+      <c r="L5" s="9">
+        <v>5299</v>
+      </c>
+      <c r="O5" s="9">
+        <v>5132</v>
+      </c>
+      <c r="P5" s="9">
+        <v>5426</v>
+      </c>
       <c r="T5" s="9">
         <f t="shared" ref="T5:Y5" si="2">T3+T4</f>
         <v>18194</v>
@@ -1111,6 +1124,10 @@
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
       <c r="T6" s="6">
         <v>9464</v>
       </c>
@@ -1175,6 +1192,10 @@
       <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
       <c r="T7" s="6">
         <v>3422</v>
       </c>
@@ -1239,6 +1260,18 @@
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="K8" s="6">
+        <v>3863</v>
+      </c>
+      <c r="L8" s="6">
+        <v>3939</v>
+      </c>
+      <c r="O8" s="6">
+        <v>3782</v>
+      </c>
+      <c r="P8" s="6">
+        <v>4091</v>
+      </c>
       <c r="T8" s="6">
         <f t="shared" ref="T8:Y8" si="6">T6+T7</f>
         <v>12886</v>
@@ -1308,68 +1341,84 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="K9" s="9">
+        <f t="shared" ref="K9" si="8">K5-K8</f>
+        <v>1348</v>
+      </c>
+      <c r="L9" s="9">
+        <f t="shared" ref="L9" si="9">L5-L8</f>
+        <v>1360</v>
+      </c>
+      <c r="O9" s="9">
+        <f t="shared" ref="O9:P9" si="10">O5-O8</f>
+        <v>1350</v>
+      </c>
+      <c r="P9" s="9">
+        <f t="shared" si="10"/>
+        <v>1335</v>
+      </c>
       <c r="T9" s="9">
-        <f t="shared" ref="T9:Y9" si="8">T5-T8</f>
+        <f t="shared" ref="T9:Y9" si="11">T5-T8</f>
         <v>5308</v>
       </c>
       <c r="U9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5376</v>
       </c>
       <c r="V9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>4927</v>
       </c>
       <c r="W9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5113</v>
       </c>
       <c r="X9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5524</v>
       </c>
       <c r="Y9" s="9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>5922.4402000000009</v>
       </c>
       <c r="Z9" s="9">
-        <f t="shared" ref="Z9:AI9" si="9">Z5-Z8</f>
+        <f t="shared" ref="Z9:AI9" si="12">Z5-Z8</f>
         <v>6218.5622100000037</v>
       </c>
       <c r="AA9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>6467.3046983999993</v>
       </c>
       <c r="AB9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>6661.3238393520005</v>
       </c>
       <c r="AC9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>6811.5270589111242</v>
       </c>
       <c r="AD9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>6965.2436451445865</v>
       </c>
       <c r="AE9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7122.5591444543825</v>
       </c>
       <c r="AF9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7283.5612725425708</v>
       </c>
       <c r="AG9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7448.3399715485029</v>
       </c>
       <c r="AH9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7616.9874687412084</v>
       </c>
       <c r="AI9" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>7789.5983368106172</v>
       </c>
     </row>
@@ -1377,6 +1426,18 @@
       <c r="B10" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="K10" s="6">
+        <v>970</v>
+      </c>
+      <c r="L10" s="6">
+        <v>884</v>
+      </c>
+      <c r="O10" s="6">
+        <v>825</v>
+      </c>
+      <c r="P10" s="6">
+        <v>764</v>
+      </c>
       <c r="T10" s="6">
         <v>3315</v>
       </c>
@@ -1393,54 +1454,66 @@
         <v>3568</v>
       </c>
       <c r="Y10" s="6">
-        <f>X10*1.05</f>
-        <v>3746.4</v>
+        <f>X10*0.87</f>
+        <v>3104.16</v>
       </c>
       <c r="Z10" s="6">
         <f>Y10*1.04</f>
-        <v>3896.2560000000003</v>
+        <v>3228.3263999999999</v>
       </c>
       <c r="AA10" s="6">
         <f>Z10*1.03</f>
-        <v>4013.1436800000006</v>
+        <v>3325.1761919999999</v>
       </c>
       <c r="AB10" s="6">
         <f>AA10*1.02</f>
-        <v>4093.4065536000007</v>
+        <v>3391.67971584</v>
       </c>
       <c r="AC10" s="6">
         <f>AB10*1.01</f>
-        <v>4134.3406191360009</v>
+        <v>3425.5965129984002</v>
       </c>
       <c r="AD10" s="6">
-        <f t="shared" ref="AD10:AI10" si="10">AC10*1.01</f>
-        <v>4175.6840253273613</v>
+        <f t="shared" ref="AD10:AI10" si="13">AC10*1.01</f>
+        <v>3459.8524781283841</v>
       </c>
       <c r="AE10" s="6">
-        <f t="shared" si="10"/>
-        <v>4217.4408655806346</v>
+        <f t="shared" si="13"/>
+        <v>3494.4510029096677</v>
       </c>
       <c r="AF10" s="6">
-        <f t="shared" si="10"/>
-        <v>4259.6152742364411</v>
+        <f t="shared" si="13"/>
+        <v>3529.3955129387646</v>
       </c>
       <c r="AG10" s="6">
-        <f t="shared" si="10"/>
-        <v>4302.2114269788053</v>
+        <f t="shared" si="13"/>
+        <v>3564.6894680681521</v>
       </c>
       <c r="AH10" s="6">
-        <f t="shared" si="10"/>
-        <v>4345.2335412485936</v>
+        <f t="shared" si="13"/>
+        <v>3600.3363627488338</v>
       </c>
       <c r="AI10" s="6">
-        <f t="shared" si="10"/>
-        <v>4388.6858766610794</v>
+        <f t="shared" si="13"/>
+        <v>3636.3397263763222</v>
       </c>
     </row>
     <row r="11" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="K11" s="6">
+        <v>0</v>
+      </c>
+      <c r="L11" s="6">
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <v>0</v>
+      </c>
+      <c r="P11" s="6">
+        <v>0</v>
+      </c>
       <c r="T11" s="6">
         <f>51+767</f>
         <v>818</v>
@@ -1496,75 +1569,103 @@
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
+      <c r="K12" s="9">
+        <f t="shared" ref="K12" si="14">K9-K10-K11</f>
+        <v>378</v>
+      </c>
+      <c r="L12" s="9">
+        <f t="shared" ref="L12" si="15">L9-L10-L11</f>
+        <v>476</v>
+      </c>
+      <c r="O12" s="9">
+        <f t="shared" ref="O12:P12" si="16">O9-O10-O11</f>
+        <v>525</v>
+      </c>
+      <c r="P12" s="9">
+        <f t="shared" si="16"/>
+        <v>571</v>
+      </c>
       <c r="T12" s="9">
-        <f t="shared" ref="T12:Y12" si="11">T9-T10-T11</f>
+        <f t="shared" ref="T12:Y12" si="17">T9-T10-T11</f>
         <v>1175</v>
       </c>
       <c r="U12" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>2109</v>
       </c>
       <c r="V12" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>1127</v>
       </c>
       <c r="W12" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>1426</v>
       </c>
       <c r="X12" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="17"/>
         <v>1918</v>
       </c>
       <c r="Y12" s="9">
-        <f t="shared" si="11"/>
-        <v>2176.0402000000008</v>
+        <f t="shared" si="17"/>
+        <v>2818.2802000000011</v>
       </c>
       <c r="Z12" s="9">
-        <f t="shared" ref="Z12:AI12" si="12">Z9-Z10-Z11</f>
-        <v>2322.3062100000034</v>
+        <f t="shared" ref="Z12:AI12" si="18">Z9-Z10-Z11</f>
+        <v>2990.2358100000038</v>
       </c>
       <c r="AA12" s="9">
-        <f t="shared" si="12"/>
-        <v>2454.1610183999987</v>
+        <f t="shared" si="18"/>
+        <v>3142.1285063999994</v>
       </c>
       <c r="AB12" s="9">
-        <f t="shared" si="12"/>
-        <v>2567.9172857519998</v>
+        <f t="shared" si="18"/>
+        <v>3269.6441235120005</v>
       </c>
       <c r="AC12" s="9">
-        <f t="shared" si="12"/>
-        <v>2677.1864397751233</v>
+        <f t="shared" si="18"/>
+        <v>3385.930545912724</v>
       </c>
       <c r="AD12" s="9">
-        <f t="shared" si="12"/>
-        <v>2789.5596198172252</v>
+        <f t="shared" si="18"/>
+        <v>3505.3911670162024</v>
       </c>
       <c r="AE12" s="9">
-        <f t="shared" si="12"/>
-        <v>2905.1182788737478</v>
+        <f t="shared" si="18"/>
+        <v>3628.1081415447147</v>
       </c>
       <c r="AF12" s="9">
-        <f t="shared" si="12"/>
-        <v>3023.9459983061297</v>
+        <f t="shared" si="18"/>
+        <v>3754.1657596038062</v>
       </c>
       <c r="AG12" s="9">
-        <f t="shared" si="12"/>
-        <v>3146.1285445696976</v>
+        <f t="shared" si="18"/>
+        <v>3883.6505034803508</v>
       </c>
       <c r="AH12" s="9">
-        <f t="shared" si="12"/>
-        <v>3271.7539274926148</v>
+        <f t="shared" si="18"/>
+        <v>4016.6511059923746</v>
       </c>
       <c r="AI12" s="9">
-        <f t="shared" si="12"/>
-        <v>3400.9124601495378</v>
+        <f t="shared" si="18"/>
+        <v>4153.2586104342954</v>
       </c>
     </row>
     <row r="13" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="K13" s="6">
+        <v>-88</v>
+      </c>
+      <c r="L13" s="6">
+        <v>-86</v>
+      </c>
+      <c r="O13" s="6">
+        <v>-84</v>
+      </c>
+      <c r="P13" s="6">
+        <v>-105</v>
+      </c>
       <c r="T13" s="6">
         <v>-401</v>
       </c>
@@ -1585,43 +1686,43 @@
         <v>-357.54</v>
       </c>
       <c r="Z13" s="6">
-        <f t="shared" ref="Z13:AI13" si="13">Y13*1.01</f>
+        <f t="shared" ref="Z13:AI13" si="19">Y13*1.01</f>
         <v>-361.11540000000002</v>
       </c>
       <c r="AA13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-364.72655400000002</v>
       </c>
       <c r="AB13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-368.37381954</v>
       </c>
       <c r="AC13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-372.0575577354</v>
       </c>
       <c r="AD13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-375.77813331275399</v>
       </c>
       <c r="AE13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-379.53591464588152</v>
       </c>
       <c r="AF13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-383.33127379234031</v>
       </c>
       <c r="AG13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-387.1645865302637</v>
       </c>
       <c r="AH13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-391.03623239556634</v>
       </c>
       <c r="AI13" s="6">
-        <f t="shared" si="13"/>
+        <f t="shared" si="19"/>
         <v>-394.94659471952201</v>
       </c>
     </row>
@@ -1629,6 +1730,18 @@
       <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="K14" s="6">
+        <v>176</v>
+      </c>
+      <c r="L14" s="6">
+        <v>172</v>
+      </c>
+      <c r="O14" s="6">
+        <v>150</v>
+      </c>
+      <c r="P14" s="6">
+        <v>152</v>
+      </c>
       <c r="T14" s="6">
         <v>254</v>
       </c>
@@ -1649,43 +1762,43 @@
         <v>681.75</v>
       </c>
       <c r="Z14" s="6">
-        <f t="shared" ref="Z14:AI14" si="14">Y14*1.01</f>
+        <f t="shared" ref="Z14:AI14" si="20">Y14*1.01</f>
         <v>688.5675</v>
       </c>
       <c r="AA14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>695.45317499999999</v>
       </c>
       <c r="AB14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>702.40770674999999</v>
       </c>
       <c r="AC14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>709.43178381749999</v>
       </c>
       <c r="AD14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>716.52610165567501</v>
       </c>
       <c r="AE14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>723.69136267223178</v>
       </c>
       <c r="AF14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>730.92827629895407</v>
       </c>
       <c r="AG14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>738.23755906194367</v>
       </c>
       <c r="AH14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>745.61993465256307</v>
       </c>
       <c r="AI14" s="6">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>753.07613399908871</v>
       </c>
     </row>
@@ -1693,75 +1806,103 @@
       <c r="B15" s="2" t="s">
         <v>24</v>
       </c>
+      <c r="K15" s="9">
+        <f t="shared" ref="K15" si="21">K12-K13-K14</f>
+        <v>290</v>
+      </c>
+      <c r="L15" s="9">
+        <f t="shared" ref="L15" si="22">L12-L13-L14</f>
+        <v>390</v>
+      </c>
+      <c r="O15" s="9">
+        <f t="shared" ref="O15:P15" si="23">O12-O13-O14</f>
+        <v>459</v>
+      </c>
+      <c r="P15" s="9">
+        <f t="shared" si="23"/>
+        <v>524</v>
+      </c>
       <c r="T15" s="9">
-        <f t="shared" ref="T15:Y15" si="15">T12-T13-T14</f>
+        <f t="shared" ref="T15:Y15" si="24">T12-T13-T14</f>
         <v>1322</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>2283</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>1273</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>1221</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" si="15"/>
+        <f t="shared" si="24"/>
         <v>1597</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" si="15"/>
-        <v>1851.8302000000008</v>
+        <f t="shared" si="24"/>
+        <v>2494.070200000001</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" ref="Z15:AI15" si="16">Z12-Z13-Z14</f>
-        <v>1994.8541100000034</v>
+        <f t="shared" ref="Z15:AI15" si="25">Z12-Z13-Z14</f>
+        <v>2662.7837100000038</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" si="16"/>
-        <v>2123.4343973999985</v>
+        <f t="shared" si="25"/>
+        <v>2811.4018853999992</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" si="16"/>
-        <v>2233.8833985419997</v>
+        <f t="shared" si="25"/>
+        <v>2935.6102363020009</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" si="16"/>
-        <v>2339.8122136930233</v>
+        <f t="shared" si="25"/>
+        <v>3048.5563198306236</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="16"/>
-        <v>2448.8116514743042</v>
+        <f t="shared" si="25"/>
+        <v>3164.6431986732814</v>
       </c>
       <c r="AE15" s="9">
-        <f t="shared" si="16"/>
-        <v>2560.9628308473975</v>
+        <f t="shared" si="25"/>
+        <v>3283.9526935183644</v>
       </c>
       <c r="AF15" s="9">
-        <f t="shared" si="16"/>
-        <v>2676.3489957995157</v>
+        <f t="shared" si="25"/>
+        <v>3406.5687570971922</v>
       </c>
       <c r="AG15" s="9">
-        <f t="shared" si="16"/>
-        <v>2795.0555720380175</v>
+        <f t="shared" si="25"/>
+        <v>3532.5775309486712</v>
       </c>
       <c r="AH15" s="9">
-        <f t="shared" si="16"/>
-        <v>2917.1702252356181</v>
+        <f t="shared" si="25"/>
+        <v>3662.0674037353779</v>
       </c>
       <c r="AI15" s="9">
-        <f t="shared" si="16"/>
-        <v>3042.7829208699713</v>
+        <f t="shared" si="25"/>
+        <v>3795.129071154729</v>
       </c>
     </row>
     <row r="16" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="K16" s="6">
+        <v>5</v>
+      </c>
+      <c r="L16" s="6">
+        <v>23</v>
+      </c>
+      <c r="O16" s="6">
+        <v>73</v>
+      </c>
+      <c r="P16" s="6">
+        <v>66</v>
+      </c>
       <c r="T16" s="6">
         <v>234</v>
       </c>
@@ -1779,53 +1920,65 @@
       </c>
       <c r="Y16" s="6">
         <f>Y15*0.1</f>
-        <v>185.18302000000008</v>
+        <v>249.4070200000001</v>
       </c>
       <c r="Z16" s="6">
-        <f t="shared" ref="Z16:AI16" si="17">Z15*0.1</f>
-        <v>199.48541100000034</v>
+        <f t="shared" ref="Z16:AI16" si="26">Z15*0.1</f>
+        <v>266.27837100000039</v>
       </c>
       <c r="AA16" s="6">
-        <f t="shared" si="17"/>
-        <v>212.34343973999987</v>
+        <f t="shared" si="26"/>
+        <v>281.14018853999994</v>
       </c>
       <c r="AB16" s="6">
-        <f t="shared" si="17"/>
-        <v>223.38833985419998</v>
+        <f t="shared" si="26"/>
+        <v>293.56102363020011</v>
       </c>
       <c r="AC16" s="6">
-        <f t="shared" si="17"/>
-        <v>233.98122136930235</v>
+        <f t="shared" si="26"/>
+        <v>304.85563198306238</v>
       </c>
       <c r="AD16" s="6">
-        <f t="shared" si="17"/>
-        <v>244.88116514743044</v>
+        <f t="shared" si="26"/>
+        <v>316.46431986732819</v>
       </c>
       <c r="AE16" s="6">
-        <f t="shared" si="17"/>
-        <v>256.09628308473975</v>
+        <f t="shared" si="26"/>
+        <v>328.39526935183648</v>
       </c>
       <c r="AF16" s="6">
-        <f t="shared" si="17"/>
-        <v>267.63489957995159</v>
+        <f t="shared" si="26"/>
+        <v>340.65687570971926</v>
       </c>
       <c r="AG16" s="6">
-        <f t="shared" si="17"/>
-        <v>279.50555720380174</v>
+        <f t="shared" si="26"/>
+        <v>353.25775309486716</v>
       </c>
       <c r="AH16" s="6">
-        <f t="shared" si="17"/>
-        <v>291.71702252356181</v>
+        <f t="shared" si="26"/>
+        <v>366.2067403735378</v>
       </c>
       <c r="AI16" s="6">
-        <f t="shared" si="17"/>
-        <v>304.27829208699717</v>
+        <f t="shared" si="26"/>
+        <v>379.5129071154729</v>
       </c>
     </row>
     <row r="17" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B17" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="K17" s="6">
+        <v>2</v>
+      </c>
+      <c r="L17" s="6">
+        <v>1</v>
+      </c>
+      <c r="O17" s="6">
+        <v>0</v>
+      </c>
+      <c r="P17" s="6">
+        <v>0</v>
+      </c>
       <c r="T17" s="6">
         <f>2-33</f>
         <v>-31</v>
@@ -1881,577 +2034,609 @@
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
+      <c r="K18" s="9">
+        <f t="shared" ref="K18" si="27">K15-K16-K17</f>
+        <v>283</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" ref="L18" si="28">L15-L16-L17</f>
+        <v>366</v>
+      </c>
+      <c r="O18" s="9">
+        <f t="shared" ref="O18:P18" si="29">O15-O16-O17</f>
+        <v>386</v>
+      </c>
+      <c r="P18" s="9">
+        <f t="shared" si="29"/>
+        <v>458</v>
+      </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18:Y18" si="18">T15-T16-T17</f>
+        <f t="shared" ref="T18:Y18" si="30">T15-T16-T17</f>
         <v>1119</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1846</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1062</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1227</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="30"/>
         <v>1502</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" si="18"/>
-        <v>1666.6471800000006</v>
+        <f t="shared" si="30"/>
+        <v>2244.6631800000009</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18:AI18" si="19">Z15-Z16-Z17</f>
-        <v>1795.3686990000031</v>
+        <f t="shared" ref="Z18:AI18" si="31">Z15-Z16-Z17</f>
+        <v>2396.5053390000035</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" si="19"/>
-        <v>1911.0909576599986</v>
+        <f t="shared" si="31"/>
+        <v>2530.2616968599991</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" si="19"/>
-        <v>2010.4950586877997</v>
+        <f t="shared" si="31"/>
+        <v>2642.0492126718009</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" si="19"/>
-        <v>2105.8309923237211</v>
+        <f t="shared" si="31"/>
+        <v>2743.7006878475613</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" si="19"/>
-        <v>2203.930486326874</v>
+        <f t="shared" si="31"/>
+        <v>2848.178878805953</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" si="19"/>
-        <v>2304.8665477626578</v>
+        <f t="shared" si="31"/>
+        <v>2955.5574241665281</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" si="19"/>
-        <v>2408.714096219564</v>
+        <f t="shared" si="31"/>
+        <v>3065.9118813874729</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" si="19"/>
-        <v>2515.5500148342157</v>
+        <f t="shared" si="31"/>
+        <v>3179.3197778538042</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" si="19"/>
-        <v>2625.4532027120563</v>
+        <f t="shared" si="31"/>
+        <v>3295.8606633618401</v>
       </c>
       <c r="AI18" s="9">
-        <f t="shared" si="19"/>
-        <v>2738.5046287829741</v>
+        <f t="shared" si="31"/>
+        <v>3415.6161640392561</v>
       </c>
       <c r="AJ18" s="2">
         <f>AI18*(1+$AL$23)</f>
-        <v>2711.1195824951442</v>
+        <v>3381.4600023988637</v>
       </c>
       <c r="AK18" s="2">
-        <f t="shared" ref="AK18:CV18" si="20">AJ18*(1+$AL$23)</f>
-        <v>2684.0083866701925</v>
+        <f t="shared" ref="AK18:CV18" si="32">AJ18*(1+$AL$23)</f>
+        <v>3347.6454023748752</v>
       </c>
       <c r="AL18" s="2">
-        <f t="shared" si="20"/>
-        <v>2657.1683028034904</v>
+        <f t="shared" si="32"/>
+        <v>3314.1689483511263</v>
       </c>
       <c r="AM18" s="2">
-        <f t="shared" si="20"/>
-        <v>2630.5966197754556</v>
+        <f t="shared" si="32"/>
+        <v>3281.0272588676153</v>
       </c>
       <c r="AN18" s="2">
-        <f t="shared" si="20"/>
-        <v>2604.2906535777011</v>
+        <f t="shared" si="32"/>
+        <v>3248.2169862789392</v>
       </c>
       <c r="AO18" s="2">
-        <f t="shared" si="20"/>
-        <v>2578.247747041924</v>
+        <f t="shared" si="32"/>
+        <v>3215.7348164161499</v>
       </c>
       <c r="AP18" s="2">
-        <f t="shared" si="20"/>
-        <v>2552.4652695715049</v>
+        <f t="shared" si="32"/>
+        <v>3183.5774682519882</v>
       </c>
       <c r="AQ18" s="2">
-        <f t="shared" si="20"/>
-        <v>2526.9406168757901</v>
+        <f t="shared" si="32"/>
+        <v>3151.7416935694682</v>
       </c>
       <c r="AR18" s="2">
-        <f t="shared" si="20"/>
-        <v>2501.6712107070321</v>
+        <f t="shared" si="32"/>
+        <v>3120.2242766337736</v>
       </c>
       <c r="AS18" s="2">
-        <f t="shared" si="20"/>
-        <v>2476.6544985999617</v>
+        <f t="shared" si="32"/>
+        <v>3089.0220338674358</v>
       </c>
       <c r="AT18" s="2">
-        <f t="shared" si="20"/>
-        <v>2451.8879536139621</v>
+        <f t="shared" si="32"/>
+        <v>3058.1318135287615</v>
       </c>
       <c r="AU18" s="2">
-        <f t="shared" si="20"/>
-        <v>2427.3690740778225</v>
+        <f t="shared" si="32"/>
+        <v>3027.5504953934737</v>
       </c>
       <c r="AV18" s="2">
-        <f t="shared" si="20"/>
-        <v>2403.095383337044</v>
+        <f t="shared" si="32"/>
+        <v>2997.2749904395391</v>
       </c>
       <c r="AW18" s="2">
-        <f t="shared" si="20"/>
-        <v>2379.0644295036736</v>
+        <f t="shared" si="32"/>
+        <v>2967.3022405351435</v>
       </c>
       <c r="AX18" s="2">
-        <f t="shared" si="20"/>
-        <v>2355.273785208637</v>
+        <f t="shared" si="32"/>
+        <v>2937.6292181297922</v>
       </c>
       <c r="AY18" s="2">
-        <f t="shared" si="20"/>
-        <v>2331.7210473565506</v>
+        <f t="shared" si="32"/>
+        <v>2908.2529259484941</v>
       </c>
       <c r="AZ18" s="2">
-        <f t="shared" si="20"/>
-        <v>2308.4038368829852</v>
+        <f t="shared" si="32"/>
+        <v>2879.1703966890091</v>
       </c>
       <c r="BA18" s="2">
-        <f t="shared" si="20"/>
-        <v>2285.3197985141551</v>
+        <f t="shared" si="32"/>
+        <v>2850.378692722119</v>
       </c>
       <c r="BB18" s="2">
-        <f t="shared" si="20"/>
-        <v>2262.4666005290137</v>
+        <f t="shared" si="32"/>
+        <v>2821.8749057948976</v>
       </c>
       <c r="BC18" s="2">
-        <f t="shared" si="20"/>
-        <v>2239.8419345237235</v>
+        <f t="shared" si="32"/>
+        <v>2793.6561567369486</v>
       </c>
       <c r="BD18" s="2">
-        <f t="shared" si="20"/>
-        <v>2217.443515178486</v>
+        <f t="shared" si="32"/>
+        <v>2765.719595169579</v>
       </c>
       <c r="BE18" s="2">
-        <f t="shared" si="20"/>
-        <v>2195.269080026701</v>
+        <f t="shared" si="32"/>
+        <v>2738.062399217883</v>
       </c>
       <c r="BF18" s="2">
-        <f t="shared" si="20"/>
-        <v>2173.3163892264338</v>
+        <f t="shared" si="32"/>
+        <v>2710.6817752257043</v>
       </c>
       <c r="BG18" s="2">
-        <f t="shared" si="20"/>
-        <v>2151.5832253341696</v>
+        <f t="shared" si="32"/>
+        <v>2683.5749574734473</v>
       </c>
       <c r="BH18" s="2">
-        <f t="shared" si="20"/>
-        <v>2130.067393080828</v>
+        <f t="shared" si="32"/>
+        <v>2656.7392078987127</v>
       </c>
       <c r="BI18" s="2">
-        <f t="shared" si="20"/>
-        <v>2108.7667191500195</v>
+        <f t="shared" si="32"/>
+        <v>2630.1718158197255</v>
       </c>
       <c r="BJ18" s="2">
-        <f t="shared" si="20"/>
-        <v>2087.6790519585193</v>
+        <f t="shared" si="32"/>
+        <v>2603.8700976615282</v>
       </c>
       <c r="BK18" s="2">
-        <f t="shared" si="20"/>
-        <v>2066.8022614389342</v>
+        <f t="shared" si="32"/>
+        <v>2577.8313966849128</v>
       </c>
       <c r="BL18" s="2">
-        <f t="shared" si="20"/>
-        <v>2046.1342388245448</v>
+        <f t="shared" si="32"/>
+        <v>2552.0530827180637</v>
       </c>
       <c r="BM18" s="2">
-        <f t="shared" si="20"/>
-        <v>2025.6728964362994</v>
+        <f t="shared" si="32"/>
+        <v>2526.532551890883</v>
       </c>
       <c r="BN18" s="2">
-        <f t="shared" si="20"/>
-        <v>2005.4161674719364</v>
+        <f t="shared" si="32"/>
+        <v>2501.2672263719742</v>
       </c>
       <c r="BO18" s="2">
-        <f t="shared" si="20"/>
-        <v>1985.3620057972171</v>
+        <f t="shared" si="32"/>
+        <v>2476.2545541082545</v>
       </c>
       <c r="BP18" s="2">
-        <f t="shared" si="20"/>
-        <v>1965.5083857392449</v>
+        <f t="shared" si="32"/>
+        <v>2451.492008567172</v>
       </c>
       <c r="BQ18" s="2">
-        <f t="shared" si="20"/>
-        <v>1945.8533018818525</v>
+        <f t="shared" si="32"/>
+        <v>2426.9770884815002</v>
       </c>
       <c r="BR18" s="2">
-        <f t="shared" si="20"/>
-        <v>1926.394768863034</v>
+        <f t="shared" si="32"/>
+        <v>2402.7073175966852</v>
       </c>
       <c r="BS18" s="2">
-        <f t="shared" si="20"/>
-        <v>1907.1308211744035</v>
+        <f t="shared" si="32"/>
+        <v>2378.6802444207183</v>
       </c>
       <c r="BT18" s="2">
-        <f t="shared" si="20"/>
-        <v>1888.0595129626595</v>
+        <f t="shared" si="32"/>
+        <v>2354.893441976511</v>
       </c>
       <c r="BU18" s="2">
-        <f t="shared" si="20"/>
-        <v>1869.178917833033</v>
+        <f t="shared" si="32"/>
+        <v>2331.3445075567461</v>
       </c>
       <c r="BV18" s="2">
-        <f t="shared" si="20"/>
-        <v>1850.4871286547027</v>
+        <f t="shared" si="32"/>
+        <v>2308.0310624811787</v>
       </c>
       <c r="BW18" s="2">
-        <f t="shared" si="20"/>
-        <v>1831.9822573681556</v>
+        <f t="shared" si="32"/>
+        <v>2284.9507518563669</v>
       </c>
       <c r="BX18" s="2">
-        <f t="shared" si="20"/>
-        <v>1813.6624347944739</v>
+        <f t="shared" si="32"/>
+        <v>2262.1012443378031</v>
       </c>
       <c r="BY18" s="2">
-        <f t="shared" si="20"/>
-        <v>1795.5258104465292</v>
+        <f t="shared" si="32"/>
+        <v>2239.4802318944248</v>
       </c>
       <c r="BZ18" s="2">
-        <f t="shared" si="20"/>
-        <v>1777.570552342064</v>
+        <f t="shared" si="32"/>
+        <v>2217.0854295754807</v>
       </c>
       <c r="CA18" s="2">
-        <f t="shared" si="20"/>
-        <v>1759.7948468186435</v>
+        <f t="shared" si="32"/>
+        <v>2194.9145752797258</v>
       </c>
       <c r="CB18" s="2">
-        <f t="shared" si="20"/>
-        <v>1742.1968983504571</v>
+        <f t="shared" si="32"/>
+        <v>2172.9654295269283</v>
       </c>
       <c r="CC18" s="2">
-        <f t="shared" si="20"/>
-        <v>1724.7749293669526</v>
+        <f t="shared" si="32"/>
+        <v>2151.2357752316589</v>
       </c>
       <c r="CD18" s="2">
-        <f t="shared" si="20"/>
-        <v>1707.527180073283</v>
+        <f t="shared" si="32"/>
+        <v>2129.7234174793421</v>
       </c>
       <c r="CE18" s="2">
-        <f t="shared" si="20"/>
-        <v>1690.4519082725501</v>
+        <f t="shared" si="32"/>
+        <v>2108.4261833045484</v>
       </c>
       <c r="CF18" s="2">
-        <f t="shared" si="20"/>
-        <v>1673.5473891898246</v>
+        <f t="shared" si="32"/>
+        <v>2087.3419214715027</v>
       </c>
       <c r="CG18" s="2">
-        <f t="shared" si="20"/>
-        <v>1656.8119152979264</v>
+        <f t="shared" si="32"/>
+        <v>2066.4685022567878</v>
       </c>
       <c r="CH18" s="2">
-        <f t="shared" si="20"/>
-        <v>1640.2437961449471</v>
+        <f t="shared" si="32"/>
+        <v>2045.8038172342199</v>
       </c>
       <c r="CI18" s="2">
-        <f t="shared" si="20"/>
-        <v>1623.8413581834975</v>
+        <f t="shared" si="32"/>
+        <v>2025.3457790618777</v>
       </c>
       <c r="CJ18" s="2">
-        <f t="shared" si="20"/>
-        <v>1607.6029446016626</v>
+        <f t="shared" si="32"/>
+        <v>2005.0923212712589</v>
       </c>
       <c r="CK18" s="2">
-        <f t="shared" si="20"/>
-        <v>1591.5269151556458</v>
+        <f t="shared" si="32"/>
+        <v>1985.0413980585463</v>
       </c>
       <c r="CL18" s="2">
-        <f t="shared" si="20"/>
-        <v>1575.6116460040894</v>
+        <f t="shared" si="32"/>
+        <v>1965.1909840779608</v>
       </c>
       <c r="CM18" s="2">
-        <f t="shared" si="20"/>
-        <v>1559.8555295440485</v>
+        <f t="shared" si="32"/>
+        <v>1945.5390742371812</v>
       </c>
       <c r="CN18" s="2">
-        <f t="shared" si="20"/>
-        <v>1544.256974248608</v>
+        <f t="shared" si="32"/>
+        <v>1926.0836834948095</v>
       </c>
       <c r="CO18" s="2">
-        <f t="shared" si="20"/>
-        <v>1528.8144045061219</v>
+        <f t="shared" si="32"/>
+        <v>1906.8228466598614</v>
       </c>
       <c r="CP18" s="2">
-        <f t="shared" si="20"/>
-        <v>1513.5262604610607</v>
+        <f t="shared" si="32"/>
+        <v>1887.7546181932628</v>
       </c>
       <c r="CQ18" s="2">
-        <f t="shared" si="20"/>
-        <v>1498.39099785645</v>
+        <f t="shared" si="32"/>
+        <v>1868.87707201133</v>
       </c>
       <c r="CR18" s="2">
-        <f t="shared" si="20"/>
-        <v>1483.4070878778855</v>
+        <f t="shared" si="32"/>
+        <v>1850.1883012912167</v>
       </c>
       <c r="CS18" s="2">
-        <f t="shared" si="20"/>
-        <v>1468.5730169991066</v>
+        <f t="shared" si="32"/>
+        <v>1831.6864182783045</v>
       </c>
       <c r="CT18" s="2">
-        <f t="shared" si="20"/>
-        <v>1453.8872868291155</v>
+        <f t="shared" si="32"/>
+        <v>1813.3695540955214</v>
       </c>
       <c r="CU18" s="2">
-        <f t="shared" si="20"/>
-        <v>1439.3484139608242</v>
+        <f t="shared" si="32"/>
+        <v>1795.2358585545662</v>
       </c>
       <c r="CV18" s="2">
-        <f t="shared" si="20"/>
-        <v>1424.954929821216</v>
+        <f t="shared" si="32"/>
+        <v>1777.2834999690206</v>
       </c>
       <c r="CW18" s="2">
-        <f t="shared" ref="CW18:EO18" si="21">CV18*(1+$AL$23)</f>
-        <v>1410.7053805230039</v>
+        <f t="shared" ref="CW18:EO18" si="33">CV18*(1+$AL$23)</f>
+        <v>1759.5106649693303</v>
       </c>
       <c r="CX18" s="2">
-        <f t="shared" si="21"/>
-        <v>1396.5983267177739</v>
+        <f t="shared" si="33"/>
+        <v>1741.9155583196371</v>
       </c>
       <c r="CY18" s="2">
-        <f t="shared" si="21"/>
-        <v>1382.6323434505962</v>
+        <f t="shared" si="33"/>
+        <v>1724.4964027364406</v>
       </c>
       <c r="CZ18" s="2">
-        <f t="shared" si="21"/>
-        <v>1368.8060200160903</v>
+        <f t="shared" si="33"/>
+        <v>1707.2514387090762</v>
       </c>
       <c r="DA18" s="2">
-        <f t="shared" si="21"/>
-        <v>1355.1179598159295</v>
+        <f t="shared" si="33"/>
+        <v>1690.1789243219855</v>
       </c>
       <c r="DB18" s="2">
-        <f t="shared" si="21"/>
-        <v>1341.5667802177702</v>
+        <f t="shared" si="33"/>
+        <v>1673.2771350787657</v>
       </c>
       <c r="DC18" s="2">
-        <f t="shared" si="21"/>
-        <v>1328.1511124155925</v>
+        <f t="shared" si="33"/>
+        <v>1656.544363727978</v>
       </c>
       <c r="DD18" s="2">
-        <f t="shared" si="21"/>
-        <v>1314.8696012914365</v>
+        <f t="shared" si="33"/>
+        <v>1639.9789200906982</v>
       </c>
       <c r="DE18" s="2">
-        <f t="shared" si="21"/>
-        <v>1301.7209052785222</v>
+        <f t="shared" si="33"/>
+        <v>1623.5791308897913</v>
       </c>
       <c r="DF18" s="2">
-        <f t="shared" si="21"/>
-        <v>1288.7036962257368</v>
+        <f t="shared" si="33"/>
+        <v>1607.3433395808934</v>
       </c>
       <c r="DG18" s="2">
-        <f t="shared" si="21"/>
-        <v>1275.8166592634796</v>
+        <f t="shared" si="33"/>
+        <v>1591.2699061850844</v>
       </c>
       <c r="DH18" s="2">
-        <f t="shared" si="21"/>
-        <v>1263.0584926708448</v>
+        <f t="shared" si="33"/>
+        <v>1575.3572071232336</v>
       </c>
       <c r="DI18" s="2">
-        <f t="shared" si="21"/>
-        <v>1250.4279077441363</v>
+        <f t="shared" si="33"/>
+        <v>1559.6036350520012</v>
       </c>
       <c r="DJ18" s="2">
-        <f t="shared" si="21"/>
-        <v>1237.9236286666949</v>
+        <f t="shared" si="33"/>
+        <v>1544.0075987014811</v>
       </c>
       <c r="DK18" s="2">
-        <f t="shared" si="21"/>
-        <v>1225.5443923800278</v>
+        <f t="shared" si="33"/>
+        <v>1528.5675227144663</v>
       </c>
       <c r="DL18" s="2">
-        <f t="shared" si="21"/>
-        <v>1213.2889484562274</v>
+        <f t="shared" si="33"/>
+        <v>1513.2818474873218</v>
       </c>
       <c r="DM18" s="2">
-        <f t="shared" si="21"/>
-        <v>1201.1560589716651</v>
+        <f t="shared" si="33"/>
+        <v>1498.1490290124486</v>
       </c>
       <c r="DN18" s="2">
-        <f t="shared" si="21"/>
-        <v>1189.1444983819483</v>
+        <f t="shared" si="33"/>
+        <v>1483.167538722324</v>
       </c>
       <c r="DO18" s="2">
-        <f t="shared" si="21"/>
-        <v>1177.2530533981289</v>
+        <f t="shared" si="33"/>
+        <v>1468.3358633351008</v>
       </c>
       <c r="DP18" s="2">
-        <f t="shared" si="21"/>
-        <v>1165.4805228641476</v>
+        <f t="shared" si="33"/>
+        <v>1453.6525047017499</v>
       </c>
       <c r="DQ18" s="2">
-        <f t="shared" si="21"/>
-        <v>1153.8257176355062</v>
+        <f t="shared" si="33"/>
+        <v>1439.1159796547324</v>
       </c>
       <c r="DR18" s="2">
-        <f t="shared" si="21"/>
-        <v>1142.2874604591511</v>
+        <f t="shared" si="33"/>
+        <v>1424.7248198581851</v>
       </c>
       <c r="DS18" s="2">
-        <f t="shared" si="21"/>
-        <v>1130.8645858545597</v>
+        <f t="shared" si="33"/>
+        <v>1410.4775716596032</v>
       </c>
       <c r="DT18" s="2">
-        <f t="shared" si="21"/>
-        <v>1119.5559399960141</v>
+        <f t="shared" si="33"/>
+        <v>1396.3727959430071</v>
       </c>
       <c r="DU18" s="2">
-        <f t="shared" si="21"/>
-        <v>1108.360380596054</v>
+        <f t="shared" si="33"/>
+        <v>1382.409067983577</v>
       </c>
       <c r="DV18" s="2">
-        <f t="shared" si="21"/>
-        <v>1097.2767767900934</v>
+        <f t="shared" si="33"/>
+        <v>1368.5849773037412</v>
       </c>
       <c r="DW18" s="2">
-        <f t="shared" si="21"/>
-        <v>1086.3040090221925</v>
+        <f t="shared" si="33"/>
+        <v>1354.8991275307037</v>
       </c>
       <c r="DX18" s="2">
-        <f t="shared" si="21"/>
-        <v>1075.4409689319707</v>
+        <f t="shared" si="33"/>
+        <v>1341.3501362553966</v>
       </c>
       <c r="DY18" s="2">
-        <f t="shared" si="21"/>
-        <v>1064.6865592426509</v>
+        <f t="shared" si="33"/>
+        <v>1327.9366348928427</v>
       </c>
       <c r="DZ18" s="2">
-        <f t="shared" si="21"/>
-        <v>1054.0396936502243</v>
+        <f t="shared" si="33"/>
+        <v>1314.6572685439141</v>
       </c>
       <c r="EA18" s="2">
-        <f t="shared" si="21"/>
-        <v>1043.4992967137221</v>
+        <f t="shared" si="33"/>
+        <v>1301.5106958584749</v>
       </c>
       <c r="EB18" s="2">
-        <f t="shared" si="21"/>
-        <v>1033.0643037465848</v>
+        <f t="shared" si="33"/>
+        <v>1288.4955888998902</v>
       </c>
       <c r="EC18" s="2">
-        <f t="shared" si="21"/>
-        <v>1022.7336607091189</v>
+        <f t="shared" si="33"/>
+        <v>1275.6106330108912</v>
       </c>
       <c r="ED18" s="2">
-        <f t="shared" si="21"/>
-        <v>1012.5063241020277</v>
+        <f t="shared" si="33"/>
+        <v>1262.8545266807823</v>
       </c>
       <c r="EE18" s="2">
-        <f t="shared" si="21"/>
-        <v>1002.3812608610075</v>
+        <f t="shared" si="33"/>
+        <v>1250.2259814139745</v>
       </c>
       <c r="EF18" s="2">
-        <f t="shared" si="21"/>
-        <v>992.35744825239738</v>
+        <f t="shared" si="33"/>
+        <v>1237.7237215998348</v>
       </c>
       <c r="EG18" s="2">
-        <f t="shared" si="21"/>
-        <v>982.43387376987334</v>
+        <f t="shared" si="33"/>
+        <v>1225.3464843838365</v>
       </c>
       <c r="EH18" s="2">
-        <f t="shared" si="21"/>
-        <v>972.60953503217456</v>
+        <f t="shared" si="33"/>
+        <v>1213.0930195399981</v>
       </c>
       <c r="EI18" s="2">
-        <f t="shared" si="21"/>
-        <v>962.88343968185279</v>
+        <f t="shared" si="33"/>
+        <v>1200.9620893445981</v>
       </c>
       <c r="EJ18" s="2">
-        <f t="shared" si="21"/>
-        <v>953.25460528503424</v>
+        <f t="shared" si="33"/>
+        <v>1188.9524684511521</v>
       </c>
       <c r="EK18" s="2">
-        <f t="shared" si="21"/>
-        <v>943.72205923218394</v>
+        <f t="shared" si="33"/>
+        <v>1177.0629437666405</v>
       </c>
       <c r="EL18" s="2">
-        <f t="shared" si="21"/>
-        <v>934.28483863986207</v>
+        <f t="shared" si="33"/>
+        <v>1165.292314328974</v>
       </c>
       <c r="EM18" s="2">
-        <f t="shared" si="21"/>
-        <v>924.94199025346347</v>
+        <f t="shared" si="33"/>
+        <v>1153.6393911856842</v>
       </c>
       <c r="EN18" s="2">
-        <f t="shared" si="21"/>
-        <v>915.6925703509288</v>
+        <f t="shared" si="33"/>
+        <v>1142.1029972738274</v>
       </c>
       <c r="EO18" s="2">
-        <f t="shared" si="21"/>
-        <v>906.53564464741953</v>
+        <f t="shared" si="33"/>
+        <v>1130.6819673010891</v>
       </c>
     </row>
     <row r="19" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B19" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="K19" s="6">
+        <f t="shared" ref="K19" si="34">188.3</f>
+        <v>188.3</v>
+      </c>
+      <c r="L19" s="6">
+        <f t="shared" ref="L19" si="35">188.3</f>
+        <v>188.3</v>
+      </c>
+      <c r="O19" s="6">
+        <f t="shared" ref="O19:P19" si="36">188.3</f>
+        <v>188.3</v>
+      </c>
+      <c r="P19" s="6">
+        <f t="shared" si="36"/>
+        <v>188.3</v>
+      </c>
       <c r="T19" s="6">
-        <f t="shared" ref="T19:Y19" si="22">188.3</f>
+        <f t="shared" ref="T19:Y19" si="37">188.3</f>
         <v>188.3</v>
       </c>
       <c r="U19" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>188.3</v>
       </c>
       <c r="V19" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>188.3</v>
       </c>
       <c r="W19" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>188.3</v>
       </c>
       <c r="X19" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>188.3</v>
       </c>
       <c r="Y19" s="6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="37"/>
         <v>188.3</v>
       </c>
       <c r="Z19" s="6">
-        <f t="shared" ref="Z19:AI19" si="23">188.3</f>
+        <f t="shared" ref="Z19:AI19" si="38">188.3</f>
         <v>188.3</v>
       </c>
       <c r="AA19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AB19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AC19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AD19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AE19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AF19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AG19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AH19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
       <c r="AI19" s="6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="38"/>
         <v>188.3</v>
       </c>
     </row>
@@ -2459,86 +2644,112 @@
       <c r="B20" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="K20" s="8">
+        <f t="shared" ref="K20" si="39">K18/K19</f>
+        <v>1.5029208709506106</v>
+      </c>
+      <c r="L20" s="8">
+        <f t="shared" ref="L20" si="40">L18/L19</f>
+        <v>1.9437068507700477</v>
+      </c>
+      <c r="O20" s="8">
+        <f t="shared" ref="O20:P20" si="41">O18/O19</f>
+        <v>2.0499203398831649</v>
+      </c>
+      <c r="P20" s="8">
+        <f t="shared" si="41"/>
+        <v>2.4322889006903874</v>
+      </c>
       <c r="T20" s="8">
-        <f t="shared" ref="T20:Y20" si="24">T18/T19</f>
+        <f t="shared" ref="T20:Y20" si="42">T18/T19</f>
         <v>5.9426447158789166</v>
       </c>
       <c r="U20" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="42"/>
         <v>9.8035050451407315</v>
       </c>
       <c r="V20" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="42"/>
         <v>5.6399362719065316</v>
       </c>
       <c r="W20" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="42"/>
         <v>6.5161975570897503</v>
       </c>
       <c r="X20" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="42"/>
         <v>7.9766330323951138</v>
       </c>
       <c r="Y20" s="8">
-        <f t="shared" si="24"/>
-        <v>8.8510206054168901</v>
+        <f t="shared" si="42"/>
+        <v>11.920675411577275</v>
       </c>
       <c r="Z20" s="8">
-        <f t="shared" ref="Z20:AI20" si="25">Z18/Z19</f>
-        <v>9.534618688263425</v>
+        <f t="shared" ref="Z20:AI20" si="43">Z18/Z19</f>
+        <v>12.727059686670225</v>
       </c>
       <c r="AA20" s="8">
-        <f t="shared" si="25"/>
-        <v>10.149181931279864</v>
+        <f t="shared" si="43"/>
+        <v>13.437396159638869</v>
       </c>
       <c r="AB20" s="8">
-        <f t="shared" si="25"/>
-        <v>10.677084751395643</v>
+        <f t="shared" si="43"/>
+        <v>14.031063264321832</v>
       </c>
       <c r="AC20" s="8">
-        <f t="shared" si="25"/>
-        <v>11.183382858862034</v>
+        <f t="shared" si="43"/>
+        <v>14.570901156917477</v>
       </c>
       <c r="AD20" s="8">
-        <f t="shared" si="25"/>
-        <v>11.704357335777344</v>
+        <f t="shared" si="43"/>
+        <v>15.125750816813344</v>
       </c>
       <c r="AE20" s="8">
-        <f t="shared" si="25"/>
-        <v>12.240395898898873</v>
+        <f t="shared" si="43"/>
+        <v>15.696003314745235</v>
       </c>
       <c r="AF20" s="8">
-        <f t="shared" si="25"/>
-        <v>12.791896421771449</v>
+        <f t="shared" si="43"/>
+        <v>16.282059911776276</v>
       </c>
       <c r="AG20" s="8">
-        <f t="shared" si="25"/>
-        <v>13.359267205704809</v>
+        <f t="shared" si="43"/>
+        <v>16.884332330609688</v>
       </c>
       <c r="AH20" s="8">
-        <f t="shared" si="25"/>
-        <v>13.942927258162804</v>
+        <f t="shared" si="43"/>
+        <v>17.503243034316728</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="25"/>
-        <v>14.543306578773096</v>
+        <f t="shared" si="43"/>
+        <v>18.139225512688562</v>
       </c>
     </row>
     <row r="22" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="O22" s="10" t="e">
+        <f t="shared" ref="O22:P23" si="44">O3/K3-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P22" s="10" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T22" s="10"/>
       <c r="U22" s="10">
-        <f t="shared" ref="U22:W24" si="26">U3/T3-1</f>
+        <f t="shared" ref="U22:W24" si="45">U3/T3-1</f>
         <v>-3.1293719166482603E-2</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>-8.0495591365156605E-2</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>0.13201620236422262</v>
       </c>
       <c r="X22" s="10">
@@ -2546,47 +2757,47 @@
         <v>0.10515554257338988</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" ref="Y22:AI24" si="27">Y3/X3-1</f>
+        <f t="shared" ref="Y22:AI24" si="46">Y3/X3-1</f>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI22" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.0000000000000018E-2</v>
       </c>
     </row>
@@ -2594,65 +2805,75 @@
       <c r="B23" s="1" t="s">
         <v>45</v>
       </c>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="O23" s="10" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P23" s="10" t="e">
+        <f t="shared" si="44"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T23" s="10"/>
       <c r="U23" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>9.7550401040538137E-3</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>6.5908115070845819E-2</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>0.15307150050352458</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" ref="X23:X24" si="28">X4/W4-1</f>
+        <f t="shared" ref="X23:X24" si="47">X4/W4-1</f>
         <v>8.1397379912663714E-2</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AE23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AG23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AH23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AI23" s="10">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AK23" s="1" t="s">
@@ -2666,65 +2887,75 @@
       <c r="B24" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="O24" s="11">
+        <f>O5/K5-1</f>
+        <v>-1.5160237958165457E-2</v>
+      </c>
+      <c r="P24" s="11">
+        <f>P5/L5-1</f>
+        <v>2.3966786186072842E-2</v>
+      </c>
       <c r="T24" s="11"/>
       <c r="U24" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>-2.0886006375728239E-2</v>
       </c>
       <c r="V24" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>-4.2213988997417795E-2</v>
       </c>
       <c r="W24" s="11">
-        <f t="shared" si="26"/>
+        <f t="shared" si="45"/>
         <v>0.13814324229281438</v>
       </c>
       <c r="X24" s="11">
-        <f t="shared" si="28"/>
+        <f t="shared" si="47"/>
         <v>9.815129512333276E-2</v>
       </c>
       <c r="Y24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>7.4193669402110141E-2</v>
       </c>
       <c r="Z24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>5.0000000000000266E-2</v>
       </c>
       <c r="AA24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AB24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AC24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2864804834117569E-2</v>
       </c>
       <c r="AD24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2884788845207726E-2</v>
       </c>
       <c r="AE24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2904855505690547E-2</v>
       </c>
       <c r="AF24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2925004368448132E-2</v>
       </c>
       <c r="AG24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2945234974837581E-2</v>
       </c>
       <c r="AH24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2965546854673224E-2</v>
       </c>
       <c r="AI24" s="11">
-        <f t="shared" si="27"/>
+        <f t="shared" si="46"/>
         <v>2.2985939526218857E-2</v>
       </c>
       <c r="AK24" s="1" t="s">
@@ -2738,20 +2969,36 @@
       <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="K25" s="10" t="e">
+        <f t="shared" ref="K25" si="48">(K3-K6)/K3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L25" s="10" t="e">
+        <f t="shared" ref="L25:L26" si="49">(L3-L6)/L3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="10" t="e">
+        <f t="shared" ref="O25:P25" si="50">(O3-O6)/O3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P25" s="10" t="e">
+        <f t="shared" si="50"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T25" s="10">
-        <f t="shared" ref="T25:W25" si="29">(T3-T6)/T3</f>
+        <f t="shared" ref="T25:W25" si="51">(T3-T6)/T3</f>
         <v>0.3031440983727266</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="51"/>
         <v>0.31536941319550016</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="51"/>
         <v>0.3093328924526742</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" si="29"/>
+        <f t="shared" si="51"/>
         <v>0.29085730977070251</v>
       </c>
       <c r="X25" s="10">
@@ -2759,47 +3006,47 @@
         <v>0.27190432139553322</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" ref="Y25:AI25" si="30">(Y3-Y6)/Y3</f>
+        <f t="shared" ref="Y25:AI25" si="52">(Y3-Y6)/Y3</f>
         <v>0.27000000000000007</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27000000000000007</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27000000000000007</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.26999999999999996</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="52"/>
         <v>0.27</v>
       </c>
       <c r="AK25" s="1" t="s">
@@ -2807,27 +3054,43 @@
       </c>
       <c r="AL25" s="6">
         <f>NPV(AL24,Y18:EO18)</f>
-        <v>28113.120561901978</v>
+        <v>35821.445969259075</v>
       </c>
     </row>
     <row r="26" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B26" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="K26" s="10" t="e">
+        <f t="shared" ref="K26" si="53">(K4-K7)/K4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L26" s="10" t="e">
+        <f t="shared" si="49"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="10" t="e">
+        <f t="shared" ref="O26:P26" si="54">(O4-O7)/O4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P26" s="10" t="e">
+        <f t="shared" si="54"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="T26" s="10">
-        <f t="shared" ref="T26:W26" si="31">(T4-T7)/T4</f>
+        <f t="shared" ref="T26:W26" si="55">(T4-T7)/T4</f>
         <v>0.25818339475395619</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="55"/>
         <v>0.2634177758694719</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="55"/>
         <v>0.23867069486404835</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="55"/>
         <v>0.19737991266375546</v>
       </c>
       <c r="X26" s="10">
@@ -2835,47 +3098,47 @@
         <v>0.22758843482474561</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" ref="Y26:AI26" si="32">(Y4-Y7)/Y4</f>
+        <f t="shared" ref="Y26:AI26" si="56">(Y4-Y7)/Y4</f>
         <v>0.22999999999999993</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.23</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.23000000000000004</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.22999999999999995</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.22999999999999995</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.23</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.22999999999999995</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="56"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="AK26" s="1" t="s">
@@ -2883,27 +3146,43 @@
       </c>
       <c r="AL26" s="6">
         <f>Main!D8</f>
-        <v>-11621</v>
+        <v>-11620</v>
       </c>
     </row>
     <row r="27" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>49</v>
       </c>
+      <c r="K27" s="10">
+        <f t="shared" ref="K27" si="57">K9/K5</f>
+        <v>0.2586835540203416</v>
+      </c>
+      <c r="L27" s="10">
+        <f t="shared" ref="L27" si="58">L9/L5</f>
+        <v>0.25665219852802418</v>
+      </c>
+      <c r="O27" s="10">
+        <f t="shared" ref="O27:P27" si="59">O9/O5</f>
+        <v>0.26305533904910366</v>
+      </c>
+      <c r="P27" s="10">
+        <f t="shared" si="59"/>
+        <v>0.24603759675635828</v>
+      </c>
       <c r="T27" s="10">
-        <f t="shared" ref="T27:W27" si="33">T9/T5</f>
+        <f t="shared" ref="T27:W27" si="60">T9/T5</f>
         <v>0.29174453116412002</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="60"/>
         <v>0.30178511283260356</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="60"/>
         <v>0.28877036689719843</v>
       </c>
       <c r="W27" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="60"/>
         <v>0.26329883104176321</v>
       </c>
       <c r="X27" s="10">
@@ -2911,47 +3190,47 @@
         <v>0.25903868698710436</v>
       </c>
       <c r="Y27" s="10">
-        <f t="shared" ref="Y27:AI27" si="34">Y9/Y5</f>
+        <f t="shared" ref="Y27:AI27" si="61">Y9/Y5</f>
         <v>0.25854078066352998</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25854078066353003</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25854078066352987</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25854078066352992</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25846084461916918</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25838057797723846</v>
       </c>
       <c r="AE27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25829998252620701</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25821906010065004</v>
       </c>
       <c r="AG27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25813781258130702</v>
       </c>
       <c r="AH27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25805624189512477</v>
       </c>
       <c r="AI27" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="61"/>
         <v>0.25797435001529051</v>
       </c>
       <c r="AK27" s="1" t="s">
@@ -2959,24 +3238,37 @@
       </c>
       <c r="AL27" s="6">
         <f>AL25+AL26</f>
-        <v>16492.120561901978</v>
+        <v>24201.445969259075</v>
       </c>
     </row>
     <row r="28" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="K28" s="10" t="e">
+        <f>K10/G10-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L28" s="10"/>
+      <c r="O28" s="10">
+        <f>O10/K10-1</f>
+        <v>-0.14948453608247425</v>
+      </c>
+      <c r="P28" s="10">
+        <f>P10/L10-1</f>
+        <v>-0.13574660633484159</v>
+      </c>
       <c r="T28" s="10"/>
       <c r="U28" s="10">
-        <f t="shared" ref="U28:W28" si="35">U10/T10-1</f>
+        <f t="shared" ref="U28:W28" si="62">U10/T10-1</f>
         <v>-1.0558069381598756E-2</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="62"/>
         <v>-8.5975609756097526E-2</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="62"/>
         <v>0.10507004669779851</v>
       </c>
       <c r="X28" s="10">
@@ -2984,47 +3276,47 @@
         <v>7.6969514035617248E-2</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" ref="Y28:AI28" si="36">Y10/X10-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="Y28:AI28" si="63">Y10/X10-1</f>
+        <v>-0.13</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="63"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK28" s="1" t="s">
@@ -3032,27 +3324,43 @@
       </c>
       <c r="AL28" s="5">
         <f>AL27/AI19</f>
-        <v>87.584283387689737</v>
+        <v>128.52600089887983</v>
       </c>
     </row>
     <row r="29" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B29" s="1" t="s">
         <v>51</v>
       </c>
+      <c r="K29" s="10">
+        <f t="shared" ref="K29" si="64">K12/K5</f>
+        <v>7.2538860103626937E-2</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" ref="L29" si="65">L12/L5</f>
+        <v>8.982826948480846E-2</v>
+      </c>
+      <c r="O29" s="10">
+        <f t="shared" ref="O29:P29" si="66">O12/O5</f>
+        <v>0.10229929851909587</v>
+      </c>
+      <c r="P29" s="10">
+        <f t="shared" si="66"/>
+        <v>0.10523405823811278</v>
+      </c>
       <c r="T29" s="10">
-        <f t="shared" ref="T29:W29" si="37">T12/T5</f>
+        <f t="shared" ref="T29:W29" si="67">T12/T5</f>
         <v>6.4581730240738711E-2</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="67"/>
         <v>0.11839003031323678</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="67"/>
         <v>6.6053217676708478E-2</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="67"/>
         <v>7.3433235491013951E-2</v>
       </c>
       <c r="X29" s="10">
@@ -3060,75 +3368,91 @@
         <v>8.9941383352872217E-2</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" ref="Y29:AI29" si="38">Y12/Y5</f>
-        <v>9.4993805435675663E-2</v>
+        <f t="shared" ref="Y29:AI29" si="68">Y12/Y5</f>
+        <v>0.1230304297604507</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="38"/>
-        <v>9.6551395675941024E-2</v>
+        <f t="shared" si="68"/>
+        <v>0.12432100453095631</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="38"/>
-        <v>9.8108985916206121E-2</v>
+        <f t="shared" si="68"/>
+        <v>0.12561157930146163</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="38"/>
-        <v>9.966657615647144E-2</v>
+        <f t="shared" si="68"/>
+        <v>0.1269021540719672</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="38"/>
-        <v>0.1015848373562621</v>
+        <f t="shared" si="68"/>
+        <v>0.12847786717276047</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="38"/>
-        <v>0.10348066249954969</v>
+        <f t="shared" si="68"/>
+        <v>0.13003493372429636</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="38"/>
-        <v>0.10535426739894579</v>
+        <f t="shared" si="68"/>
+        <v>0.13157353284933346</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" si="38"/>
-        <v>0.10720586595754034</v>
+        <f t="shared" si="68"/>
+        <v>0.13309384209635919</v>
       </c>
       <c r="AG29" s="10">
-        <f t="shared" si="38"/>
-        <v>0.10903567018920471</v>
+        <f t="shared" si="68"/>
+        <v>0.13459603745642229</v>
       </c>
       <c r="AH29" s="10">
-        <f t="shared" si="38"/>
-        <v>0.11084389023865468</v>
+        <f t="shared" si="68"/>
+        <v>0.13608029337976388</v>
       </c>
       <c r="AI29" s="10">
-        <f t="shared" si="38"/>
-        <v>0.11263073440128135</v>
+        <f t="shared" si="68"/>
+        <v>0.13754678279225438</v>
       </c>
       <c r="AK29" s="1" t="s">
         <v>59</v>
       </c>
       <c r="AL29" s="5">
         <f>Main!D3</f>
-        <v>212.27</v>
+        <v>277.22000000000003</v>
       </c>
     </row>
     <row r="30" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="K30" s="10">
+        <f t="shared" ref="K30" si="69">K16/K15</f>
+        <v>1.7241379310344827E-2</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" ref="L30" si="70">L16/L15</f>
+        <v>5.8974358974358973E-2</v>
+      </c>
+      <c r="O30" s="10">
+        <f t="shared" ref="O30:P30" si="71">O16/O15</f>
+        <v>0.15904139433551198</v>
+      </c>
+      <c r="P30" s="10">
+        <f t="shared" si="71"/>
+        <v>0.12595419847328243</v>
+      </c>
       <c r="T30" s="10">
-        <f t="shared" ref="T30:W30" si="39">T16/T15</f>
+        <f t="shared" ref="T30:W30" si="72">T16/T15</f>
         <v>0.17700453857791226</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="72"/>
         <v>0.19272886552781429</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="72"/>
         <v>0.16653574234092694</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="72"/>
         <v>1.8837018837018837E-2</v>
       </c>
       <c r="X30" s="10">
@@ -3136,47 +3460,47 @@
         <v>5.3224796493425174E-2</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" ref="Y30:AI30" si="40">Y16/Y15</f>
+        <f t="shared" ref="Y30:AI30" si="73">Y16/Y15</f>
         <v>0.1</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="73"/>
+        <v>0.10000000000000002</v>
+      </c>
+      <c r="AE30" s="10">
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
-      <c r="AE30" s="10">
-        <f t="shared" si="40"/>
+      <c r="AF30" s="10">
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
-      <c r="AF30" s="10">
-        <f t="shared" si="40"/>
+      <c r="AG30" s="10">
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
-      <c r="AG30" s="10">
-        <f t="shared" si="40"/>
-        <v>9.9999999999999992E-2</v>
-      </c>
       <c r="AH30" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="73"/>
         <v>0.1</v>
       </c>
       <c r="AK30" s="2" t="s">
@@ -3184,27 +3508,43 @@
       </c>
       <c r="AL30" s="11">
         <f>AL28/AL29-1</f>
-        <v>-0.58739207901404</v>
+        <v>-0.5363754386448315</v>
       </c>
     </row>
     <row r="31" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B31" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="K31" s="10">
+        <f t="shared" ref="K31" si="74">K18/K5</f>
+        <v>5.4308194204567263E-2</v>
+      </c>
+      <c r="L31" s="10">
+        <f t="shared" ref="L31" si="75">L18/L5</f>
+        <v>6.9069635780335911E-2</v>
+      </c>
+      <c r="O31" s="10">
+        <f t="shared" ref="O31:P31" si="76">O18/O5</f>
+        <v>7.5214341387373346E-2</v>
+      </c>
+      <c r="P31" s="10">
+        <f t="shared" si="76"/>
+        <v>8.4408403980833033E-2</v>
+      </c>
       <c r="T31" s="10">
-        <f t="shared" ref="T31:W31" si="41">T18/T5</f>
+        <f t="shared" ref="T31:W31" si="77">T18/T5</f>
         <v>6.1503792459052437E-2</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="77"/>
         <v>0.10362636128887392</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="77"/>
         <v>6.2243582229515884E-2</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="77"/>
         <v>6.3185539935115095E-2</v>
       </c>
       <c r="X31" s="10">
@@ -3212,48 +3552,48 @@
         <v>7.0433763188745599E-2</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" ref="Y31:AI31" si="42">Y18/Y5</f>
-        <v>7.2756540962266011E-2</v>
+        <f t="shared" ref="Y31:AI31" si="78">Y18/Y5</f>
+        <v>9.7989502854563537E-2</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" si="42"/>
-        <v>7.4643624899641686E-2</v>
+        <f t="shared" si="78"/>
+        <v>9.963627286915544E-2</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" si="42"/>
-        <v>7.6398897400746749E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.10115123144747673</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="42"/>
-        <v>7.8031780848516391E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.1025438009724626</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" si="42"/>
-        <v>7.9904968767490842E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.10410869560233937</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" si="42"/>
-        <v>8.1756340752811241E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.10565518485508324</v>
       </c>
       <c r="AE31" s="10">
-        <f t="shared" si="42"/>
-        <v>8.3586106754321599E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.10718344565967051</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" si="42"/>
-        <v>8.539447485967E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.10869365338460696</v>
       </c>
       <c r="AG31" s="10">
-        <f t="shared" si="42"/>
-        <v>8.7181651314068298E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.11018598185456413</v>
       </c>
       <c r="AH31" s="10">
-        <f t="shared" si="42"/>
-        <v>8.8947840539818981E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.11166060336681724</v>
       </c>
       <c r="AI31" s="10">
-        <f t="shared" si="42"/>
-        <v>9.0693245155617053E-2</v>
+        <f t="shared" si="78"/>
+        <v>0.11311768870749278</v>
       </c>
       <c r="AK31" s="1" t="s">
         <v>61</v>

--- a/Financial Analysis/LHX.xlsx
+++ b/Financial Analysis/LHX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F6F2F1-31AD-4D24-9DBD-58F98712BDE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425E71FB-8AE1-411B-B1F7-C3BCB006D305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C2D3018F-E467-4E1E-BD9F-9383343E0F25}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="66">
   <si>
     <t>LHX</t>
   </si>
@@ -215,16 +215,26 @@
   </si>
   <si>
     <t>Heavily overvalued</t>
+  </si>
+  <si>
+    <t>L+S/E</t>
+  </si>
+  <si>
+    <t>EV/B</t>
+  </si>
+  <si>
+    <t>B/EV</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,6 +267,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -303,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -322,6 +341,8 @@
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -718,14 +739,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>277.22000000000003</v>
+        <v>297.39</v>
       </c>
       <c r="E3" s="4">
-        <v>45898</v>
+        <v>45934</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45898</v>
+        <v>45934</v>
       </c>
       <c r="G3" s="4">
         <v>45953</v>
@@ -748,7 +769,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>51867.862000000001</v>
+        <v>55641.668999999994</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -790,7 +811,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>63487.862000000001</v>
+        <v>67261.668999999994</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C127D1A-B1AA-4685-BD0F-764C53F340E2}">
-  <dimension ref="B2:EO31"/>
+  <dimension ref="B2:EO37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -3416,7 +3437,7 @@
       </c>
       <c r="AL29" s="5">
         <f>Main!D3</f>
-        <v>277.22000000000003</v>
+        <v>297.39</v>
       </c>
     </row>
     <row r="30" spans="2:145" x14ac:dyDescent="0.3">
@@ -3508,7 +3529,7 @@
       </c>
       <c r="AL30" s="11">
         <f>AL28/AL29-1</f>
-        <v>-0.5363754386448315</v>
+        <v>-0.56782003127583369</v>
       </c>
     </row>
     <row r="31" spans="2:145" x14ac:dyDescent="0.3">
@@ -3600,6 +3621,32 @@
       </c>
       <c r="AL31" s="7" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="P34" s="12">
+        <v>41240</v>
+      </c>
+    </row>
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P36" s="13">
+        <f>Main!D9/Model!P34</f>
+        <v>1.6309813045586807</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="P37" s="10">
+        <f>P34/Main!D9-1</f>
+        <v>-0.38687218718881322</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/LHX.xlsx
+++ b/Financial Analysis/LHX.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8AB9EE1-6599-4CBA-9499-AF49A8C8956A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DA4A1D0-1DCC-4892-A1F1-3D4AD4FEB762}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{C2D3018F-E467-4E1E-BD9F-9383343E0F25}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="76">
   <si>
     <t>LHX</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Aerojet Rocketdyne y/y</t>
+  </si>
+  <si>
+    <t>Backlog</t>
   </si>
 </sst>
 </file>
@@ -261,7 +264,7 @@
     <numFmt numFmtId="164" formatCode="[$$-409]#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -301,6 +304,15 @@
     <font>
       <b/>
       <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -349,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -382,6 +394,12 @@
     <xf numFmtId="3" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,7 +429,7 @@
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -461,7 +479,7 @@
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -828,14 +846,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="5">
-        <v>294.39999999999998</v>
+        <v>277.77999999999997</v>
       </c>
       <c r="E3" s="4">
-        <v>45961</v>
+        <v>45983</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45962</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="4">
         <v>46044</v>
@@ -858,7 +876,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>55082.239999999991</v>
+        <v>51972.637999999992</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -900,7 +918,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>66702.239999999991</v>
+        <v>63592.637999999992</v>
       </c>
     </row>
   </sheetData>
@@ -910,7 +928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C127D1A-B1AA-4685-BD0F-764C53F340E2}">
-  <dimension ref="B2:EO49"/>
+  <dimension ref="B2:EO55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="1"/>
@@ -1025,51 +1043,34 @@
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="15">
-        <v>1686</v>
-      </c>
+      <c r="E3" s="7"/>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="15">
-        <v>1683</v>
-      </c>
+      <c r="I3" s="7"/>
       <c r="J3" s="15">
-        <v>1800</v>
-      </c>
-      <c r="K3" s="15">
-        <v>1294</v>
-      </c>
-      <c r="L3" s="15">
-        <v>1346</v>
-      </c>
-      <c r="M3" s="15">
-        <v>1382</v>
-      </c>
+        <v>6300</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
       <c r="N3" s="15">
-        <v>1728</v>
-      </c>
-      <c r="O3" s="15">
-        <v>1352</v>
-      </c>
-      <c r="P3" s="15">
-        <v>1376</v>
-      </c>
+        <v>7300</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7"/>
       <c r="Q3" s="15">
-        <v>1462</v>
-      </c>
-      <c r="R3" s="15">
-        <f>N3*1.01</f>
-        <v>1745.28</v>
-      </c>
-      <c r="W3" s="15"/>
+        <v>7100</v>
+      </c>
+      <c r="R3" s="7"/>
+      <c r="W3" s="15">
+        <v>6300</v>
+      </c>
       <c r="X3" s="15">
-        <f>SUM(K3:N3)</f>
-        <v>5750</v>
-      </c>
-      <c r="Y3" s="6">
-        <f>SUM(O3:R3)</f>
-        <v>5935.28</v>
+        <v>7300</v>
+      </c>
+      <c r="Y3" s="15">
+        <v>7100</v>
       </c>
     </row>
     <row r="4" spans="2:35" x14ac:dyDescent="0.3">
@@ -1078,51 +1079,34 @@
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="15">
-        <v>1568</v>
-      </c>
+      <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
-      <c r="I4" s="15">
-        <v>1671</v>
-      </c>
+      <c r="I4" s="7"/>
       <c r="J4" s="15">
-        <v>1627</v>
-      </c>
-      <c r="K4" s="15">
-        <v>1627</v>
-      </c>
-      <c r="L4" s="15">
-        <v>1671</v>
-      </c>
-      <c r="M4" s="15">
-        <v>1608</v>
-      </c>
+        <v>9700</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
       <c r="N4" s="15">
-        <v>1773</v>
-      </c>
-      <c r="O4" s="15">
-        <v>1592</v>
-      </c>
-      <c r="P4" s="15">
-        <v>1622</v>
-      </c>
+        <v>10500</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
       <c r="Q4" s="15">
-        <v>1700</v>
-      </c>
-      <c r="R4" s="15">
-        <f>N4*0.98</f>
-        <v>1737.54</v>
-      </c>
-      <c r="W4" s="15"/>
+        <v>10100</v>
+      </c>
+      <c r="R4" s="7"/>
+      <c r="W4" s="15">
+        <v>9700</v>
+      </c>
       <c r="X4" s="15">
-        <f t="shared" ref="X4:X7" si="0">SUM(K4:N4)</f>
-        <v>6679</v>
-      </c>
-      <c r="Y4" s="6">
-        <f>SUM(O4:R4)</f>
-        <v>6651.54</v>
+        <v>10500</v>
+      </c>
+      <c r="Y4" s="15">
+        <v>10100</v>
       </c>
     </row>
     <row r="5" spans="2:35" x14ac:dyDescent="0.3">
@@ -1131,51 +1115,34 @@
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
-      <c r="E5" s="15">
-        <v>1255</v>
-      </c>
+      <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
-      <c r="I5" s="15">
-        <v>1382</v>
-      </c>
+      <c r="I5" s="7"/>
       <c r="J5" s="15">
-        <v>1363</v>
-      </c>
-      <c r="K5" s="15">
-        <v>1751</v>
-      </c>
-      <c r="L5" s="15">
-        <v>1707</v>
-      </c>
-      <c r="M5" s="15">
-        <v>1683</v>
-      </c>
+        <v>9500</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
       <c r="N5" s="15">
-        <v>1437</v>
-      </c>
-      <c r="O5" s="15">
-        <v>1611</v>
-      </c>
-      <c r="P5" s="15">
-        <v>1787</v>
-      </c>
+        <v>9400</v>
+      </c>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
       <c r="Q5" s="15">
-        <v>1809</v>
-      </c>
-      <c r="R5" s="15">
-        <f>N5*1.3</f>
-        <v>1868.1000000000001</v>
-      </c>
-      <c r="W5" s="15"/>
+        <v>10800</v>
+      </c>
+      <c r="R5" s="7"/>
+      <c r="W5" s="15">
+        <v>9500</v>
+      </c>
       <c r="X5" s="15">
-        <f t="shared" si="0"/>
-        <v>6578</v>
-      </c>
-      <c r="Y5" s="6">
-        <f>SUM(O5:R5)</f>
-        <v>7075.1</v>
+        <v>9400</v>
+      </c>
+      <c r="Y5" s="15">
+        <v>10800</v>
       </c>
     </row>
     <row r="6" spans="2:35" x14ac:dyDescent="0.3">
@@ -1184,3285 +1151,3540 @@
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
-      <c r="E6" s="15">
-        <v>455</v>
-      </c>
+      <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="15">
-        <v>596</v>
-      </c>
+      <c r="I6" s="7"/>
       <c r="J6" s="15">
-        <v>597</v>
-      </c>
-      <c r="K6" s="15">
-        <v>584</v>
-      </c>
-      <c r="L6" s="15">
-        <v>633</v>
-      </c>
-      <c r="M6" s="15">
-        <v>669</v>
-      </c>
+        <v>7200</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
       <c r="N6" s="15">
-        <v>628</v>
-      </c>
-      <c r="O6" s="15">
-        <v>629</v>
-      </c>
-      <c r="P6" s="15">
-        <v>698</v>
-      </c>
+        <v>7000</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
       <c r="Q6" s="15">
-        <v>755</v>
-      </c>
-      <c r="R6" s="15">
-        <f>N6*1.25</f>
-        <v>785</v>
-      </c>
-      <c r="W6" s="15"/>
+        <v>8300</v>
+      </c>
+      <c r="R6" s="7"/>
+      <c r="W6" s="15">
+        <v>7200</v>
+      </c>
       <c r="X6" s="15">
-        <f t="shared" si="0"/>
-        <v>2514</v>
-      </c>
-      <c r="Y6" s="6">
-        <f>SUM(O6:R6)</f>
-        <v>2867</v>
-      </c>
-    </row>
-    <row r="7" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B7" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="15">
-        <v>-49</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="15">
-        <v>-40</v>
-      </c>
-      <c r="J7" s="15">
-        <v>-47</v>
-      </c>
-      <c r="K7" s="15">
-        <v>-45</v>
-      </c>
-      <c r="L7" s="15">
-        <v>-58</v>
-      </c>
-      <c r="M7" s="15">
-        <v>-50</v>
-      </c>
-      <c r="N7" s="15">
-        <v>-43</v>
-      </c>
-      <c r="O7" s="15">
-        <v>-52</v>
-      </c>
-      <c r="P7" s="15">
-        <v>-57</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>-67</v>
-      </c>
-      <c r="R7" s="15">
-        <f>N7*1.7</f>
-        <v>-73.099999999999994</v>
-      </c>
-      <c r="W7" s="15"/>
-      <c r="X7" s="15">
-        <f t="shared" si="0"/>
-        <v>-196</v>
-      </c>
-    </row>
-    <row r="8" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="16">
-        <f>SUM(E3:E7)</f>
-        <v>4915</v>
-      </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="16">
-        <f t="shared" ref="I8:R8" si="1">SUM(I3:I7)</f>
-        <v>5292</v>
-      </c>
-      <c r="J8" s="16">
-        <f t="shared" si="1"/>
-        <v>5340</v>
-      </c>
-      <c r="K8" s="16">
-        <f t="shared" si="1"/>
-        <v>5211</v>
-      </c>
-      <c r="L8" s="16">
-        <f t="shared" si="1"/>
-        <v>5299</v>
-      </c>
-      <c r="M8" s="16">
-        <f t="shared" si="1"/>
-        <v>5292</v>
-      </c>
-      <c r="N8" s="16">
-        <f t="shared" si="1"/>
-        <v>5523</v>
-      </c>
-      <c r="O8" s="16">
-        <f t="shared" si="1"/>
-        <v>5132</v>
-      </c>
-      <c r="P8" s="16">
-        <f t="shared" si="1"/>
-        <v>5426</v>
-      </c>
-      <c r="Q8" s="16">
-        <f t="shared" si="1"/>
-        <v>5659</v>
-      </c>
-      <c r="R8" s="16">
-        <f t="shared" si="1"/>
-        <v>6062.82</v>
-      </c>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16">
-        <f>SUM(X3:X7)</f>
-        <v>21325</v>
-      </c>
+        <v>7000</v>
+      </c>
+      <c r="Y6" s="15">
+        <v>8300</v>
+      </c>
+    </row>
+    <row r="7" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="14"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="16">
+        <f>SUM(J3:J6)</f>
+        <v>32700</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" s="14"/>
+      <c r="M7" s="14"/>
+      <c r="N7" s="16">
+        <f>SUM(N3:N6)</f>
+        <v>34200</v>
+      </c>
+      <c r="O7" s="14"/>
+      <c r="P7" s="14"/>
+      <c r="Q7" s="16">
+        <f>SUM(Q3:Q6)</f>
+        <v>36300</v>
+      </c>
+      <c r="R7" s="14"/>
+      <c r="W7" s="16">
+        <f>SUM(W3:W6)</f>
+        <v>32700</v>
+      </c>
+      <c r="X7" s="16">
+        <f>SUM(X3:X6)</f>
+        <v>34200</v>
+      </c>
+      <c r="Y7" s="16">
+        <f>SUM(Y3:Y6)</f>
+        <v>36300</v>
+      </c>
+    </row>
+    <row r="8" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
     </row>
     <row r="9" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
+      <c r="E9" s="15">
+        <v>1686</v>
+      </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
+      <c r="I9" s="15">
+        <v>1683</v>
+      </c>
+      <c r="J9" s="15">
+        <v>1800</v>
+      </c>
+      <c r="K9" s="15">
+        <v>1294</v>
+      </c>
+      <c r="L9" s="15">
+        <v>1346</v>
+      </c>
+      <c r="M9" s="15">
+        <v>1382</v>
+      </c>
+      <c r="N9" s="15">
+        <v>1728</v>
+      </c>
+      <c r="O9" s="15">
+        <v>1352</v>
+      </c>
+      <c r="P9" s="15">
+        <v>1376</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>1462</v>
+      </c>
+      <c r="R9" s="20">
+        <f>N9*1.01</f>
+        <v>1745.28</v>
+      </c>
+      <c r="W9" s="15"/>
+      <c r="X9" s="15">
+        <f>SUM(K9:N9)</f>
+        <v>5750</v>
+      </c>
+      <c r="Y9" s="18">
+        <f>SUM(O9:R9)</f>
+        <v>5935.28</v>
+      </c>
     </row>
     <row r="10" spans="2:35" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="15">
+        <v>1568</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="15">
+        <v>1671</v>
+      </c>
+      <c r="J10" s="15">
+        <v>1627</v>
+      </c>
+      <c r="K10" s="15">
+        <v>1627</v>
+      </c>
+      <c r="L10" s="15">
+        <v>1671</v>
+      </c>
+      <c r="M10" s="15">
+        <v>1608</v>
+      </c>
+      <c r="N10" s="15">
+        <v>1773</v>
+      </c>
+      <c r="O10" s="15">
+        <v>1592</v>
+      </c>
+      <c r="P10" s="15">
+        <v>1622</v>
+      </c>
+      <c r="Q10" s="15">
+        <v>1700</v>
+      </c>
+      <c r="R10" s="20">
+        <f>N10*0.98</f>
+        <v>1737.54</v>
+      </c>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15">
+        <f t="shared" ref="X10:X13" si="0">SUM(K10:N10)</f>
+        <v>6679</v>
+      </c>
+      <c r="Y10" s="18">
+        <f>SUM(O10:R10)</f>
+        <v>6651.54</v>
+      </c>
+    </row>
+    <row r="11" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="15">
+        <v>1255</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="15">
+        <v>1382</v>
+      </c>
+      <c r="J11" s="15">
+        <v>1363</v>
+      </c>
+      <c r="K11" s="15">
+        <v>1751</v>
+      </c>
+      <c r="L11" s="15">
+        <v>1707</v>
+      </c>
+      <c r="M11" s="15">
+        <v>1683</v>
+      </c>
+      <c r="N11" s="15">
+        <v>1437</v>
+      </c>
+      <c r="O11" s="15">
+        <v>1611</v>
+      </c>
+      <c r="P11" s="15">
+        <v>1787</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>1809</v>
+      </c>
+      <c r="R11" s="20">
+        <f>N11*1.3</f>
+        <v>1868.1000000000001</v>
+      </c>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15">
+        <f t="shared" si="0"/>
+        <v>6578</v>
+      </c>
+      <c r="Y11" s="18">
+        <f>SUM(O11:R11)</f>
+        <v>7075.1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="15">
+        <v>455</v>
+      </c>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="15">
+        <v>596</v>
+      </c>
+      <c r="J12" s="15">
+        <v>597</v>
+      </c>
+      <c r="K12" s="15">
+        <v>584</v>
+      </c>
+      <c r="L12" s="15">
+        <v>633</v>
+      </c>
+      <c r="M12" s="15">
+        <v>669</v>
+      </c>
+      <c r="N12" s="15">
+        <v>628</v>
+      </c>
+      <c r="O12" s="15">
+        <v>629</v>
+      </c>
+      <c r="P12" s="15">
+        <v>698</v>
+      </c>
+      <c r="Q12" s="15">
+        <v>755</v>
+      </c>
+      <c r="R12" s="20">
+        <f>N12*1.25</f>
+        <v>785</v>
+      </c>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15">
+        <f t="shared" si="0"/>
+        <v>2514</v>
+      </c>
+      <c r="Y12" s="18">
+        <f>SUM(O12:R12)</f>
+        <v>2867</v>
+      </c>
+    </row>
+    <row r="13" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="15">
+        <v>-49</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="15">
+        <v>-40</v>
+      </c>
+      <c r="J13" s="15">
+        <v>-47</v>
+      </c>
+      <c r="K13" s="15">
+        <v>-45</v>
+      </c>
+      <c r="L13" s="15">
+        <v>-58</v>
+      </c>
+      <c r="M13" s="15">
+        <v>-50</v>
+      </c>
+      <c r="N13" s="15">
+        <v>-43</v>
+      </c>
+      <c r="O13" s="15">
+        <v>-52</v>
+      </c>
+      <c r="P13" s="15">
+        <v>-57</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>-67</v>
+      </c>
+      <c r="R13" s="20">
+        <f>N13*1.7</f>
+        <v>-73.099999999999994</v>
+      </c>
+      <c r="W13" s="15"/>
+      <c r="X13" s="15">
+        <f t="shared" si="0"/>
+        <v>-196</v>
+      </c>
+    </row>
+    <row r="14" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="16">
+        <f>SUM(E9:E13)</f>
+        <v>4915</v>
+      </c>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="16">
+        <f t="shared" ref="I14:R14" si="1">SUM(I9:I13)</f>
+        <v>5292</v>
+      </c>
+      <c r="J14" s="16">
+        <f t="shared" si="1"/>
+        <v>5340</v>
+      </c>
+      <c r="K14" s="16">
+        <f t="shared" si="1"/>
+        <v>5211</v>
+      </c>
+      <c r="L14" s="16">
+        <f t="shared" si="1"/>
+        <v>5299</v>
+      </c>
+      <c r="M14" s="16">
+        <f t="shared" si="1"/>
+        <v>5292</v>
+      </c>
+      <c r="N14" s="16">
+        <f t="shared" si="1"/>
+        <v>5523</v>
+      </c>
+      <c r="O14" s="16">
+        <f t="shared" si="1"/>
+        <v>5132</v>
+      </c>
+      <c r="P14" s="16">
+        <f t="shared" si="1"/>
+        <v>5426</v>
+      </c>
+      <c r="Q14" s="16">
+        <f t="shared" si="1"/>
+        <v>5659</v>
+      </c>
+      <c r="R14" s="21">
+        <f t="shared" si="1"/>
+        <v>6062.82</v>
+      </c>
+      <c r="W14" s="16"/>
+      <c r="X14" s="16">
+        <f>SUM(X9:X13)</f>
+        <v>21325</v>
+      </c>
+    </row>
+    <row r="15" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+    </row>
+    <row r="16" spans="2:35" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P10" s="6"/>
-      <c r="T10" s="6">
+      <c r="P16" s="6"/>
+      <c r="T16" s="6">
         <v>13581</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U16" s="6">
         <v>13156</v>
       </c>
-      <c r="V10" s="6">
+      <c r="V16" s="6">
         <v>12097</v>
       </c>
-      <c r="W10" s="6">
+      <c r="W16" s="6">
         <v>13694</v>
       </c>
-      <c r="X10" s="6">
+      <c r="X16" s="6">
         <v>15134</v>
       </c>
-      <c r="Y10" s="18">
-        <f>X10*1.06</f>
+      <c r="Y16" s="18">
+        <f>X16*1.06</f>
         <v>16042.04</v>
       </c>
-      <c r="Z10" s="6">
-        <f>Y10*1.05</f>
+      <c r="Z16" s="6">
+        <f>Y16*1.05</f>
         <v>16844.142</v>
       </c>
-      <c r="AA10" s="6">
-        <f>Z10*1.04</f>
+      <c r="AA16" s="6">
+        <f>Z16*1.04</f>
         <v>17517.90768</v>
       </c>
-      <c r="AB10" s="6">
-        <f>AA10*1.03</f>
+      <c r="AB16" s="6">
+        <f>AA16*1.03</f>
         <v>18043.444910400001</v>
       </c>
-      <c r="AC10" s="6">
-        <f t="shared" ref="AC10:AI10" si="2">AB10*1.02</f>
+      <c r="AC16" s="6">
+        <f t="shared" ref="AC16:AI16" si="2">AB16*1.02</f>
         <v>18404.313808608003</v>
       </c>
-      <c r="AD10" s="6">
+      <c r="AD16" s="6">
         <f t="shared" si="2"/>
         <v>18772.400084780165</v>
       </c>
-      <c r="AE10" s="6">
+      <c r="AE16" s="6">
         <f t="shared" si="2"/>
         <v>19147.848086475769</v>
       </c>
-      <c r="AF10" s="6">
+      <c r="AF16" s="6">
         <f t="shared" si="2"/>
         <v>19530.805048205286</v>
       </c>
-      <c r="AG10" s="6">
+      <c r="AG16" s="6">
         <f t="shared" si="2"/>
         <v>19921.421149169393</v>
       </c>
-      <c r="AH10" s="6">
+      <c r="AH16" s="6">
         <f t="shared" si="2"/>
         <v>20319.84957215278</v>
       </c>
-      <c r="AI10" s="6">
+      <c r="AI16" s="6">
         <f t="shared" si="2"/>
         <v>20726.246563595836</v>
       </c>
     </row>
-    <row r="11" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B11" s="1" t="s">
+    <row r="17" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P11" s="6"/>
-      <c r="T11" s="6">
+      <c r="P17" s="6"/>
+      <c r="T17" s="6">
         <v>4613</v>
       </c>
-      <c r="U11" s="6">
+      <c r="U17" s="6">
         <v>4658</v>
       </c>
-      <c r="V11" s="6">
+      <c r="V17" s="6">
         <v>4965</v>
       </c>
-      <c r="W11" s="6">
+      <c r="W17" s="6">
         <v>5725</v>
       </c>
-      <c r="X11" s="6">
+      <c r="X17" s="6">
         <v>6191</v>
       </c>
-      <c r="Y11" s="18">
-        <f>X11*1.04</f>
+      <c r="Y17" s="18">
+        <f>X17*1.04</f>
         <v>6438.64</v>
       </c>
-      <c r="Z11" s="6">
-        <f>Y11*1.05</f>
+      <c r="Z17" s="6">
+        <f>Y17*1.05</f>
         <v>6760.572000000001</v>
       </c>
-      <c r="AA11" s="6">
-        <f>Z11*1.04</f>
+      <c r="AA17" s="6">
+        <f>Z17*1.04</f>
         <v>7030.9948800000011</v>
       </c>
-      <c r="AB11" s="6">
-        <f>AA11*1.03</f>
+      <c r="AB17" s="6">
+        <f>AA17*1.03</f>
         <v>7241.9247264000014</v>
       </c>
-      <c r="AC11" s="6">
-        <f t="shared" ref="AC11:AI11" si="3">AB11*1.03</f>
+      <c r="AC17" s="6">
+        <f t="shared" ref="AC17:AI17" si="3">AB17*1.03</f>
         <v>7459.1824681920016</v>
       </c>
-      <c r="AD11" s="6">
+      <c r="AD17" s="6">
         <f t="shared" si="3"/>
         <v>7682.9579422377619</v>
       </c>
-      <c r="AE11" s="6">
+      <c r="AE17" s="6">
         <f t="shared" si="3"/>
         <v>7913.4466805048951</v>
       </c>
-      <c r="AF11" s="6">
+      <c r="AF17" s="6">
         <f t="shared" si="3"/>
         <v>8150.8500809200423</v>
       </c>
-      <c r="AG11" s="6">
+      <c r="AG17" s="6">
         <f t="shared" si="3"/>
         <v>8395.3755833476444</v>
       </c>
-      <c r="AH11" s="6">
+      <c r="AH17" s="6">
         <f t="shared" si="3"/>
         <v>8647.236850848074</v>
       </c>
-      <c r="AI11" s="6">
+      <c r="AI17" s="6">
         <f t="shared" si="3"/>
         <v>8906.6539563735168</v>
       </c>
     </row>
-    <row r="12" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="18" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K18" s="9">
         <v>5211</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L18" s="9">
         <v>5299</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M18" s="9">
         <v>5292</v>
       </c>
-      <c r="N12" s="9">
-        <f>X12-M12-L12-K12</f>
+      <c r="N18" s="9">
+        <f>X18-M18-L18-K18</f>
         <v>5523</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O18" s="9">
         <v>5132</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P18" s="9">
         <v>5426</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="Q18" s="9">
         <v>5659</v>
       </c>
-      <c r="R12" s="16">
-        <f>R8</f>
+      <c r="R18" s="16">
+        <f>R14</f>
         <v>6062.82</v>
       </c>
-      <c r="T12" s="9">
-        <f t="shared" ref="T12:X12" si="4">T10+T11</f>
+      <c r="T18" s="9">
+        <f t="shared" ref="T18:X18" si="4">T16+T17</f>
         <v>18194</v>
       </c>
-      <c r="U12" s="9">
+      <c r="U18" s="9">
         <f t="shared" si="4"/>
         <v>17814</v>
       </c>
-      <c r="V12" s="9">
+      <c r="V18" s="9">
         <f t="shared" si="4"/>
         <v>17062</v>
       </c>
-      <c r="W12" s="9">
+      <c r="W18" s="9">
         <f t="shared" si="4"/>
         <v>19419</v>
       </c>
-      <c r="X12" s="9">
+      <c r="X18" s="9">
         <f t="shared" si="4"/>
         <v>21325</v>
       </c>
-      <c r="Y12" s="9">
-        <f>SUM(O12:R12)</f>
+      <c r="Y18" s="9">
+        <f>SUM(O18:R18)</f>
         <v>22279.82</v>
       </c>
-      <c r="Z12" s="9">
-        <f t="shared" ref="Z12:AI12" si="5">Z10+Z11</f>
+      <c r="Z18" s="9">
+        <f t="shared" ref="Z18:AI18" si="5">Z16+Z17</f>
         <v>23604.714</v>
       </c>
-      <c r="AA12" s="9">
+      <c r="AA18" s="9">
         <f t="shared" si="5"/>
         <v>24548.902560000002</v>
       </c>
-      <c r="AB12" s="9">
+      <c r="AB18" s="9">
         <f t="shared" si="5"/>
         <v>25285.369636800002</v>
       </c>
-      <c r="AC12" s="9">
+      <c r="AC18" s="9">
         <f t="shared" si="5"/>
         <v>25863.496276800004</v>
       </c>
-      <c r="AD12" s="9">
+      <c r="AD18" s="9">
         <f t="shared" si="5"/>
         <v>26455.358027017926</v>
       </c>
-      <c r="AE12" s="9">
+      <c r="AE18" s="9">
         <f t="shared" si="5"/>
         <v>27061.294766980664</v>
       </c>
-      <c r="AF12" s="9">
+      <c r="AF18" s="9">
         <f t="shared" si="5"/>
         <v>27681.655129125327</v>
       </c>
-      <c r="AG12" s="9">
+      <c r="AG18" s="9">
         <f t="shared" si="5"/>
         <v>28316.796732517039</v>
       </c>
-      <c r="AH12" s="9">
+      <c r="AH18" s="9">
         <f t="shared" si="5"/>
         <v>28967.086423000852</v>
       </c>
-      <c r="AI12" s="9">
+      <c r="AI18" s="9">
         <f t="shared" si="5"/>
         <v>29632.900519969353</v>
       </c>
     </row>
-    <row r="13" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
+    <row r="19" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="T13" s="6">
+      <c r="K19" s="6"/>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6"/>
+      <c r="T19" s="6">
         <v>9464</v>
       </c>
-      <c r="U13" s="6">
+      <c r="U19" s="6">
         <v>9007</v>
       </c>
-      <c r="V13" s="6">
+      <c r="V19" s="6">
         <v>8355</v>
       </c>
-      <c r="W13" s="6">
+      <c r="W19" s="6">
         <v>9711</v>
       </c>
-      <c r="X13" s="6">
+      <c r="X19" s="6">
         <v>11019</v>
       </c>
-      <c r="Y13" s="18">
-        <f>Y10*0.73</f>
+      <c r="Y19" s="18">
+        <f>Y16*0.73</f>
         <v>11710.689200000001</v>
       </c>
-      <c r="Z13" s="6">
-        <f t="shared" ref="Z13:AI13" si="6">Z10*0.73</f>
+      <c r="Z19" s="6">
+        <f t="shared" ref="Z19:AI19" si="6">Z16*0.73</f>
         <v>12296.22366</v>
       </c>
-      <c r="AA13" s="6">
+      <c r="AA19" s="6">
         <f t="shared" si="6"/>
         <v>12788.072606399999</v>
       </c>
-      <c r="AB13" s="6">
+      <c r="AB19" s="6">
         <f t="shared" si="6"/>
         <v>13171.714784592001</v>
       </c>
-      <c r="AC13" s="6">
+      <c r="AC19" s="6">
         <f t="shared" si="6"/>
         <v>13435.149080283842</v>
       </c>
-      <c r="AD13" s="6">
+      <c r="AD19" s="6">
         <f t="shared" si="6"/>
         <v>13703.85206188952</v>
       </c>
-      <c r="AE13" s="6">
+      <c r="AE19" s="6">
         <f t="shared" si="6"/>
         <v>13977.929103127311</v>
       </c>
-      <c r="AF13" s="6">
+      <c r="AF19" s="6">
         <f t="shared" si="6"/>
         <v>14257.487685189859</v>
       </c>
-      <c r="AG13" s="6">
+      <c r="AG19" s="6">
         <f t="shared" si="6"/>
         <v>14542.637438893657</v>
       </c>
-      <c r="AH13" s="6">
+      <c r="AH19" s="6">
         <f t="shared" si="6"/>
         <v>14833.490187671528</v>
       </c>
-      <c r="AI13" s="6">
+      <c r="AI19" s="6">
         <f t="shared" si="6"/>
         <v>15130.15999142496</v>
       </c>
     </row>
-    <row r="14" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B14" s="1" t="s">
+    <row r="20" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="T14" s="6">
+      <c r="K20" s="6"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="T20" s="6">
         <v>3422</v>
       </c>
-      <c r="U14" s="6">
+      <c r="U20" s="6">
         <v>3431</v>
       </c>
-      <c r="V14" s="6">
+      <c r="V20" s="6">
         <v>3780</v>
       </c>
-      <c r="W14" s="6">
+      <c r="W20" s="6">
         <v>4595</v>
       </c>
-      <c r="X14" s="6">
+      <c r="X20" s="6">
         <v>4782</v>
       </c>
-      <c r="Y14" s="18">
-        <f>Y11*0.77</f>
+      <c r="Y20" s="18">
+        <f>Y17*0.77</f>
         <v>4957.7528000000002</v>
       </c>
-      <c r="Z14" s="6">
-        <f t="shared" ref="Z14:AI14" si="7">Z11*0.77</f>
+      <c r="Z20" s="6">
+        <f t="shared" ref="Z20:AI20" si="7">Z17*0.77</f>
         <v>5205.640440000001</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AA20" s="6">
         <f t="shared" si="7"/>
         <v>5413.8660576000011</v>
       </c>
-      <c r="AB14" s="6">
+      <c r="AB20" s="6">
         <f t="shared" si="7"/>
         <v>5576.2820393280008</v>
       </c>
-      <c r="AC14" s="6">
+      <c r="AC20" s="6">
         <f t="shared" si="7"/>
         <v>5743.5705005078416</v>
       </c>
-      <c r="AD14" s="6">
+      <c r="AD20" s="6">
         <f t="shared" si="7"/>
         <v>5915.8776155230771</v>
       </c>
-      <c r="AE14" s="6">
+      <c r="AE20" s="6">
         <f t="shared" si="7"/>
         <v>6093.3539439887691</v>
       </c>
-      <c r="AF14" s="6">
+      <c r="AF20" s="6">
         <f t="shared" si="7"/>
         <v>6276.154562308433</v>
       </c>
-      <c r="AG14" s="6">
+      <c r="AG20" s="6">
         <f t="shared" si="7"/>
         <v>6464.4391991776865</v>
       </c>
-      <c r="AH14" s="6">
+      <c r="AH20" s="6">
         <f t="shared" si="7"/>
         <v>6658.3723751530169</v>
       </c>
-      <c r="AI14" s="6">
+      <c r="AI20" s="6">
         <f t="shared" si="7"/>
         <v>6858.123546407608</v>
       </c>
     </row>
-    <row r="15" spans="2:35" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+    <row r="21" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K21" s="6">
         <v>3863</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L21" s="6">
         <v>3939</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M21" s="6">
         <v>3873</v>
       </c>
-      <c r="N15" s="9">
-        <f>X15-M15-L15-K15</f>
+      <c r="N21" s="9">
+        <f>X21-M21-L21-K21</f>
         <v>4126</v>
       </c>
-      <c r="O15" s="6">
+      <c r="O21" s="6">
         <v>3782</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P21" s="6">
         <v>4091</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="Q21" s="6">
         <v>4165</v>
       </c>
-      <c r="R15" s="6">
-        <f>R12-R16</f>
+      <c r="R21" s="6">
+        <f>R18-R22</f>
         <v>4486.4867999999997</v>
       </c>
-      <c r="T15" s="6">
-        <f t="shared" ref="T15:X15" si="8">T13+T14</f>
+      <c r="T21" s="6">
+        <f t="shared" ref="T21:X21" si="8">T19+T20</f>
         <v>12886</v>
       </c>
-      <c r="U15" s="6">
+      <c r="U21" s="6">
         <f t="shared" si="8"/>
         <v>12438</v>
       </c>
-      <c r="V15" s="6">
+      <c r="V21" s="6">
         <f t="shared" si="8"/>
         <v>12135</v>
       </c>
-      <c r="W15" s="6">
+      <c r="W21" s="6">
         <f t="shared" si="8"/>
         <v>14306</v>
       </c>
-      <c r="X15" s="6">
+      <c r="X21" s="6">
         <f t="shared" si="8"/>
         <v>15801</v>
       </c>
-      <c r="Y15" s="6">
-        <f>SUM(O15:R15)</f>
+      <c r="Y21" s="6">
+        <f>SUM(O21:R21)</f>
         <v>16524.486799999999</v>
       </c>
-      <c r="Z15" s="6">
-        <f t="shared" ref="Z15:AI15" si="9">Z13+Z14</f>
+      <c r="Z21" s="6">
+        <f t="shared" ref="Z21:AI21" si="9">Z19+Z20</f>
         <v>17501.864099999999</v>
       </c>
-      <c r="AA15" s="6">
+      <c r="AA21" s="6">
         <f t="shared" si="9"/>
         <v>18201.938664000001</v>
       </c>
-      <c r="AB15" s="6">
+      <c r="AB21" s="6">
         <f t="shared" si="9"/>
         <v>18747.996823920002</v>
       </c>
-      <c r="AC15" s="6">
+      <c r="AC21" s="6">
         <f t="shared" si="9"/>
         <v>19178.719580791683</v>
       </c>
-      <c r="AD15" s="6">
+      <c r="AD21" s="6">
         <f t="shared" si="9"/>
         <v>19619.729677412597</v>
       </c>
-      <c r="AE15" s="6">
+      <c r="AE21" s="6">
         <f t="shared" si="9"/>
         <v>20071.283047116081</v>
       </c>
-      <c r="AF15" s="6">
+      <c r="AF21" s="6">
         <f t="shared" si="9"/>
         <v>20533.64224749829</v>
       </c>
-      <c r="AG15" s="6">
+      <c r="AG21" s="6">
         <f t="shared" si="9"/>
         <v>21007.076638071343</v>
       </c>
-      <c r="AH15" s="6">
+      <c r="AH21" s="6">
         <f t="shared" si="9"/>
         <v>21491.862562824546</v>
       </c>
-      <c r="AI15" s="6">
+      <c r="AI21" s="6">
         <f t="shared" si="9"/>
         <v>21988.283537832569</v>
       </c>
     </row>
-    <row r="16" spans="2:35" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="22" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="9">
-        <f t="shared" ref="K16" si="10">K12-K15</f>
+      <c r="K22" s="9">
+        <f t="shared" ref="K22" si="10">K18-K21</f>
         <v>1348</v>
       </c>
-      <c r="L16" s="9">
-        <f t="shared" ref="L16:M16" si="11">L12-L15</f>
+      <c r="L22" s="9">
+        <f t="shared" ref="L22:M22" si="11">L18-L21</f>
         <v>1360</v>
       </c>
-      <c r="M16" s="9">
+      <c r="M22" s="9">
         <f t="shared" si="11"/>
         <v>1419</v>
       </c>
-      <c r="N16" s="9">
-        <f t="shared" ref="N16" si="12">N12-N15</f>
+      <c r="N22" s="9">
+        <f t="shared" ref="N22" si="12">N18-N21</f>
         <v>1397</v>
       </c>
-      <c r="O16" s="9">
-        <f t="shared" ref="O16:P16" si="13">O12-O15</f>
+      <c r="O22" s="9">
+        <f t="shared" ref="O22:P22" si="13">O18-O21</f>
         <v>1350</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P22" s="9">
         <f t="shared" si="13"/>
         <v>1335</v>
       </c>
-      <c r="Q16" s="9">
-        <f t="shared" ref="Q16" si="14">Q12-Q15</f>
+      <c r="Q22" s="9">
+        <f t="shared" ref="Q22" si="14">Q18-Q21</f>
         <v>1494</v>
       </c>
-      <c r="R16" s="9">
-        <f>R12*0.26</f>
+      <c r="R22" s="9">
+        <f>R18*0.26</f>
         <v>1576.3332</v>
       </c>
-      <c r="T16" s="9">
-        <f t="shared" ref="T16:Y16" si="15">T12-T15</f>
+      <c r="T22" s="9">
+        <f t="shared" ref="T22:Y22" si="15">T18-T21</f>
         <v>5308</v>
       </c>
-      <c r="U16" s="9">
+      <c r="U22" s="9">
         <f t="shared" si="15"/>
         <v>5376</v>
       </c>
-      <c r="V16" s="9">
+      <c r="V22" s="9">
         <f t="shared" si="15"/>
         <v>4927</v>
       </c>
-      <c r="W16" s="9">
+      <c r="W22" s="9">
         <f t="shared" si="15"/>
         <v>5113</v>
       </c>
-      <c r="X16" s="9">
+      <c r="X22" s="9">
         <f t="shared" si="15"/>
         <v>5524</v>
       </c>
-      <c r="Y16" s="9">
+      <c r="Y22" s="9">
         <f t="shared" si="15"/>
         <v>5755.3332000000009</v>
       </c>
-      <c r="Z16" s="9">
-        <f t="shared" ref="Z16:AI16" si="16">Z12-Z15</f>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22:AI22" si="16">Z18-Z21</f>
         <v>6102.8499000000011</v>
       </c>
-      <c r="AA16" s="9">
+      <c r="AA22" s="9">
         <f t="shared" si="16"/>
         <v>6346.9638960000011</v>
       </c>
-      <c r="AB16" s="9">
+      <c r="AB22" s="9">
         <f t="shared" si="16"/>
         <v>6537.3728128799994</v>
       </c>
-      <c r="AC16" s="9">
+      <c r="AC22" s="9">
         <f t="shared" si="16"/>
         <v>6684.7766960083209</v>
       </c>
-      <c r="AD16" s="9">
+      <c r="AD22" s="9">
         <f t="shared" si="16"/>
         <v>6835.6283496053293</v>
       </c>
-      <c r="AE16" s="9">
+      <c r="AE22" s="9">
         <f t="shared" si="16"/>
         <v>6990.0117198645821</v>
       </c>
-      <c r="AF16" s="9">
+      <c r="AF22" s="9">
         <f t="shared" si="16"/>
         <v>7148.0128816270371</v>
       </c>
-      <c r="AG16" s="9">
+      <c r="AG22" s="9">
         <f t="shared" si="16"/>
         <v>7309.7200944456963</v>
       </c>
-      <c r="AH16" s="9">
+      <c r="AH22" s="9">
         <f t="shared" si="16"/>
         <v>7475.2238601763056</v>
       </c>
-      <c r="AI16" s="9">
+      <c r="AI22" s="9">
         <f t="shared" si="16"/>
         <v>7644.6169821367839</v>
       </c>
     </row>
-    <row r="17" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B17" s="1" t="s">
+    <row r="23" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K23" s="6">
         <v>970</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L23" s="6">
         <v>884</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M23" s="6">
         <v>924</v>
       </c>
-      <c r="N17" s="6">
-        <f>X17-M17-L17-K17+X18</f>
+      <c r="N23" s="6">
+        <f>X23-M23-L23-K23+X24</f>
         <v>828</v>
       </c>
-      <c r="O17" s="6">
+      <c r="O23" s="6">
         <v>825</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P23" s="6">
         <v>764</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q23" s="6">
         <v>873</v>
       </c>
-      <c r="R17" s="6">
-        <f>N17*0.98</f>
+      <c r="R23" s="6">
+        <f>N23*0.98</f>
         <v>811.43999999999994</v>
       </c>
-      <c r="T17" s="6">
+      <c r="T23" s="6">
         <v>3315</v>
       </c>
-      <c r="U17" s="6">
+      <c r="U23" s="6">
         <v>3280</v>
       </c>
-      <c r="V17" s="6">
+      <c r="V23" s="6">
         <v>2998</v>
       </c>
-      <c r="W17" s="6">
+      <c r="W23" s="6">
         <v>3313</v>
       </c>
-      <c r="X17" s="6">
+      <c r="X23" s="6">
         <v>3568</v>
       </c>
-      <c r="Y17" s="6">
-        <f t="shared" ref="Y17:Y18" si="17">SUM(O17:R17)</f>
+      <c r="Y23" s="6">
+        <f t="shared" ref="Y23:Y24" si="17">SUM(O23:R23)</f>
         <v>3273.44</v>
       </c>
-      <c r="Z17" s="6">
-        <f>Y17*1.04</f>
+      <c r="Z23" s="6">
+        <f>Y23*1.04</f>
         <v>3404.3776000000003</v>
       </c>
-      <c r="AA17" s="6">
-        <f>Z17*1.03</f>
+      <c r="AA23" s="6">
+        <f>Z23*1.03</f>
         <v>3506.5089280000002</v>
       </c>
-      <c r="AB17" s="6">
-        <f>AA17*1.02</f>
+      <c r="AB23" s="6">
+        <f>AA23*1.02</f>
         <v>3576.6391065600001</v>
       </c>
-      <c r="AC17" s="6">
-        <f>AB17*1.01</f>
+      <c r="AC23" s="6">
+        <f>AB23*1.01</f>
         <v>3612.4054976256002</v>
       </c>
-      <c r="AD17" s="6">
-        <f t="shared" ref="AD17:AI17" si="18">AC17*1.01</f>
+      <c r="AD23" s="6">
+        <f t="shared" ref="AD23:AI23" si="18">AC23*1.01</f>
         <v>3648.5295526018563</v>
       </c>
-      <c r="AE17" s="6">
+      <c r="AE23" s="6">
         <f t="shared" si="18"/>
         <v>3685.0148481278748</v>
       </c>
-      <c r="AF17" s="6">
+      <c r="AF23" s="6">
         <f t="shared" si="18"/>
         <v>3721.8649966091534</v>
       </c>
-      <c r="AG17" s="6">
+      <c r="AG23" s="6">
         <f t="shared" si="18"/>
         <v>3759.083646575245</v>
       </c>
-      <c r="AH17" s="6">
+      <c r="AH23" s="6">
         <f t="shared" si="18"/>
         <v>3796.6744830409975</v>
       </c>
-      <c r="AI17" s="6">
+      <c r="AI23" s="6">
         <f t="shared" si="18"/>
         <v>3834.6412278714074</v>
       </c>
     </row>
-    <row r="18" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B18" s="1" t="s">
+    <row r="24" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K24" s="6">
         <v>0</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L24" s="6">
         <v>0</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M24" s="6">
         <v>0</v>
       </c>
-      <c r="N18" s="6">
+      <c r="N24" s="6">
         <v>0</v>
       </c>
-      <c r="O18" s="6">
+      <c r="O24" s="6">
         <v>0</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P24" s="6">
         <v>0</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q24" s="6">
         <v>0</v>
       </c>
-      <c r="R18" s="1">
+      <c r="R24" s="1">
         <v>0</v>
       </c>
-      <c r="T18" s="6">
+      <c r="T24" s="6">
         <f>51+767</f>
         <v>818</v>
       </c>
-      <c r="U18" s="6">
+      <c r="U24" s="6">
         <f>-220+207</f>
         <v>-13</v>
       </c>
-      <c r="V18" s="6">
+      <c r="V24" s="6">
         <v>802</v>
       </c>
-      <c r="W18" s="6">
+      <c r="W24" s="6">
         <v>374</v>
       </c>
-      <c r="X18" s="6">
+      <c r="X24" s="6">
         <v>38</v>
       </c>
-      <c r="Y18" s="6">
+      <c r="Y24" s="6">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="Z18" s="6">
+      <c r="Z24" s="6">
         <v>0</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AA24" s="6">
         <v>0</v>
       </c>
-      <c r="AB18" s="6">
+      <c r="AB24" s="6">
         <v>0</v>
       </c>
-      <c r="AC18" s="6">
+      <c r="AC24" s="6">
         <v>0</v>
       </c>
-      <c r="AD18" s="6">
+      <c r="AD24" s="6">
         <v>0</v>
       </c>
-      <c r="AE18" s="6">
+      <c r="AE24" s="6">
         <v>0</v>
       </c>
-      <c r="AF18" s="6">
+      <c r="AF24" s="6">
         <v>0</v>
       </c>
-      <c r="AG18" s="6">
+      <c r="AG24" s="6">
         <v>0</v>
       </c>
-      <c r="AH18" s="6">
+      <c r="AH24" s="6">
         <v>0</v>
       </c>
-      <c r="AI18" s="6">
+      <c r="AI24" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="2" t="s">
+    <row r="25" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K19" s="9">
-        <f t="shared" ref="K19" si="19">K16-K17-K18</f>
+      <c r="K25" s="9">
+        <f t="shared" ref="K25" si="19">K22-K23-K24</f>
         <v>378</v>
       </c>
-      <c r="L19" s="9">
-        <f t="shared" ref="L19:M19" si="20">L16-L17-L18</f>
+      <c r="L25" s="9">
+        <f t="shared" ref="L25:M25" si="20">L22-L23-L24</f>
         <v>476</v>
       </c>
-      <c r="M19" s="9">
+      <c r="M25" s="9">
         <f t="shared" si="20"/>
         <v>495</v>
       </c>
-      <c r="N19" s="9">
-        <f t="shared" ref="N19" si="21">N16-N17-N18</f>
+      <c r="N25" s="9">
+        <f t="shared" ref="N25" si="21">N22-N23-N24</f>
         <v>569</v>
       </c>
-      <c r="O19" s="9">
-        <f t="shared" ref="O19:P19" si="22">O16-O17-O18</f>
+      <c r="O25" s="9">
+        <f t="shared" ref="O25:P25" si="22">O22-O23-O24</f>
         <v>525</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P25" s="9">
         <f t="shared" si="22"/>
         <v>571</v>
       </c>
-      <c r="Q19" s="9">
-        <f t="shared" ref="Q19:R19" si="23">Q16-Q17-Q18</f>
+      <c r="Q25" s="9">
+        <f t="shared" ref="Q25:R25" si="23">Q22-Q23-Q24</f>
         <v>621</v>
       </c>
-      <c r="R19" s="9">
+      <c r="R25" s="9">
         <f t="shared" si="23"/>
         <v>764.89320000000009</v>
       </c>
-      <c r="T19" s="9">
-        <f t="shared" ref="T19:Y19" si="24">T16-T17-T18</f>
+      <c r="T25" s="9">
+        <f t="shared" ref="T25:Y25" si="24">T22-T23-T24</f>
         <v>1175</v>
       </c>
-      <c r="U19" s="9">
+      <c r="U25" s="9">
         <f t="shared" si="24"/>
         <v>2109</v>
       </c>
-      <c r="V19" s="9">
+      <c r="V25" s="9">
         <f t="shared" si="24"/>
         <v>1127</v>
       </c>
-      <c r="W19" s="9">
+      <c r="W25" s="9">
         <f t="shared" si="24"/>
         <v>1426</v>
       </c>
-      <c r="X19" s="9">
+      <c r="X25" s="9">
         <f t="shared" si="24"/>
         <v>1918</v>
       </c>
-      <c r="Y19" s="9">
+      <c r="Y25" s="9">
         <f t="shared" si="24"/>
         <v>2481.8932000000009</v>
       </c>
-      <c r="Z19" s="9">
-        <f t="shared" ref="Z19:AI19" si="25">Z16-Z17-Z18</f>
+      <c r="Z25" s="9">
+        <f t="shared" ref="Z25:AI25" si="25">Z22-Z23-Z24</f>
         <v>2698.4723000000008</v>
       </c>
-      <c r="AA19" s="9">
+      <c r="AA25" s="9">
         <f t="shared" si="25"/>
         <v>2840.4549680000009</v>
       </c>
-      <c r="AB19" s="9">
+      <c r="AB25" s="9">
         <f t="shared" si="25"/>
         <v>2960.7337063199993</v>
       </c>
-      <c r="AC19" s="9">
+      <c r="AC25" s="9">
         <f t="shared" si="25"/>
         <v>3072.3711983827206</v>
       </c>
-      <c r="AD19" s="9">
+      <c r="AD25" s="9">
         <f t="shared" si="25"/>
         <v>3187.098797003473</v>
       </c>
-      <c r="AE19" s="9">
+      <c r="AE25" s="9">
         <f t="shared" si="25"/>
         <v>3304.9968717367074</v>
       </c>
-      <c r="AF19" s="9">
+      <c r="AF25" s="9">
         <f t="shared" si="25"/>
         <v>3426.1478850178837</v>
       </c>
-      <c r="AG19" s="9">
+      <c r="AG25" s="9">
         <f t="shared" si="25"/>
         <v>3550.6364478704513</v>
       </c>
-      <c r="AH19" s="9">
+      <c r="AH25" s="9">
         <f t="shared" si="25"/>
         <v>3678.5493771353081</v>
       </c>
-      <c r="AI19" s="9">
+      <c r="AI25" s="9">
         <f t="shared" si="25"/>
         <v>3809.9757542653765</v>
       </c>
     </row>
-    <row r="20" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B20" s="1" t="s">
+    <row r="26" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K26" s="6">
         <v>-88</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L26" s="6">
         <v>-86</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M26" s="6">
         <v>-101</v>
       </c>
-      <c r="N20" s="6">
-        <f>X20-M20-L20-K20</f>
+      <c r="N26" s="6">
+        <f>X26-M26-L26-K26</f>
         <v>-79</v>
       </c>
-      <c r="O20" s="6">
+      <c r="O26" s="6">
         <v>-84</v>
       </c>
-      <c r="P20" s="6">
+      <c r="P26" s="6">
         <v>-105</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="Q26" s="6">
         <v>-98</v>
       </c>
-      <c r="R20" s="6">
+      <c r="R26" s="6">
         <v>-100</v>
       </c>
-      <c r="T20" s="6">
+      <c r="T26" s="6">
         <v>-401</v>
       </c>
-      <c r="U20" s="6">
+      <c r="U26" s="6">
         <v>-439</v>
       </c>
-      <c r="V20" s="6">
+      <c r="V26" s="6">
         <v>-425</v>
       </c>
-      <c r="W20" s="6">
+      <c r="W26" s="6">
         <v>-338</v>
       </c>
-      <c r="X20" s="6">
+      <c r="X26" s="6">
         <v>-354</v>
       </c>
-      <c r="Y20" s="6">
-        <f t="shared" ref="Y20:Y21" si="26">SUM(O20:R20)</f>
+      <c r="Y26" s="6">
+        <f t="shared" ref="Y26:Y27" si="26">SUM(O26:R26)</f>
         <v>-387</v>
       </c>
-      <c r="Z20" s="6">
-        <f t="shared" ref="Z20:AI20" si="27">Y20*1.01</f>
+      <c r="Z26" s="6">
+        <f t="shared" ref="Z26:AI26" si="27">Y26*1.01</f>
         <v>-390.87</v>
       </c>
-      <c r="AA20" s="6">
+      <c r="AA26" s="6">
         <f t="shared" si="27"/>
         <v>-394.77870000000001</v>
       </c>
-      <c r="AB20" s="6">
+      <c r="AB26" s="6">
         <f t="shared" si="27"/>
         <v>-398.72648700000002</v>
       </c>
-      <c r="AC20" s="6">
+      <c r="AC26" s="6">
         <f t="shared" si="27"/>
         <v>-402.71375187000001</v>
       </c>
-      <c r="AD20" s="6">
+      <c r="AD26" s="6">
         <f t="shared" si="27"/>
         <v>-406.7408893887</v>
       </c>
-      <c r="AE20" s="6">
+      <c r="AE26" s="6">
         <f t="shared" si="27"/>
         <v>-410.80829828258697</v>
       </c>
-      <c r="AF20" s="6">
+      <c r="AF26" s="6">
         <f t="shared" si="27"/>
         <v>-414.91638126541284</v>
       </c>
-      <c r="AG20" s="6">
+      <c r="AG26" s="6">
         <f t="shared" si="27"/>
         <v>-419.06554507806698</v>
       </c>
-      <c r="AH20" s="6">
+      <c r="AH26" s="6">
         <f t="shared" si="27"/>
         <v>-423.25620052884767</v>
       </c>
-      <c r="AI20" s="6">
+      <c r="AI26" s="6">
         <f t="shared" si="27"/>
         <v>-427.48876253413613</v>
       </c>
     </row>
-    <row r="21" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B21" s="1" t="s">
+    <row r="27" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B27" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K27" s="6">
         <v>176</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L27" s="6">
         <v>172</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M27" s="6">
         <v>166</v>
       </c>
-      <c r="N21" s="6">
-        <f>X21-M21-L21-K21</f>
+      <c r="N27" s="6">
+        <f>X27-M27-L27-K27</f>
         <v>161</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O27" s="6">
         <v>150</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P27" s="6">
         <v>152</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="Q27" s="6">
         <v>152</v>
       </c>
-      <c r="R21" s="6">
+      <c r="R27" s="6">
         <v>152</v>
       </c>
-      <c r="T21" s="6">
+      <c r="T27" s="6">
         <v>254</v>
       </c>
-      <c r="U21" s="6">
+      <c r="U27" s="6">
         <v>265</v>
       </c>
-      <c r="V21" s="6">
+      <c r="V27" s="6">
         <v>279</v>
       </c>
-      <c r="W21" s="6">
+      <c r="W27" s="6">
         <v>543</v>
       </c>
-      <c r="X21" s="6">
+      <c r="X27" s="6">
         <v>675</v>
       </c>
-      <c r="Y21" s="6">
+      <c r="Y27" s="6">
         <f t="shared" si="26"/>
         <v>606</v>
       </c>
-      <c r="Z21" s="6">
-        <f t="shared" ref="Z21:AI21" si="28">Y21*1.01</f>
+      <c r="Z27" s="6">
+        <f t="shared" ref="Z27:AI27" si="28">Y27*1.01</f>
         <v>612.06000000000006</v>
       </c>
-      <c r="AA21" s="6">
+      <c r="AA27" s="6">
         <f t="shared" si="28"/>
         <v>618.18060000000003</v>
       </c>
-      <c r="AB21" s="6">
+      <c r="AB27" s="6">
         <f t="shared" si="28"/>
         <v>624.36240600000008</v>
       </c>
-      <c r="AC21" s="6">
+      <c r="AC27" s="6">
         <f t="shared" si="28"/>
         <v>630.60603006000008</v>
       </c>
-      <c r="AD21" s="6">
+      <c r="AD27" s="6">
         <f t="shared" si="28"/>
         <v>636.91209036060013</v>
       </c>
-      <c r="AE21" s="6">
+      <c r="AE27" s="6">
         <f t="shared" si="28"/>
         <v>643.28121126420615</v>
       </c>
-      <c r="AF21" s="6">
+      <c r="AF27" s="6">
         <f t="shared" si="28"/>
         <v>649.71402337684822</v>
       </c>
-      <c r="AG21" s="6">
+      <c r="AG27" s="6">
         <f t="shared" si="28"/>
         <v>656.21116361061672</v>
       </c>
-      <c r="AH21" s="6">
+      <c r="AH27" s="6">
         <f t="shared" si="28"/>
         <v>662.77327524672285</v>
       </c>
-      <c r="AI21" s="6">
+      <c r="AI27" s="6">
         <f t="shared" si="28"/>
         <v>669.40100799919003</v>
       </c>
     </row>
-    <row r="22" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="2" t="s">
+    <row r="28" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="9">
-        <f t="shared" ref="K22" si="29">K19-K20-K21</f>
+      <c r="K28" s="9">
+        <f t="shared" ref="K28" si="29">K25-K26-K27</f>
         <v>290</v>
       </c>
-      <c r="L22" s="9">
-        <f t="shared" ref="L22:M22" si="30">L19-L20-L21</f>
+      <c r="L28" s="9">
+        <f t="shared" ref="L28:M28" si="30">L25-L26-L27</f>
         <v>390</v>
       </c>
-      <c r="M22" s="9">
+      <c r="M28" s="9">
         <f t="shared" si="30"/>
         <v>430</v>
       </c>
-      <c r="N22" s="9">
-        <f t="shared" ref="N22" si="31">N19-N20-N21</f>
+      <c r="N28" s="9">
+        <f t="shared" ref="N28" si="31">N25-N26-N27</f>
         <v>487</v>
       </c>
-      <c r="O22" s="9">
-        <f t="shared" ref="O22:P22" si="32">O19-O20-O21</f>
+      <c r="O28" s="9">
+        <f t="shared" ref="O28:P28" si="32">O25-O26-O27</f>
         <v>459</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P28" s="9">
         <f t="shared" si="32"/>
         <v>524</v>
       </c>
-      <c r="Q22" s="9">
-        <f t="shared" ref="Q22:R22" si="33">Q19-Q20-Q21</f>
+      <c r="Q28" s="9">
+        <f t="shared" ref="Q28:R28" si="33">Q25-Q26-Q27</f>
         <v>567</v>
       </c>
-      <c r="R22" s="9">
+      <c r="R28" s="9">
         <f t="shared" si="33"/>
         <v>712.89320000000009</v>
       </c>
-      <c r="T22" s="9">
-        <f t="shared" ref="T22:Y22" si="34">T19-T20-T21</f>
+      <c r="T28" s="9">
+        <f t="shared" ref="T28:Y28" si="34">T25-T26-T27</f>
         <v>1322</v>
       </c>
-      <c r="U22" s="9">
+      <c r="U28" s="9">
         <f t="shared" si="34"/>
         <v>2283</v>
       </c>
-      <c r="V22" s="9">
+      <c r="V28" s="9">
         <f t="shared" si="34"/>
         <v>1273</v>
       </c>
-      <c r="W22" s="9">
+      <c r="W28" s="9">
         <f t="shared" si="34"/>
         <v>1221</v>
       </c>
-      <c r="X22" s="9">
+      <c r="X28" s="9">
         <f t="shared" si="34"/>
         <v>1597</v>
       </c>
-      <c r="Y22" s="9">
+      <c r="Y28" s="9">
         <f t="shared" si="34"/>
         <v>2262.8932000000009</v>
       </c>
-      <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AI22" si="35">Z19-Z20-Z21</f>
+      <c r="Z28" s="9">
+        <f t="shared" ref="Z28:AI28" si="35">Z25-Z26-Z27</f>
         <v>2477.2823000000008</v>
       </c>
-      <c r="AA22" s="9">
+      <c r="AA28" s="9">
         <f t="shared" si="35"/>
         <v>2617.0530680000006</v>
       </c>
-      <c r="AB22" s="9">
+      <c r="AB28" s="9">
         <f t="shared" si="35"/>
         <v>2735.097787319999</v>
       </c>
-      <c r="AC22" s="9">
+      <c r="AC28" s="9">
         <f t="shared" si="35"/>
         <v>2844.4789201927206</v>
       </c>
-      <c r="AD22" s="9">
+      <c r="AD28" s="9">
         <f t="shared" si="35"/>
         <v>2956.9275960315726</v>
       </c>
-      <c r="AE22" s="9">
+      <c r="AE28" s="9">
         <f t="shared" si="35"/>
         <v>3072.5239587550886</v>
       </c>
-      <c r="AF22" s="9">
+      <c r="AF28" s="9">
         <f t="shared" si="35"/>
         <v>3191.3502429064483</v>
       </c>
-      <c r="AG22" s="9">
+      <c r="AG28" s="9">
         <f t="shared" si="35"/>
         <v>3313.4908293379012</v>
       </c>
-      <c r="AH22" s="9">
+      <c r="AH28" s="9">
         <f t="shared" si="35"/>
         <v>3439.0323024174331</v>
       </c>
-      <c r="AI22" s="9">
+      <c r="AI28" s="9">
         <f t="shared" si="35"/>
         <v>3568.0635088003223</v>
       </c>
     </row>
-    <row r="23" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B23" s="1" t="s">
+    <row r="29" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K29" s="6">
         <v>5</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L29" s="6">
         <v>23</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M29" s="6">
         <v>26</v>
       </c>
-      <c r="N23" s="6">
-        <f t="shared" ref="N23:N24" si="36">X23-M23-L23-K23</f>
+      <c r="N29" s="6">
+        <f t="shared" ref="N29:N30" si="36">X29-M29-L29-K29</f>
         <v>31</v>
       </c>
-      <c r="O23" s="6">
+      <c r="O29" s="6">
         <v>73</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P29" s="6">
         <v>66</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="Q29" s="6">
         <v>105</v>
       </c>
-      <c r="R23" s="6">
-        <f>R22*0.15</f>
+      <c r="R29" s="6">
+        <f>R28*0.15</f>
         <v>106.93398000000001</v>
       </c>
-      <c r="T23" s="6">
+      <c r="T29" s="6">
         <v>234</v>
       </c>
-      <c r="U23" s="6">
+      <c r="U29" s="6">
         <v>440</v>
       </c>
-      <c r="V23" s="6">
+      <c r="V29" s="6">
         <v>212</v>
       </c>
-      <c r="W23" s="6">
+      <c r="W29" s="6">
         <v>23</v>
       </c>
-      <c r="X23" s="6">
+      <c r="X29" s="6">
         <v>85</v>
       </c>
-      <c r="Y23" s="6">
-        <f t="shared" ref="Y23:Y24" si="37">SUM(O23:R23)</f>
+      <c r="Y29" s="6">
+        <f t="shared" ref="Y29:Y30" si="37">SUM(O29:R29)</f>
         <v>350.93398000000002</v>
       </c>
-      <c r="Z23" s="6">
-        <f>Z22*0.15</f>
+      <c r="Z29" s="6">
+        <f>Z28*0.15</f>
         <v>371.59234500000008</v>
       </c>
-      <c r="AA23" s="6">
-        <f t="shared" ref="AA23:AI23" si="38">AA22*0.15</f>
+      <c r="AA29" s="6">
+        <f t="shared" ref="AA29:AI29" si="38">AA28*0.15</f>
         <v>392.55796020000008</v>
       </c>
-      <c r="AB23" s="6">
+      <c r="AB29" s="6">
         <f t="shared" si="38"/>
         <v>410.26466809799985</v>
       </c>
-      <c r="AC23" s="6">
+      <c r="AC29" s="6">
         <f t="shared" si="38"/>
         <v>426.6718380289081</v>
       </c>
-      <c r="AD23" s="6">
+      <c r="AD29" s="6">
         <f t="shared" si="38"/>
         <v>443.53913940473586</v>
       </c>
-      <c r="AE23" s="6">
+      <c r="AE29" s="6">
         <f t="shared" si="38"/>
         <v>460.87859381326325</v>
       </c>
-      <c r="AF23" s="6">
+      <c r="AF29" s="6">
         <f t="shared" si="38"/>
         <v>478.7025364359672</v>
       </c>
-      <c r="AG23" s="6">
+      <c r="AG29" s="6">
         <f t="shared" si="38"/>
         <v>497.02362440068515</v>
       </c>
-      <c r="AH23" s="6">
+      <c r="AH29" s="6">
         <f t="shared" si="38"/>
         <v>515.85484536261492</v>
       </c>
-      <c r="AI23" s="6">
+      <c r="AI29" s="6">
         <f t="shared" si="38"/>
         <v>535.20952632004833</v>
       </c>
     </row>
-    <row r="24" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B24" s="1" t="s">
+    <row r="30" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K30" s="6">
         <v>2</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L30" s="6">
         <v>1</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M30" s="6">
         <v>4</v>
       </c>
-      <c r="N24" s="6">
+      <c r="N30" s="6">
         <f t="shared" si="36"/>
         <v>3</v>
       </c>
-      <c r="O24" s="6">
+      <c r="O30" s="6">
         <v>0</v>
       </c>
-      <c r="P24" s="6">
+      <c r="P30" s="6">
         <v>0</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="Q30" s="6">
         <v>0</v>
       </c>
-      <c r="R24" s="6">
+      <c r="R30" s="6">
         <v>0</v>
       </c>
-      <c r="T24" s="6">
+      <c r="T30" s="6">
         <f>2-33</f>
         <v>-31</v>
       </c>
-      <c r="U24" s="6">
+      <c r="U30" s="6">
         <f>1-4</f>
         <v>-3</v>
       </c>
-      <c r="V24" s="6">
+      <c r="V30" s="6">
         <v>-1</v>
       </c>
-      <c r="W24" s="6">
+      <c r="W30" s="6">
         <v>-29</v>
       </c>
-      <c r="X24" s="6">
+      <c r="X30" s="6">
         <v>10</v>
       </c>
-      <c r="Y24" s="6">
+      <c r="Y30" s="6">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="Z30" s="6">
         <v>0</v>
       </c>
-      <c r="AA24" s="6">
+      <c r="AA30" s="6">
         <v>0</v>
       </c>
-      <c r="AB24" s="6">
+      <c r="AB30" s="6">
         <v>0</v>
       </c>
-      <c r="AC24" s="6">
+      <c r="AC30" s="6">
         <v>0</v>
       </c>
-      <c r="AD24" s="6">
+      <c r="AD30" s="6">
         <v>0</v>
       </c>
-      <c r="AE24" s="6">
+      <c r="AE30" s="6">
         <v>0</v>
       </c>
-      <c r="AF24" s="6">
+      <c r="AF30" s="6">
         <v>0</v>
       </c>
-      <c r="AG24" s="6">
+      <c r="AG30" s="6">
         <v>0</v>
       </c>
-      <c r="AH24" s="6">
+      <c r="AH30" s="6">
         <v>0</v>
       </c>
-      <c r="AI24" s="6">
+      <c r="AI30" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="2" t="s">
+    <row r="31" spans="2:145" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K25" s="9">
-        <f t="shared" ref="K25" si="39">K22-K23-K24</f>
+      <c r="K31" s="9">
+        <f t="shared" ref="K31" si="39">K28-K29-K30</f>
         <v>283</v>
       </c>
-      <c r="L25" s="9">
-        <f t="shared" ref="L25:M25" si="40">L22-L23-L24</f>
+      <c r="L31" s="9">
+        <f t="shared" ref="L31:M31" si="40">L28-L29-L30</f>
         <v>366</v>
       </c>
-      <c r="M25" s="9">
+      <c r="M31" s="9">
         <f t="shared" si="40"/>
         <v>400</v>
       </c>
-      <c r="N25" s="9">
-        <f t="shared" ref="N25" si="41">N22-N23-N24</f>
+      <c r="N31" s="9">
+        <f t="shared" ref="N31" si="41">N28-N29-N30</f>
         <v>453</v>
       </c>
-      <c r="O25" s="9">
-        <f t="shared" ref="O25:P25" si="42">O22-O23-O24</f>
+      <c r="O31" s="9">
+        <f t="shared" ref="O31:P31" si="42">O28-O29-O30</f>
         <v>386</v>
       </c>
-      <c r="P25" s="9">
+      <c r="P31" s="9">
         <f t="shared" si="42"/>
         <v>458</v>
       </c>
-      <c r="Q25" s="9">
-        <f t="shared" ref="Q25:R25" si="43">Q22-Q23-Q24</f>
+      <c r="Q31" s="9">
+        <f t="shared" ref="Q31:R31" si="43">Q28-Q29-Q30</f>
         <v>462</v>
       </c>
-      <c r="R25" s="9">
+      <c r="R31" s="9">
         <f t="shared" si="43"/>
         <v>605.95922000000007</v>
       </c>
-      <c r="T25" s="9">
-        <f t="shared" ref="T25:Y25" si="44">T22-T23-T24</f>
+      <c r="T31" s="9">
+        <f t="shared" ref="T31:Y31" si="44">T28-T29-T30</f>
         <v>1119</v>
       </c>
-      <c r="U25" s="9">
+      <c r="U31" s="9">
         <f t="shared" si="44"/>
         <v>1846</v>
       </c>
-      <c r="V25" s="9">
+      <c r="V31" s="9">
         <f t="shared" si="44"/>
         <v>1062</v>
       </c>
-      <c r="W25" s="9">
+      <c r="W31" s="9">
         <f t="shared" si="44"/>
         <v>1227</v>
       </c>
-      <c r="X25" s="9">
+      <c r="X31" s="9">
         <f t="shared" si="44"/>
         <v>1502</v>
       </c>
-      <c r="Y25" s="9">
+      <c r="Y31" s="9">
         <f t="shared" si="44"/>
         <v>1911.9592200000009</v>
       </c>
-      <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AI25" si="45">Z22-Z23-Z24</f>
+      <c r="Z31" s="9">
+        <f t="shared" ref="Z31:AI31" si="45">Z28-Z29-Z30</f>
         <v>2105.6899550000007</v>
       </c>
-      <c r="AA25" s="9">
+      <c r="AA31" s="9">
         <f t="shared" si="45"/>
         <v>2224.4951078000004</v>
       </c>
-      <c r="AB25" s="9">
+      <c r="AB31" s="9">
         <f t="shared" si="45"/>
         <v>2324.8331192219994</v>
       </c>
-      <c r="AC25" s="9">
+      <c r="AC31" s="9">
         <f t="shared" si="45"/>
         <v>2417.8070821638125</v>
       </c>
-      <c r="AD25" s="9">
+      <c r="AD31" s="9">
         <f t="shared" si="45"/>
         <v>2513.3884566268366</v>
       </c>
-      <c r="AE25" s="9">
+      <c r="AE31" s="9">
         <f t="shared" si="45"/>
         <v>2611.6453649418254</v>
       </c>
-      <c r="AF25" s="9">
+      <c r="AF31" s="9">
         <f t="shared" si="45"/>
         <v>2712.6477064704814</v>
       </c>
-      <c r="AG25" s="9">
+      <c r="AG31" s="9">
         <f t="shared" si="45"/>
         <v>2816.4672049372161</v>
       </c>
-      <c r="AH25" s="9">
+      <c r="AH31" s="9">
         <f t="shared" si="45"/>
         <v>2923.1774570548182</v>
       </c>
-      <c r="AI25" s="9">
+      <c r="AI31" s="9">
         <f t="shared" si="45"/>
         <v>3032.8539824802738</v>
       </c>
-      <c r="AJ25" s="2">
-        <f>AI25*(1+$AL$35)</f>
+      <c r="AJ31" s="2">
+        <f>AI31*(1+$AL$41)</f>
         <v>3002.5254426554711</v>
       </c>
-      <c r="AK25" s="2">
-        <f t="shared" ref="AK25:CV25" si="46">AJ25*(1+$AL$35)</f>
+      <c r="AK31" s="2">
+        <f t="shared" ref="AK31:CV31" si="46">AJ31*(1+$AL$41)</f>
         <v>2972.5001882289166</v>
       </c>
-      <c r="AL25" s="2">
+      <c r="AL31" s="2">
         <f t="shared" si="46"/>
         <v>2942.7751863466274</v>
       </c>
-      <c r="AM25" s="2">
+      <c r="AM31" s="2">
         <f t="shared" si="46"/>
         <v>2913.3474344831611</v>
       </c>
-      <c r="AN25" s="2">
+      <c r="AN31" s="2">
         <f t="shared" si="46"/>
         <v>2884.2139601383296</v>
       </c>
-      <c r="AO25" s="2">
+      <c r="AO31" s="2">
         <f t="shared" si="46"/>
         <v>2855.3718205369464</v>
       </c>
-      <c r="AP25" s="2">
+      <c r="AP31" s="2">
         <f t="shared" si="46"/>
         <v>2826.8181023315769</v>
       </c>
-      <c r="AQ25" s="2">
+      <c r="AQ31" s="2">
         <f t="shared" si="46"/>
         <v>2798.5499213082612</v>
       </c>
-      <c r="AR25" s="2">
+      <c r="AR31" s="2">
         <f t="shared" si="46"/>
         <v>2770.5644220951785</v>
       </c>
-      <c r="AS25" s="2">
+      <c r="AS31" s="2">
         <f t="shared" si="46"/>
         <v>2742.8587778742267</v>
       </c>
-      <c r="AT25" s="2">
+      <c r="AT31" s="2">
         <f t="shared" si="46"/>
         <v>2715.4301900954842</v>
       </c>
-      <c r="AU25" s="2">
+      <c r="AU31" s="2">
         <f t="shared" si="46"/>
         <v>2688.2758881945292</v>
       </c>
-      <c r="AV25" s="2">
+      <c r="AV31" s="2">
         <f t="shared" si="46"/>
         <v>2661.3931293125838</v>
       </c>
-      <c r="AW25" s="2">
+      <c r="AW31" s="2">
         <f t="shared" si="46"/>
         <v>2634.7791980194579</v>
       </c>
-      <c r="AX25" s="2">
+      <c r="AX31" s="2">
         <f t="shared" si="46"/>
         <v>2608.4314060392635</v>
       </c>
-      <c r="AY25" s="2">
+      <c r="AY31" s="2">
         <f t="shared" si="46"/>
         <v>2582.347091978871</v>
       </c>
-      <c r="AZ25" s="2">
+      <c r="AZ31" s="2">
         <f t="shared" si="46"/>
         <v>2556.5236210590824</v>
       </c>
-      <c r="BA25" s="2">
+      <c r="BA31" s="2">
         <f t="shared" si="46"/>
         <v>2530.9583848484917</v>
       </c>
-      <c r="BB25" s="2">
+      <c r="BB31" s="2">
         <f t="shared" si="46"/>
         <v>2505.6488010000066</v>
       </c>
-      <c r="BC25" s="2">
+      <c r="BC31" s="2">
         <f t="shared" si="46"/>
         <v>2480.5923129900066</v>
       </c>
-      <c r="BD25" s="2">
+      <c r="BD31" s="2">
         <f t="shared" si="46"/>
         <v>2455.7863898601063</v>
       </c>
-      <c r="BE25" s="2">
+      <c r="BE31" s="2">
         <f t="shared" si="46"/>
         <v>2431.2285259615051</v>
       </c>
-      <c r="BF25" s="2">
+      <c r="BF31" s="2">
         <f t="shared" si="46"/>
         <v>2406.9162407018898</v>
       </c>
-      <c r="BG25" s="2">
+      <c r="BG31" s="2">
         <f t="shared" si="46"/>
         <v>2382.8470782948707</v>
       </c>
-      <c r="BH25" s="2">
+      <c r="BH31" s="2">
         <f t="shared" si="46"/>
         <v>2359.0186075119218</v>
       </c>
-      <c r="BI25" s="2">
+      <c r="BI31" s="2">
         <f t="shared" si="46"/>
         <v>2335.4284214368026</v>
       </c>
-      <c r="BJ25" s="2">
+      <c r="BJ31" s="2">
         <f t="shared" si="46"/>
         <v>2312.0741372224347</v>
       </c>
-      <c r="BK25" s="2">
+      <c r="BK31" s="2">
         <f t="shared" si="46"/>
         <v>2288.9533958502102</v>
       </c>
-      <c r="BL25" s="2">
+      <c r="BL31" s="2">
         <f t="shared" si="46"/>
         <v>2266.0638618917083</v>
       </c>
-      <c r="BM25" s="2">
+      <c r="BM31" s="2">
         <f t="shared" si="46"/>
         <v>2243.4032232727914</v>
       </c>
-      <c r="BN25" s="2">
+      <c r="BN31" s="2">
         <f t="shared" si="46"/>
         <v>2220.9691910400634</v>
       </c>
-      <c r="BO25" s="2">
+      <c r="BO31" s="2">
         <f t="shared" si="46"/>
         <v>2198.7594991296628</v>
       </c>
-      <c r="BP25" s="2">
+      <c r="BP31" s="2">
         <f t="shared" si="46"/>
         <v>2176.7719041383662</v>
       </c>
-      <c r="BQ25" s="2">
+      <c r="BQ31" s="2">
         <f t="shared" si="46"/>
         <v>2155.0041850969824</v>
       </c>
-      <c r="BR25" s="2">
+      <c r="BR31" s="2">
         <f t="shared" si="46"/>
         <v>2133.4541432460123</v>
       </c>
-      <c r="BS25" s="2">
+      <c r="BS31" s="2">
         <f t="shared" si="46"/>
         <v>2112.119601813552</v>
       </c>
-      <c r="BT25" s="2">
+      <c r="BT31" s="2">
         <f t="shared" si="46"/>
         <v>2090.9984057954166</v>
       </c>
-      <c r="BU25" s="2">
+      <c r="BU31" s="2">
         <f t="shared" si="46"/>
         <v>2070.0884217374623</v>
       </c>
-      <c r="BV25" s="2">
+      <c r="BV31" s="2">
         <f t="shared" si="46"/>
         <v>2049.3875375200878</v>
       </c>
-      <c r="BW25" s="2">
+      <c r="BW31" s="2">
         <f t="shared" si="46"/>
         <v>2028.893662144887</v>
       </c>
-      <c r="BX25" s="2">
+      <c r="BX31" s="2">
         <f t="shared" si="46"/>
         <v>2008.6047255234382</v>
       </c>
-      <c r="BY25" s="2">
+      <c r="BY31" s="2">
         <f t="shared" si="46"/>
         <v>1988.5186782682038</v>
       </c>
-      <c r="BZ25" s="2">
+      <c r="BZ31" s="2">
         <f t="shared" si="46"/>
         <v>1968.6334914855217</v>
       </c>
-      <c r="CA25" s="2">
+      <c r="CA31" s="2">
         <f t="shared" si="46"/>
         <v>1948.9471565706665</v>
       </c>
-      <c r="CB25" s="2">
+      <c r="CB31" s="2">
         <f t="shared" si="46"/>
         <v>1929.4576850049598</v>
       </c>
-      <c r="CC25" s="2">
+      <c r="CC31" s="2">
         <f t="shared" si="46"/>
         <v>1910.1631081549101</v>
       </c>
-      <c r="CD25" s="2">
+      <c r="CD31" s="2">
         <f t="shared" si="46"/>
         <v>1891.0614770733609</v>
       </c>
-      <c r="CE25" s="2">
+      <c r="CE31" s="2">
         <f t="shared" si="46"/>
         <v>1872.1508623026273</v>
       </c>
-      <c r="CF25" s="2">
+      <c r="CF31" s="2">
         <f t="shared" si="46"/>
         <v>1853.429353679601</v>
       </c>
-      <c r="CG25" s="2">
+      <c r="CG31" s="2">
         <f t="shared" si="46"/>
         <v>1834.8950601428051</v>
       </c>
-      <c r="CH25" s="2">
+      <c r="CH31" s="2">
         <f t="shared" si="46"/>
         <v>1816.5461095413771</v>
       </c>
-      <c r="CI25" s="2">
+      <c r="CI31" s="2">
         <f t="shared" si="46"/>
         <v>1798.3806484459633</v>
       </c>
-      <c r="CJ25" s="2">
+      <c r="CJ31" s="2">
         <f t="shared" si="46"/>
         <v>1780.3968419615037</v>
       </c>
-      <c r="CK25" s="2">
+      <c r="CK31" s="2">
         <f t="shared" si="46"/>
         <v>1762.5928735418886</v>
       </c>
-      <c r="CL25" s="2">
+      <c r="CL31" s="2">
         <f t="shared" si="46"/>
         <v>1744.9669448064697</v>
       </c>
-      <c r="CM25" s="2">
+      <c r="CM31" s="2">
         <f t="shared" si="46"/>
         <v>1727.517275358405</v>
       </c>
-      <c r="CN25" s="2">
+      <c r="CN31" s="2">
         <f t="shared" si="46"/>
         <v>1710.242102604821</v>
       </c>
-      <c r="CO25" s="2">
+      <c r="CO31" s="2">
         <f t="shared" si="46"/>
         <v>1693.1396815787728</v>
       </c>
-      <c r="CP25" s="2">
+      <c r="CP31" s="2">
         <f t="shared" si="46"/>
         <v>1676.2082847629849</v>
       </c>
-      <c r="CQ25" s="2">
+      <c r="CQ31" s="2">
         <f t="shared" si="46"/>
         <v>1659.446201915355</v>
       </c>
-      <c r="CR25" s="2">
+      <c r="CR31" s="2">
         <f t="shared" si="46"/>
         <v>1642.8517398962015</v>
       </c>
-      <c r="CS25" s="2">
+      <c r="CS31" s="2">
         <f t="shared" si="46"/>
         <v>1626.4232224972395</v>
       </c>
-      <c r="CT25" s="2">
+      <c r="CT31" s="2">
         <f t="shared" si="46"/>
         <v>1610.1589902722671</v>
       </c>
-      <c r="CU25" s="2">
+      <c r="CU31" s="2">
         <f t="shared" si="46"/>
         <v>1594.0574003695444</v>
       </c>
-      <c r="CV25" s="2">
+      <c r="CV31" s="2">
         <f t="shared" si="46"/>
         <v>1578.116826365849</v>
       </c>
-      <c r="CW25" s="2">
-        <f t="shared" ref="CW25:EO25" si="47">CV25*(1+$AL$35)</f>
+      <c r="CW31" s="2">
+        <f t="shared" ref="CW31:EO31" si="47">CV31*(1+$AL$41)</f>
         <v>1562.3356581021906</v>
       </c>
-      <c r="CX25" s="2">
+      <c r="CX31" s="2">
         <f t="shared" si="47"/>
         <v>1546.7123015211687</v>
       </c>
-      <c r="CY25" s="2">
+      <c r="CY31" s="2">
         <f t="shared" si="47"/>
         <v>1531.245178505957</v>
       </c>
-      <c r="CZ25" s="2">
+      <c r="CZ31" s="2">
         <f t="shared" si="47"/>
         <v>1515.9327267208973</v>
       </c>
-      <c r="DA25" s="2">
+      <c r="DA31" s="2">
         <f t="shared" si="47"/>
         <v>1500.7733994536884</v>
       </c>
-      <c r="DB25" s="2">
+      <c r="DB31" s="2">
         <f t="shared" si="47"/>
         <v>1485.7656654591515</v>
       </c>
-      <c r="DC25" s="2">
+      <c r="DC31" s="2">
         <f t="shared" si="47"/>
         <v>1470.90800880456</v>
       </c>
-      <c r="DD25" s="2">
+      <c r="DD31" s="2">
         <f t="shared" si="47"/>
         <v>1456.1989287165145</v>
       </c>
-      <c r="DE25" s="2">
+      <c r="DE31" s="2">
         <f t="shared" si="47"/>
         <v>1441.6369394293492</v>
       </c>
-      <c r="DF25" s="2">
+      <c r="DF31" s="2">
         <f t="shared" si="47"/>
         <v>1427.2205700350557</v>
       </c>
-      <c r="DG25" s="2">
+      <c r="DG31" s="2">
         <f t="shared" si="47"/>
         <v>1412.9483643347053</v>
       </c>
-      <c r="DH25" s="2">
+      <c r="DH31" s="2">
         <f t="shared" si="47"/>
         <v>1398.8188806913581</v>
       </c>
-      <c r="DI25" s="2">
+      <c r="DI31" s="2">
         <f t="shared" si="47"/>
         <v>1384.8306918844446</v>
       </c>
-      <c r="DJ25" s="2">
+      <c r="DJ31" s="2">
         <f t="shared" si="47"/>
         <v>1370.9823849656002</v>
       </c>
-      <c r="DK25" s="2">
+      <c r="DK31" s="2">
         <f t="shared" si="47"/>
         <v>1357.2725611159442</v>
       </c>
-      <c r="DL25" s="2">
+      <c r="DL31" s="2">
         <f t="shared" si="47"/>
         <v>1343.6998355047847</v>
       </c>
-      <c r="DM25" s="2">
+      <c r="DM31" s="2">
         <f t="shared" si="47"/>
         <v>1330.2628371497369</v>
       </c>
-      <c r="DN25" s="2">
+      <c r="DN31" s="2">
         <f t="shared" si="47"/>
         <v>1316.9602087782396</v>
       </c>
-      <c r="DO25" s="2">
+      <c r="DO31" s="2">
         <f t="shared" si="47"/>
         <v>1303.7906066904573</v>
       </c>
-      <c r="DP25" s="2">
+      <c r="DP31" s="2">
         <f t="shared" si="47"/>
         <v>1290.7527006235528</v>
       </c>
-      <c r="DQ25" s="2">
+      <c r="DQ31" s="2">
         <f t="shared" si="47"/>
         <v>1277.8451736173172</v>
       </c>
-      <c r="DR25" s="2">
+      <c r="DR31" s="2">
         <f t="shared" si="47"/>
         <v>1265.0667218811441</v>
       </c>
-      <c r="DS25" s="2">
+      <c r="DS31" s="2">
         <f t="shared" si="47"/>
         <v>1252.4160546623327</v>
       </c>
-      <c r="DT25" s="2">
+      <c r="DT31" s="2">
         <f t="shared" si="47"/>
         <v>1239.8918941157094</v>
       </c>
-      <c r="DU25" s="2">
+      <c r="DU31" s="2">
         <f t="shared" si="47"/>
         <v>1227.4929751745524</v>
       </c>
-      <c r="DV25" s="2">
+      <c r="DV31" s="2">
         <f t="shared" si="47"/>
         <v>1215.2180454228069</v>
       </c>
-      <c r="DW25" s="2">
+      <c r="DW31" s="2">
         <f t="shared" si="47"/>
         <v>1203.0658649685788</v>
       </c>
-      <c r="DX25" s="2">
+      <c r="DX31" s="2">
         <f t="shared" si="47"/>
         <v>1191.035206318893</v>
       </c>
-      <c r="DY25" s="2">
+      <c r="DY31" s="2">
         <f t="shared" si="47"/>
         <v>1179.1248542557041</v>
       </c>
-      <c r="DZ25" s="2">
+      <c r="DZ31" s="2">
         <f t="shared" si="47"/>
         <v>1167.3336057131471</v>
       </c>
-      <c r="EA25" s="2">
+      <c r="EA31" s="2">
         <f t="shared" si="47"/>
         <v>1155.6602696560155</v>
       </c>
-      <c r="EB25" s="2">
+      <c r="EB31" s="2">
         <f t="shared" si="47"/>
         <v>1144.1036669594553</v>
       </c>
-      <c r="EC25" s="2">
+      <c r="EC31" s="2">
         <f t="shared" si="47"/>
         <v>1132.6626302898608</v>
       </c>
-      <c r="ED25" s="2">
+      <c r="ED31" s="2">
         <f t="shared" si="47"/>
         <v>1121.3360039869622</v>
       </c>
-      <c r="EE25" s="2">
+      <c r="EE31" s="2">
         <f t="shared" si="47"/>
         <v>1110.1226439470925</v>
       </c>
-      <c r="EF25" s="2">
+      <c r="EF31" s="2">
         <f t="shared" si="47"/>
         <v>1099.0214175076214</v>
       </c>
-      <c r="EG25" s="2">
+      <c r="EG31" s="2">
         <f t="shared" si="47"/>
         <v>1088.0312033325451</v>
       </c>
-      <c r="EH25" s="2">
+      <c r="EH31" s="2">
         <f t="shared" si="47"/>
         <v>1077.1508912992197</v>
       </c>
-      <c r="EI25" s="2">
+      <c r="EI31" s="2">
         <f t="shared" si="47"/>
         <v>1066.3793823862275</v>
       </c>
-      <c r="EJ25" s="2">
+      <c r="EJ31" s="2">
         <f t="shared" si="47"/>
         <v>1055.7155885623652</v>
       </c>
-      <c r="EK25" s="2">
+      <c r="EK31" s="2">
         <f t="shared" si="47"/>
         <v>1045.1584326767415</v>
       </c>
-      <c r="EL25" s="2">
+      <c r="EL31" s="2">
         <f t="shared" si="47"/>
         <v>1034.7068483499741</v>
       </c>
-      <c r="EM25" s="2">
+      <c r="EM31" s="2">
         <f t="shared" si="47"/>
         <v>1024.3597798664744</v>
       </c>
-      <c r="EN25" s="2">
+      <c r="EN31" s="2">
         <f t="shared" si="47"/>
         <v>1014.1161820678096</v>
       </c>
-      <c r="EO25" s="2">
+      <c r="EO31" s="2">
         <f t="shared" si="47"/>
         <v>1003.9750202471315</v>
       </c>
     </row>
-    <row r="26" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B26" s="1" t="s">
+    <row r="32" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="K26" s="6">
-        <f t="shared" ref="K26" si="48">188.3</f>
+      <c r="K32" s="6">
+        <f t="shared" ref="K32" si="48">188.3</f>
         <v>188.3</v>
       </c>
-      <c r="L26" s="6">
-        <f t="shared" ref="L26:N26" si="49">188.3</f>
+      <c r="L32" s="6">
+        <f t="shared" ref="L32:N32" si="49">188.3</f>
         <v>188.3</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M32" s="6">
         <f t="shared" si="49"/>
         <v>188.3</v>
       </c>
-      <c r="N26" s="6">
+      <c r="N32" s="6">
         <f t="shared" si="49"/>
         <v>188.3</v>
       </c>
-      <c r="O26" s="6">
-        <f t="shared" ref="O26:P26" si="50">188.3</f>
+      <c r="O32" s="6">
+        <f t="shared" ref="O32:P32" si="50">188.3</f>
         <v>188.3</v>
       </c>
-      <c r="P26" s="6">
+      <c r="P32" s="6">
         <f t="shared" si="50"/>
         <v>188.3</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="Q32" s="6">
         <v>187.1</v>
       </c>
-      <c r="R26" s="6">
+      <c r="R32" s="6">
         <v>187.1</v>
       </c>
-      <c r="T26" s="6">
-        <f t="shared" ref="T26:X26" si="51">188.3</f>
+      <c r="T32" s="6">
+        <f t="shared" ref="T32:X32" si="51">188.3</f>
         <v>188.3</v>
       </c>
-      <c r="U26" s="6">
+      <c r="U32" s="6">
         <f t="shared" si="51"/>
         <v>188.3</v>
       </c>
-      <c r="V26" s="6">
+      <c r="V32" s="6">
         <f t="shared" si="51"/>
         <v>188.3</v>
       </c>
-      <c r="W26" s="6">
+      <c r="W32" s="6">
         <f t="shared" si="51"/>
         <v>188.3</v>
       </c>
-      <c r="X26" s="6">
+      <c r="X32" s="6">
         <f t="shared" si="51"/>
         <v>188.3</v>
       </c>
-      <c r="Y26" s="6">
+      <c r="Y32" s="6">
         <v>187.1</v>
       </c>
-      <c r="Z26" s="6">
+      <c r="Z32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AA26" s="6">
+      <c r="AA32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AB26" s="6">
+      <c r="AB32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AC26" s="6">
+      <c r="AC32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AD26" s="6">
+      <c r="AD32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AE26" s="6">
+      <c r="AE32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AF26" s="6">
+      <c r="AF32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AG26" s="6">
+      <c r="AG32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AH26" s="6">
+      <c r="AH32" s="6">
         <v>187.1</v>
       </c>
-      <c r="AI26" s="6">
+      <c r="AI32" s="6">
         <v>187.1</v>
       </c>
     </row>
-    <row r="27" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B27" s="1" t="s">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K27" s="8">
-        <f t="shared" ref="K27" si="52">K25/K26</f>
+      <c r="K33" s="8">
+        <f t="shared" ref="K33" si="52">K31/K32</f>
         <v>1.5029208709506106</v>
       </c>
-      <c r="L27" s="8">
-        <f t="shared" ref="L27:M27" si="53">L25/L26</f>
+      <c r="L33" s="8">
+        <f t="shared" ref="L33:M33" si="53">L31/L32</f>
         <v>1.9437068507700477</v>
       </c>
-      <c r="M27" s="8">
+      <c r="M33" s="8">
         <f t="shared" si="53"/>
         <v>2.1242697822623473</v>
       </c>
-      <c r="N27" s="8">
-        <f t="shared" ref="N27" si="54">N25/N26</f>
+      <c r="N33" s="8">
+        <f t="shared" ref="N33" si="54">N31/N32</f>
         <v>2.4057355284121082</v>
       </c>
-      <c r="O27" s="8">
-        <f t="shared" ref="O27:P27" si="55">O25/O26</f>
+      <c r="O33" s="8">
+        <f t="shared" ref="O33:P33" si="55">O31/O32</f>
         <v>2.0499203398831649</v>
       </c>
-      <c r="P27" s="8">
+      <c r="P33" s="8">
         <f t="shared" si="55"/>
         <v>2.4322889006903874</v>
       </c>
-      <c r="Q27" s="8">
-        <f t="shared" ref="Q27:R27" si="56">Q25/Q26</f>
+      <c r="Q33" s="8">
+        <f t="shared" ref="Q33:R33" si="56">Q31/Q32</f>
         <v>2.4692677712453235</v>
       </c>
-      <c r="R27" s="8">
+      <c r="R33" s="8">
         <f t="shared" si="56"/>
         <v>3.2386917156600754</v>
       </c>
-      <c r="T27" s="8">
-        <f t="shared" ref="T27:Y27" si="57">T25/T26</f>
+      <c r="T33" s="8">
+        <f t="shared" ref="T33:Y33" si="57">T31/T32</f>
         <v>5.9426447158789166</v>
       </c>
-      <c r="U27" s="8">
+      <c r="U33" s="8">
         <f t="shared" si="57"/>
         <v>9.8035050451407315</v>
       </c>
-      <c r="V27" s="8">
+      <c r="V33" s="8">
         <f t="shared" si="57"/>
         <v>5.6399362719065316</v>
       </c>
-      <c r="W27" s="8">
+      <c r="W33" s="8">
         <f t="shared" si="57"/>
         <v>6.5161975570897503</v>
       </c>
-      <c r="X27" s="8">
+      <c r="X33" s="8">
         <f t="shared" si="57"/>
         <v>7.9766330323951138</v>
       </c>
-      <c r="Y27" s="8">
+      <c r="Y33" s="8">
         <f t="shared" si="57"/>
         <v>10.218916194548374</v>
       </c>
-      <c r="Z27" s="8">
-        <f t="shared" ref="Z27:AI27" si="58">Z25/Z26</f>
+      <c r="Z33" s="8">
+        <f t="shared" ref="Z33:AI33" si="58">Z31/Z32</f>
         <v>11.25435571886692</v>
       </c>
-      <c r="AA27" s="8">
+      <c r="AA33" s="8">
         <f t="shared" si="58"/>
         <v>11.889337828968468</v>
       </c>
-      <c r="AB27" s="8">
+      <c r="AB33" s="8">
         <f t="shared" si="58"/>
         <v>12.425617954152857</v>
       </c>
-      <c r="AC27" s="8">
+      <c r="AC33" s="8">
         <f t="shared" si="58"/>
         <v>12.922539188475749</v>
       </c>
-      <c r="AD27" s="8">
+      <c r="AD33" s="8">
         <f t="shared" si="58"/>
         <v>13.433396347551238</v>
       </c>
-      <c r="AE27" s="8">
+      <c r="AE33" s="8">
         <f t="shared" si="58"/>
         <v>13.958553527214461</v>
       </c>
-      <c r="AF27" s="8">
+      <c r="AF33" s="8">
         <f t="shared" si="58"/>
         <v>14.498384321060831</v>
       </c>
-      <c r="AG27" s="8">
+      <c r="AG33" s="8">
         <f t="shared" si="58"/>
         <v>15.053272073421786</v>
       </c>
-      <c r="AH27" s="8">
+      <c r="AH33" s="8">
         <f t="shared" si="58"/>
         <v>15.62361013925611</v>
       </c>
-      <c r="AI27" s="8">
+      <c r="AI33" s="8">
         <f t="shared" si="58"/>
         <v>16.209802151150583</v>
       </c>
     </row>
-    <row r="29" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="M29" s="10">
-        <f t="shared" ref="M29:N32" si="59">M3/I3-1</f>
+      <c r="M35" s="10">
+        <f t="shared" ref="M35:N38" si="59">M9/I9-1</f>
         <v>-0.17884729649435527</v>
       </c>
-      <c r="N29" s="10">
+      <c r="N35" s="10">
         <f t="shared" si="59"/>
         <v>-4.0000000000000036E-2</v>
       </c>
-      <c r="O29" s="10">
-        <f>O3/K3-1</f>
+      <c r="O35" s="10">
+        <f>O9/K9-1</f>
         <v>4.4822256568779029E-2</v>
       </c>
-      <c r="P29" s="10">
-        <f>P3/L3-1</f>
+      <c r="P35" s="10">
+        <f>P9/L9-1</f>
         <v>2.2288261515601704E-2</v>
       </c>
-      <c r="Q29" s="10">
-        <f>Q3/M3-1</f>
+      <c r="Q35" s="10">
+        <f>Q9/M9-1</f>
         <v>5.7887120115774238E-2</v>
       </c>
-      <c r="R29" s="10">
-        <f>R3/N3-1</f>
+      <c r="R35" s="10">
+        <f>R9/N9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="Y29" s="10">
-        <f>Y3/X3-1</f>
+      <c r="Y35" s="10">
+        <f>Y9/X9-1</f>
         <v>3.2222608695652077E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B30" s="1" t="s">
+    <row r="36" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B36" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="M30" s="10">
+      <c r="M36" s="10">
         <f t="shared" si="59"/>
         <v>-3.7701974865350096E-2</v>
       </c>
-      <c r="N30" s="10">
+      <c r="N36" s="10">
         <f t="shared" si="59"/>
         <v>8.973570989551316E-2</v>
       </c>
-      <c r="O30" s="10">
-        <f t="shared" ref="O30:R32" si="60">O4/K4-1</f>
+      <c r="O36" s="10">
+        <f t="shared" ref="O36:R38" si="60">O10/K10-1</f>
         <v>-2.1511985248924392E-2</v>
       </c>
-      <c r="P30" s="10">
+      <c r="P36" s="10">
         <f t="shared" si="60"/>
         <v>-2.9323758228605667E-2</v>
       </c>
-      <c r="Q30" s="10">
+      <c r="Q36" s="10">
         <f t="shared" si="60"/>
         <v>5.7213930348258613E-2</v>
       </c>
-      <c r="R30" s="10">
+      <c r="R36" s="10">
         <f t="shared" si="60"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="Y30" s="10">
-        <f t="shared" ref="Y30:Y32" si="61">Y4/X4-1</f>
+      <c r="Y36" s="10">
+        <f t="shared" ref="Y36:Y38" si="61">Y10/X10-1</f>
         <v>-4.1113939212457096E-3</v>
       </c>
     </row>
-    <row r="31" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B31" s="1" t="s">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="M31" s="10">
+      <c r="M37" s="10">
         <f t="shared" si="59"/>
         <v>0.21780028943560059</v>
       </c>
-      <c r="N31" s="10">
+      <c r="N37" s="10">
         <f t="shared" si="59"/>
         <v>5.4292002934702932E-2</v>
       </c>
-      <c r="O31" s="10">
+      <c r="O37" s="10">
         <f t="shared" si="60"/>
         <v>-7.9954311821816115E-2</v>
       </c>
-      <c r="P31" s="10">
+      <c r="P37" s="10">
         <f t="shared" si="60"/>
         <v>4.6865846514352771E-2</v>
       </c>
-      <c r="Q31" s="10">
+      <c r="Q37" s="10">
         <f t="shared" si="60"/>
         <v>7.4866310160427885E-2</v>
       </c>
-      <c r="R31" s="10">
+      <c r="R37" s="10">
         <f t="shared" si="60"/>
         <v>0.30000000000000004</v>
       </c>
-      <c r="Y31" s="10">
+      <c r="Y37" s="10">
         <f t="shared" si="61"/>
         <v>7.5570082091821256E-2</v>
       </c>
     </row>
-    <row r="32" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B32" s="1" t="s">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="M32" s="10">
+      <c r="M38" s="10">
         <f t="shared" si="59"/>
         <v>0.12248322147651014</v>
       </c>
-      <c r="N32" s="10">
+      <c r="N38" s="10">
         <f t="shared" si="59"/>
         <v>5.1926298157453976E-2</v>
       </c>
-      <c r="O32" s="10">
+      <c r="O38" s="10">
         <f t="shared" si="60"/>
         <v>7.7054794520547976E-2</v>
       </c>
-      <c r="P32" s="10">
+      <c r="P38" s="10">
         <f t="shared" si="60"/>
         <v>0.10268562401263814</v>
       </c>
-      <c r="Q32" s="10">
+      <c r="Q38" s="10">
         <f t="shared" si="60"/>
         <v>0.12855007473841562</v>
       </c>
-      <c r="R32" s="10">
+      <c r="R38" s="10">
         <f t="shared" si="60"/>
         <v>0.25</v>
       </c>
-      <c r="Y32" s="10">
+      <c r="Y38" s="10">
         <f t="shared" si="61"/>
         <v>0.14041368337311066</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B34" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="K34" s="10"/>
-      <c r="L34" s="10"/>
-      <c r="M34" s="10"/>
-      <c r="O34" s="10"/>
-      <c r="P34" s="10"/>
-      <c r="Q34" s="10"/>
-      <c r="T34" s="10"/>
-      <c r="U34" s="10">
-        <f t="shared" ref="U34:W36" si="62">U10/T10-1</f>
-        <v>-3.1293719166482603E-2</v>
-      </c>
-      <c r="V34" s="10">
-        <f t="shared" si="62"/>
-        <v>-8.0495591365156605E-2</v>
-      </c>
-      <c r="W34" s="10">
-        <f t="shared" si="62"/>
-        <v>0.13201620236422262</v>
-      </c>
-      <c r="X34" s="10">
-        <f>X10/W10-1</f>
-        <v>0.10515554257338988</v>
-      </c>
-      <c r="Y34" s="19">
-        <f t="shared" ref="Y34:AI36" si="63">Y10/X10-1</f>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="Z34" s="10">
-        <f t="shared" si="63"/>
-        <v>4.9999999999999822E-2</v>
-      </c>
-      <c r="AA34" s="10">
-        <f t="shared" si="63"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AB34" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AC34" s="10">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AD34" s="10">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AE34" s="10">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AF34" s="10">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AG34" s="10">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AH34" s="10">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AI34" s="10">
-        <f t="shared" si="63"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B35" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="T35" s="10"/>
-      <c r="U35" s="10">
-        <f t="shared" si="62"/>
-        <v>9.7550401040538137E-3</v>
-      </c>
-      <c r="V35" s="10">
-        <f t="shared" si="62"/>
-        <v>6.5908115070845819E-2</v>
-      </c>
-      <c r="W35" s="10">
-        <f t="shared" si="62"/>
-        <v>0.15307150050352458</v>
-      </c>
-      <c r="X35" s="10">
-        <f t="shared" ref="X35:X36" si="64">X11/W11-1</f>
-        <v>8.1397379912663714E-2</v>
-      </c>
-      <c r="Y35" s="19">
-        <f t="shared" si="63"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="Z35" s="10">
-        <f t="shared" si="63"/>
-        <v>5.0000000000000044E-2</v>
-      </c>
-      <c r="AA35" s="10">
-        <f t="shared" si="63"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AB35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AC35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AD35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AE35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AF35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AG35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AH35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AI35" s="10">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AK35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="AL35" s="10">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="36" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B36" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="O36" s="11">
-        <f>O12/K12-1</f>
-        <v>-1.5160237958165457E-2</v>
-      </c>
-      <c r="P36" s="11">
-        <f>P12/L12-1</f>
-        <v>2.3966786186072842E-2</v>
-      </c>
-      <c r="Q36" s="11">
-        <f>Q12/M12-1</f>
-        <v>6.9349962207104987E-2</v>
-      </c>
-      <c r="R36" s="11">
-        <f>R12/N12-1</f>
-        <v>9.774035850081475E-2</v>
-      </c>
-      <c r="T36" s="11"/>
-      <c r="U36" s="11">
-        <f t="shared" si="62"/>
-        <v>-2.0886006375728239E-2</v>
-      </c>
-      <c r="V36" s="11">
-        <f t="shared" si="62"/>
-        <v>-4.2213988997417795E-2</v>
-      </c>
-      <c r="W36" s="11">
-        <f t="shared" si="62"/>
-        <v>0.13814324229281438</v>
-      </c>
-      <c r="X36" s="11">
-        <f t="shared" si="64"/>
-        <v>9.815129512333276E-2</v>
-      </c>
-      <c r="Y36" s="11">
-        <f t="shared" si="63"/>
-        <v>4.4774677608440783E-2</v>
-      </c>
-      <c r="Z36" s="11">
-        <f t="shared" si="63"/>
-        <v>5.946609981588713E-2</v>
-      </c>
-      <c r="AA36" s="11">
-        <f t="shared" si="63"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AB36" s="11">
-        <f t="shared" si="63"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="AC36" s="11">
-        <f t="shared" si="63"/>
-        <v>2.2864077065284594E-2</v>
-      </c>
-      <c r="AD36" s="11">
-        <f t="shared" si="63"/>
-        <v>2.2884058051688472E-2</v>
-      </c>
-      <c r="AE36" s="11">
-        <f t="shared" si="63"/>
-        <v>2.2904121703585245E-2</v>
-      </c>
-      <c r="AF36" s="11">
-        <f t="shared" si="63"/>
-        <v>2.2924267574277568E-2</v>
-      </c>
-      <c r="AG36" s="11">
-        <f t="shared" si="63"/>
-        <v>2.2944495205543092E-2</v>
-      </c>
-      <c r="AH36" s="11">
-        <f t="shared" si="63"/>
-        <v>2.2964804127617588E-2</v>
-      </c>
-      <c r="AI36" s="11">
-        <f t="shared" si="63"/>
-        <v>2.2985193859187181E-2</v>
-      </c>
-      <c r="AK36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="AL36" s="10">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B37" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
-      <c r="O37" s="10"/>
-      <c r="P37" s="10"/>
-      <c r="Q37" s="10"/>
-      <c r="T37" s="10">
-        <f t="shared" ref="T37:W37" si="65">(T10-T13)/T10</f>
-        <v>0.3031440983727266</v>
-      </c>
-      <c r="U37" s="10">
-        <f t="shared" si="65"/>
-        <v>0.31536941319550016</v>
-      </c>
-      <c r="V37" s="10">
-        <f t="shared" si="65"/>
-        <v>0.3093328924526742</v>
-      </c>
-      <c r="W37" s="10">
-        <f t="shared" si="65"/>
-        <v>0.29085730977070251</v>
-      </c>
-      <c r="X37" s="10">
-        <f>(X10-X13)/X10</f>
-        <v>0.27190432139553322</v>
-      </c>
-      <c r="Y37" s="19">
-        <f t="shared" ref="Y37:AI37" si="66">(Y10-Y13)/Y10</f>
-        <v>0.27</v>
-      </c>
-      <c r="Z37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27</v>
-      </c>
-      <c r="AA37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27000000000000007</v>
-      </c>
-      <c r="AB37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27</v>
-      </c>
-      <c r="AC37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27000000000000007</v>
-      </c>
-      <c r="AD37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27</v>
-      </c>
-      <c r="AE37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27</v>
-      </c>
-      <c r="AF37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.26999999999999996</v>
-      </c>
-      <c r="AG37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27</v>
-      </c>
-      <c r="AH37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27</v>
-      </c>
-      <c r="AI37" s="10">
-        <f t="shared" si="66"/>
-        <v>0.27</v>
-      </c>
-      <c r="AK37" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="AL37" s="6">
-        <f>NPV(AL36,Y25:EO25)</f>
-        <v>31639.932404523122</v>
-      </c>
-    </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B38" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-      <c r="O38" s="10"/>
-      <c r="P38" s="10"/>
-      <c r="Q38" s="10"/>
-      <c r="T38" s="10">
-        <f t="shared" ref="T38:W38" si="67">(T11-T14)/T11</f>
-        <v>0.25818339475395619</v>
-      </c>
-      <c r="U38" s="10">
-        <f t="shared" si="67"/>
-        <v>0.2634177758694719</v>
-      </c>
-      <c r="V38" s="10">
-        <f t="shared" si="67"/>
-        <v>0.23867069486404835</v>
-      </c>
-      <c r="W38" s="10">
-        <f t="shared" si="67"/>
-        <v>0.19737991266375546</v>
-      </c>
-      <c r="X38" s="10">
-        <f>(X11-X14)/X11</f>
-        <v>0.22758843482474561</v>
-      </c>
-      <c r="Y38" s="19">
-        <f t="shared" ref="Y38:AI38" si="68">(Y11-Y14)/Y11</f>
-        <v>0.23</v>
-      </c>
-      <c r="Z38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.22999999999999995</v>
-      </c>
-      <c r="AA38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.22999999999999995</v>
-      </c>
-      <c r="AB38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.23000000000000004</v>
-      </c>
-      <c r="AC38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.22999999999999995</v>
-      </c>
-      <c r="AD38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.22999999999999995</v>
-      </c>
-      <c r="AE38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.23</v>
-      </c>
-      <c r="AF38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.22999999999999995</v>
-      </c>
-      <c r="AG38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.22999999999999995</v>
-      </c>
-      <c r="AH38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.23</v>
-      </c>
-      <c r="AI38" s="10">
-        <f t="shared" si="68"/>
-        <v>0.22999999999999998</v>
-      </c>
-      <c r="AK38" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AL38" s="6">
-        <f>Main!D8</f>
-        <v>-11620</v>
-      </c>
-    </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B39" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K39" s="10">
-        <f t="shared" ref="K39" si="69">K16/K12</f>
-        <v>0.2586835540203416</v>
-      </c>
-      <c r="L39" s="10">
-        <f t="shared" ref="L39:N39" si="70">L16/L12</f>
-        <v>0.25665219852802418</v>
-      </c>
-      <c r="M39" s="10">
-        <f t="shared" si="70"/>
-        <v>0.26814058956916098</v>
-      </c>
-      <c r="N39" s="10">
-        <f t="shared" si="70"/>
-        <v>0.25294224153539741</v>
-      </c>
-      <c r="O39" s="10">
-        <f t="shared" ref="O39:P39" si="71">O16/O12</f>
-        <v>0.26305533904910366</v>
-      </c>
-      <c r="P39" s="10">
-        <f t="shared" si="71"/>
-        <v>0.24603759675635828</v>
-      </c>
-      <c r="Q39" s="10">
-        <f t="shared" ref="Q39:R39" si="72">Q16/Q12</f>
-        <v>0.26400424103198444</v>
-      </c>
-      <c r="R39" s="10">
-        <f t="shared" si="72"/>
-        <v>0.26</v>
-      </c>
-      <c r="T39" s="10">
-        <f t="shared" ref="T39:W39" si="73">T16/T12</f>
-        <v>0.29174453116412002</v>
-      </c>
-      <c r="U39" s="10">
-        <f t="shared" si="73"/>
-        <v>0.30178511283260356</v>
-      </c>
-      <c r="V39" s="10">
-        <f t="shared" si="73"/>
-        <v>0.28877036689719843</v>
-      </c>
-      <c r="W39" s="10">
-        <f t="shared" si="73"/>
-        <v>0.26329883104176321</v>
-      </c>
-      <c r="X39" s="10">
-        <f>X16/X12</f>
-        <v>0.25903868698710436</v>
-      </c>
-      <c r="Y39" s="10">
-        <f t="shared" ref="Y39:AI39" si="74">Y16/Y12</f>
-        <v>0.25832045321730612</v>
-      </c>
-      <c r="Z39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25854369173886205</v>
-      </c>
-      <c r="AA39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25854369173886199</v>
-      </c>
-      <c r="AB39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25854369173886194</v>
-      </c>
-      <c r="AC39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25846376779324609</v>
-      </c>
-      <c r="AD39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.2583835131856595</v>
-      </c>
-      <c r="AE39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25830292970288965</v>
-      </c>
-      <c r="AF39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25822201917782855</v>
-      </c>
-      <c r="AG39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25814078348952946</v>
-      </c>
-      <c r="AH39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25805922456325203</v>
-      </c>
-      <c r="AI39" s="10">
-        <f t="shared" si="74"/>
-        <v>0.25797734437049602</v>
-      </c>
-      <c r="AK39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL39" s="6">
-        <f>AL37+AL38</f>
-        <v>20019.932404523122</v>
-      </c>
-    </row>
     <row r="40" spans="2:38" x14ac:dyDescent="0.3">
       <c r="B40" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
       <c r="M40" s="10"/>
-      <c r="O40" s="10">
-        <f>O17/K17-1</f>
-        <v>-0.14948453608247425</v>
-      </c>
-      <c r="P40" s="10">
-        <f>P17/L17-1</f>
-        <v>-0.13574660633484159</v>
-      </c>
-      <c r="Q40" s="10">
-        <f>Q17/M17-1</f>
-        <v>-5.5194805194805241E-2</v>
-      </c>
-      <c r="R40" s="10">
-        <f>R17/N17-1</f>
-        <v>-2.0000000000000018E-2</v>
-      </c>
+      <c r="O40" s="10"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="10"/>
       <c r="T40" s="10"/>
       <c r="U40" s="10">
-        <f t="shared" ref="U40:W40" si="75">U17/T17-1</f>
+        <f t="shared" ref="U40:W42" si="62">U16/T16-1</f>
+        <v>-3.1293719166482603E-2</v>
+      </c>
+      <c r="V40" s="10">
+        <f t="shared" si="62"/>
+        <v>-8.0495591365156605E-2</v>
+      </c>
+      <c r="W40" s="10">
+        <f t="shared" si="62"/>
+        <v>0.13201620236422262</v>
+      </c>
+      <c r="X40" s="10">
+        <f>X16/W16-1</f>
+        <v>0.10515554257338988</v>
+      </c>
+      <c r="Y40" s="19">
+        <f t="shared" ref="Y40:AI42" si="63">Y16/X16-1</f>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="Z40" s="10">
+        <f t="shared" si="63"/>
+        <v>4.9999999999999822E-2</v>
+      </c>
+      <c r="AA40" s="10">
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB40" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC40" s="10">
+        <f t="shared" si="63"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AD40" s="10">
+        <f t="shared" si="63"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AE40" s="10">
+        <f t="shared" si="63"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AF40" s="10">
+        <f t="shared" si="63"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AG40" s="10">
+        <f t="shared" si="63"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AH40" s="10">
+        <f t="shared" si="63"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="AI40" s="10">
+        <f t="shared" si="63"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K41" s="10"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="10"/>
+      <c r="O41" s="10"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="10"/>
+      <c r="T41" s="10"/>
+      <c r="U41" s="10">
+        <f t="shared" si="62"/>
+        <v>9.7550401040538137E-3</v>
+      </c>
+      <c r="V41" s="10">
+        <f t="shared" si="62"/>
+        <v>6.5908115070845819E-2</v>
+      </c>
+      <c r="W41" s="10">
+        <f t="shared" si="62"/>
+        <v>0.15307150050352458</v>
+      </c>
+      <c r="X41" s="10">
+        <f t="shared" ref="X41:X42" si="64">X17/W17-1</f>
+        <v>8.1397379912663714E-2</v>
+      </c>
+      <c r="Y41" s="19">
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="Z41" s="10">
+        <f t="shared" si="63"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AA41" s="10">
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AD41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AE41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AF41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AG41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AI41" s="10">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AK41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL41" s="10">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="42" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="O42" s="11">
+        <f>O18/K18-1</f>
+        <v>-1.5160237958165457E-2</v>
+      </c>
+      <c r="P42" s="11">
+        <f>P18/L18-1</f>
+        <v>2.3966786186072842E-2</v>
+      </c>
+      <c r="Q42" s="11">
+        <f>Q18/M18-1</f>
+        <v>6.9349962207104987E-2</v>
+      </c>
+      <c r="R42" s="11">
+        <f>R18/N18-1</f>
+        <v>9.774035850081475E-2</v>
+      </c>
+      <c r="T42" s="11"/>
+      <c r="U42" s="11">
+        <f t="shared" si="62"/>
+        <v>-2.0886006375728239E-2</v>
+      </c>
+      <c r="V42" s="11">
+        <f t="shared" si="62"/>
+        <v>-4.2213988997417795E-2</v>
+      </c>
+      <c r="W42" s="11">
+        <f t="shared" si="62"/>
+        <v>0.13814324229281438</v>
+      </c>
+      <c r="X42" s="11">
+        <f t="shared" si="64"/>
+        <v>9.815129512333276E-2</v>
+      </c>
+      <c r="Y42" s="11">
+        <f t="shared" si="63"/>
+        <v>4.4774677608440783E-2</v>
+      </c>
+      <c r="Z42" s="11">
+        <f t="shared" si="63"/>
+        <v>5.946609981588713E-2</v>
+      </c>
+      <c r="AA42" s="11">
+        <f t="shared" si="63"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="AB42" s="11">
+        <f t="shared" si="63"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AC42" s="11">
+        <f t="shared" si="63"/>
+        <v>2.2864077065284594E-2</v>
+      </c>
+      <c r="AD42" s="11">
+        <f t="shared" si="63"/>
+        <v>2.2884058051688472E-2</v>
+      </c>
+      <c r="AE42" s="11">
+        <f t="shared" si="63"/>
+        <v>2.2904121703585245E-2</v>
+      </c>
+      <c r="AF42" s="11">
+        <f t="shared" si="63"/>
+        <v>2.2924267574277568E-2</v>
+      </c>
+      <c r="AG42" s="11">
+        <f t="shared" si="63"/>
+        <v>2.2944495205543092E-2</v>
+      </c>
+      <c r="AH42" s="11">
+        <f t="shared" si="63"/>
+        <v>2.2964804127617588E-2</v>
+      </c>
+      <c r="AI42" s="11">
+        <f t="shared" si="63"/>
+        <v>2.2985193859187181E-2</v>
+      </c>
+      <c r="AK42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL42" s="10">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B43" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K43" s="10"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="10"/>
+      <c r="O43" s="10"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="10"/>
+      <c r="T43" s="10">
+        <f t="shared" ref="T43:W43" si="65">(T16-T19)/T16</f>
+        <v>0.3031440983727266</v>
+      </c>
+      <c r="U43" s="10">
+        <f t="shared" si="65"/>
+        <v>0.31536941319550016</v>
+      </c>
+      <c r="V43" s="10">
+        <f t="shared" si="65"/>
+        <v>0.3093328924526742</v>
+      </c>
+      <c r="W43" s="10">
+        <f t="shared" si="65"/>
+        <v>0.29085730977070251</v>
+      </c>
+      <c r="X43" s="10">
+        <f>(X16-X19)/X16</f>
+        <v>0.27190432139553322</v>
+      </c>
+      <c r="Y43" s="19">
+        <f t="shared" ref="Y43:AI43" si="66">(Y16-Y19)/Y16</f>
+        <v>0.27</v>
+      </c>
+      <c r="Z43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27</v>
+      </c>
+      <c r="AA43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="AB43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27</v>
+      </c>
+      <c r="AC43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27000000000000007</v>
+      </c>
+      <c r="AD43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27</v>
+      </c>
+      <c r="AE43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27</v>
+      </c>
+      <c r="AF43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.26999999999999996</v>
+      </c>
+      <c r="AG43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27</v>
+      </c>
+      <c r="AH43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27</v>
+      </c>
+      <c r="AI43" s="10">
+        <f t="shared" si="66"/>
+        <v>0.27</v>
+      </c>
+      <c r="AK43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL43" s="6">
+        <f>NPV(AL42,Y31:EO31)</f>
+        <v>36105.72402856344</v>
+      </c>
+    </row>
+    <row r="44" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="T44" s="10">
+        <f t="shared" ref="T44:W44" si="67">(T17-T20)/T17</f>
+        <v>0.25818339475395619</v>
+      </c>
+      <c r="U44" s="10">
+        <f t="shared" si="67"/>
+        <v>0.2634177758694719</v>
+      </c>
+      <c r="V44" s="10">
+        <f t="shared" si="67"/>
+        <v>0.23867069486404835</v>
+      </c>
+      <c r="W44" s="10">
+        <f t="shared" si="67"/>
+        <v>0.19737991266375546</v>
+      </c>
+      <c r="X44" s="10">
+        <f>(X17-X20)/X17</f>
+        <v>0.22758843482474561</v>
+      </c>
+      <c r="Y44" s="19">
+        <f t="shared" ref="Y44:AI44" si="68">(Y17-Y20)/Y17</f>
+        <v>0.23</v>
+      </c>
+      <c r="Z44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AA44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AB44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.23000000000000004</v>
+      </c>
+      <c r="AC44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AD44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AE44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.23</v>
+      </c>
+      <c r="AF44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AG44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.22999999999999995</v>
+      </c>
+      <c r="AH44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.23</v>
+      </c>
+      <c r="AI44" s="10">
+        <f t="shared" si="68"/>
+        <v>0.22999999999999998</v>
+      </c>
+      <c r="AK44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL44" s="6">
+        <f>Main!D8</f>
+        <v>-11620</v>
+      </c>
+    </row>
+    <row r="45" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="K45" s="10">
+        <f t="shared" ref="K45" si="69">K22/K18</f>
+        <v>0.2586835540203416</v>
+      </c>
+      <c r="L45" s="10">
+        <f t="shared" ref="L45:N45" si="70">L22/L18</f>
+        <v>0.25665219852802418</v>
+      </c>
+      <c r="M45" s="10">
+        <f t="shared" si="70"/>
+        <v>0.26814058956916098</v>
+      </c>
+      <c r="N45" s="10">
+        <f t="shared" si="70"/>
+        <v>0.25294224153539741</v>
+      </c>
+      <c r="O45" s="10">
+        <f t="shared" ref="O45:P45" si="71">O22/O18</f>
+        <v>0.26305533904910366</v>
+      </c>
+      <c r="P45" s="10">
+        <f t="shared" si="71"/>
+        <v>0.24603759675635828</v>
+      </c>
+      <c r="Q45" s="10">
+        <f t="shared" ref="Q45:R45" si="72">Q22/Q18</f>
+        <v>0.26400424103198444</v>
+      </c>
+      <c r="R45" s="10">
+        <f t="shared" si="72"/>
+        <v>0.26</v>
+      </c>
+      <c r="T45" s="10">
+        <f t="shared" ref="T45:W45" si="73">T22/T18</f>
+        <v>0.29174453116412002</v>
+      </c>
+      <c r="U45" s="10">
+        <f t="shared" si="73"/>
+        <v>0.30178511283260356</v>
+      </c>
+      <c r="V45" s="10">
+        <f t="shared" si="73"/>
+        <v>0.28877036689719843</v>
+      </c>
+      <c r="W45" s="10">
+        <f t="shared" si="73"/>
+        <v>0.26329883104176321</v>
+      </c>
+      <c r="X45" s="10">
+        <f>X22/X18</f>
+        <v>0.25903868698710436</v>
+      </c>
+      <c r="Y45" s="10">
+        <f t="shared" ref="Y45:AI45" si="74">Y22/Y18</f>
+        <v>0.25832045321730612</v>
+      </c>
+      <c r="Z45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25854369173886205</v>
+      </c>
+      <c r="AA45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25854369173886199</v>
+      </c>
+      <c r="AB45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25854369173886194</v>
+      </c>
+      <c r="AC45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25846376779324609</v>
+      </c>
+      <c r="AD45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.2583835131856595</v>
+      </c>
+      <c r="AE45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25830292970288965</v>
+      </c>
+      <c r="AF45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25822201917782855</v>
+      </c>
+      <c r="AG45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25814078348952946</v>
+      </c>
+      <c r="AH45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25805922456325203</v>
+      </c>
+      <c r="AI45" s="10">
+        <f t="shared" si="74"/>
+        <v>0.25797734437049602</v>
+      </c>
+      <c r="AK45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AL45" s="6">
+        <f>AL43+AL44</f>
+        <v>24485.72402856344</v>
+      </c>
+    </row>
+    <row r="46" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K46" s="10"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="10"/>
+      <c r="O46" s="10">
+        <f>O23/K23-1</f>
+        <v>-0.14948453608247425</v>
+      </c>
+      <c r="P46" s="10">
+        <f>P23/L23-1</f>
+        <v>-0.13574660633484159</v>
+      </c>
+      <c r="Q46" s="10">
+        <f>Q23/M23-1</f>
+        <v>-5.5194805194805241E-2</v>
+      </c>
+      <c r="R46" s="10">
+        <f>R23/N23-1</f>
+        <v>-2.0000000000000018E-2</v>
+      </c>
+      <c r="T46" s="10"/>
+      <c r="U46" s="10">
+        <f t="shared" ref="U46:W46" si="75">U23/T23-1</f>
         <v>-1.0558069381598756E-2</v>
       </c>
-      <c r="V40" s="10">
+      <c r="V46" s="10">
         <f t="shared" si="75"/>
         <v>-8.5975609756097526E-2</v>
       </c>
-      <c r="W40" s="10">
+      <c r="W46" s="10">
         <f t="shared" si="75"/>
         <v>0.10507004669779851</v>
       </c>
-      <c r="X40" s="10">
-        <f>X17/W17-1</f>
+      <c r="X46" s="10">
+        <f>X23/W23-1</f>
         <v>7.6969514035617248E-2</v>
       </c>
-      <c r="Y40" s="10">
-        <f t="shared" ref="Y40:AI40" si="76">Y17/X17-1</f>
+      <c r="Y46" s="10">
+        <f t="shared" ref="Y46:AI46" si="76">Y23/X23-1</f>
         <v>-8.2556053811659202E-2</v>
       </c>
-      <c r="Z40" s="10">
+      <c r="Z46" s="10">
         <f t="shared" si="76"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AA40" s="10">
+      <c r="AA46" s="10">
         <f t="shared" si="76"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AB40" s="10">
+      <c r="AB46" s="10">
         <f t="shared" si="76"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AC40" s="10">
+      <c r="AC46" s="10">
         <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AD40" s="10">
+      <c r="AD46" s="10">
         <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AE40" s="10">
+      <c r="AE46" s="10">
         <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AF40" s="10">
+      <c r="AF46" s="10">
         <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AG40" s="10">
+      <c r="AG46" s="10">
         <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AH40" s="10">
+      <c r="AH46" s="10">
         <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AI40" s="10">
+      <c r="AI46" s="10">
         <f t="shared" si="76"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AK40" s="1" t="s">
+      <c r="AK46" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AL40" s="5">
-        <f>AL39/AI26</f>
-        <v>107.00124214069012</v>
-      </c>
-    </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B41" s="1" t="s">
+      <c r="AL46" s="5">
+        <f>AL45/AI32</f>
+        <v>130.86971688168595</v>
+      </c>
+    </row>
+    <row r="47" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K41" s="10">
-        <f t="shared" ref="K41" si="77">K19/K12</f>
+      <c r="K47" s="10">
+        <f t="shared" ref="K47" si="77">K25/K18</f>
         <v>7.2538860103626937E-2</v>
       </c>
-      <c r="L41" s="10">
-        <f t="shared" ref="L41:M41" si="78">L19/L12</f>
+      <c r="L47" s="10">
+        <f t="shared" ref="L47:M47" si="78">L25/L18</f>
         <v>8.982826948480846E-2</v>
       </c>
-      <c r="M41" s="10">
+      <c r="M47" s="10">
         <f t="shared" si="78"/>
         <v>9.3537414965986401E-2</v>
       </c>
-      <c r="N41" s="10">
-        <f t="shared" ref="N41" si="79">N19/N12</f>
+      <c r="N47" s="10">
+        <f t="shared" ref="N47" si="79">N25/N18</f>
         <v>0.10302371899330075</v>
       </c>
-      <c r="O41" s="10">
-        <f t="shared" ref="O41:P41" si="80">O19/O12</f>
+      <c r="O47" s="10">
+        <f t="shared" ref="O47:P47" si="80">O25/O18</f>
         <v>0.10229929851909587</v>
       </c>
-      <c r="P41" s="10">
+      <c r="P47" s="10">
         <f t="shared" si="80"/>
         <v>0.10523405823811278</v>
       </c>
-      <c r="Q41" s="10">
-        <f t="shared" ref="Q41:R41" si="81">Q19/Q12</f>
+      <c r="Q47" s="10">
+        <f t="shared" ref="Q47:R47" si="81">Q25/Q18</f>
         <v>0.10973670259763209</v>
       </c>
-      <c r="R41" s="10">
+      <c r="R47" s="10">
         <f t="shared" si="81"/>
         <v>0.12616129128029532</v>
       </c>
-      <c r="T41" s="10">
-        <f t="shared" ref="T41:W41" si="82">T19/T12</f>
+      <c r="T47" s="10">
+        <f t="shared" ref="T47:W47" si="82">T25/T18</f>
         <v>6.4581730240738711E-2</v>
       </c>
-      <c r="U41" s="10">
+      <c r="U47" s="10">
         <f t="shared" si="82"/>
         <v>0.11839003031323678</v>
       </c>
-      <c r="V41" s="10">
+      <c r="V47" s="10">
         <f t="shared" si="82"/>
         <v>6.6053217676708478E-2</v>
       </c>
-      <c r="W41" s="10">
+      <c r="W47" s="10">
         <f t="shared" si="82"/>
         <v>7.3433235491013951E-2</v>
       </c>
-      <c r="X41" s="10">
-        <f>X19/X12</f>
+      <c r="X47" s="10">
+        <f>X25/X18</f>
         <v>8.9941383352872217E-2</v>
       </c>
-      <c r="Y41" s="10">
-        <f t="shared" ref="Y41:AI41" si="83">Y19/Y12</f>
+      <c r="Y47" s="10">
+        <f t="shared" ref="Y47:AI47" si="83">Y25/Y18</f>
         <v>0.11139646550106783</v>
       </c>
-      <c r="Z41" s="10">
+      <c r="Z47" s="10">
         <f t="shared" si="83"/>
         <v>0.11431921183200952</v>
       </c>
-      <c r="AA41" s="10">
+      <c r="AA47" s="10">
         <f t="shared" si="83"/>
         <v>0.11570598567726771</v>
       </c>
-      <c r="AB41" s="10">
+      <c r="AB47" s="10">
         <f t="shared" si="83"/>
         <v>0.11709275952252585</v>
       </c>
-      <c r="AC41" s="10">
+      <c r="AC47" s="10">
         <f t="shared" si="83"/>
         <v>0.11879179695974398</v>
       </c>
-      <c r="AD41" s="10">
+      <c r="AD47" s="10">
         <f t="shared" si="83"/>
         <v>0.12047082461513471</v>
       </c>
-      <c r="AE41" s="10">
+      <c r="AE47" s="10">
         <f t="shared" si="83"/>
         <v>0.12213003480414987</v>
       </c>
-      <c r="AF41" s="10">
+      <c r="AF47" s="10">
         <f t="shared" si="83"/>
         <v>0.12376961814732866</v>
       </c>
-      <c r="AG41" s="10">
+      <c r="AG47" s="10">
         <f t="shared" si="83"/>
         <v>0.12538976358837747</v>
       </c>
-      <c r="AH41" s="10">
+      <c r="AH47" s="10">
         <f t="shared" si="83"/>
         <v>0.1269906584120388</v>
       </c>
-      <c r="AI41" s="10">
+      <c r="AI47" s="10">
         <f t="shared" si="83"/>
         <v>0.12857248826175038</v>
       </c>
-      <c r="AK41" s="1" t="s">
+      <c r="AK47" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AL41" s="5">
+      <c r="AL47" s="5">
         <f>Main!D3</f>
-        <v>294.39999999999998</v>
-      </c>
-    </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B42" s="1" t="s">
+        <v>277.77999999999997</v>
+      </c>
+    </row>
+    <row r="48" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B48" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K42" s="10">
-        <f t="shared" ref="K42" si="84">K23/K22</f>
+      <c r="K48" s="10">
+        <f t="shared" ref="K48" si="84">K29/K28</f>
         <v>1.7241379310344827E-2</v>
       </c>
-      <c r="L42" s="10">
-        <f t="shared" ref="L42:M42" si="85">L23/L22</f>
+      <c r="L48" s="10">
+        <f t="shared" ref="L48:M48" si="85">L29/L28</f>
         <v>5.8974358974358973E-2</v>
       </c>
-      <c r="M42" s="10">
+      <c r="M48" s="10">
         <f t="shared" si="85"/>
         <v>6.0465116279069767E-2</v>
       </c>
-      <c r="N42" s="10">
-        <f t="shared" ref="N42" si="86">N23/N22</f>
+      <c r="N48" s="10">
+        <f t="shared" ref="N48" si="86">N29/N28</f>
         <v>6.3655030800821355E-2</v>
       </c>
-      <c r="O42" s="10">
-        <f t="shared" ref="O42:P42" si="87">O23/O22</f>
+      <c r="O48" s="10">
+        <f t="shared" ref="O48:P48" si="87">O29/O28</f>
         <v>0.15904139433551198</v>
       </c>
-      <c r="P42" s="10">
+      <c r="P48" s="10">
         <f t="shared" si="87"/>
         <v>0.12595419847328243</v>
       </c>
-      <c r="Q42" s="10">
-        <f t="shared" ref="Q42:R42" si="88">Q23/Q22</f>
+      <c r="Q48" s="10">
+        <f t="shared" ref="Q48:R48" si="88">Q29/Q28</f>
         <v>0.18518518518518517</v>
       </c>
-      <c r="R42" s="10">
+      <c r="R48" s="10">
         <f t="shared" si="88"/>
         <v>0.15</v>
       </c>
-      <c r="T42" s="10">
-        <f t="shared" ref="T42:W42" si="89">T23/T22</f>
+      <c r="T48" s="10">
+        <f t="shared" ref="T48:W48" si="89">T29/T28</f>
         <v>0.17700453857791226</v>
       </c>
-      <c r="U42" s="10">
+      <c r="U48" s="10">
         <f t="shared" si="89"/>
         <v>0.19272886552781429</v>
       </c>
-      <c r="V42" s="10">
+      <c r="V48" s="10">
         <f t="shared" si="89"/>
         <v>0.16653574234092694</v>
       </c>
-      <c r="W42" s="10">
+      <c r="W48" s="10">
         <f t="shared" si="89"/>
         <v>1.8837018837018837E-2</v>
       </c>
-      <c r="X42" s="10">
-        <f>X23/X22</f>
+      <c r="X48" s="10">
+        <f>X29/X28</f>
         <v>5.3224796493425174E-2</v>
       </c>
-      <c r="Y42" s="10">
-        <f t="shared" ref="Y42:AI42" si="90">Y23/Y22</f>
+      <c r="Y48" s="10">
+        <f t="shared" ref="Y48:AI48" si="90">Y29/Y28</f>
         <v>0.155081989728901</v>
       </c>
-      <c r="Z42" s="10">
+      <c r="Z48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AA42" s="10">
+      <c r="AA48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AB42" s="10">
+      <c r="AB48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AC42" s="10">
+      <c r="AC48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AD42" s="10">
+      <c r="AD48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AE42" s="10">
+      <c r="AE48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AF42" s="10">
+      <c r="AF48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AG42" s="10">
+      <c r="AG48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AH42" s="10">
+      <c r="AH48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AI42" s="10">
+      <c r="AI48" s="10">
         <f t="shared" si="90"/>
         <v>0.15</v>
       </c>
-      <c r="AK42" s="2" t="s">
+      <c r="AK48" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="AL42" s="11">
-        <f>AL40/AL41-1</f>
-        <v>-0.63654469381559053</v>
-      </c>
-    </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B43" s="1" t="s">
+      <c r="AL48" s="11">
+        <f>AL46/AL47-1</f>
+        <v>-0.5288727882436246</v>
+      </c>
+    </row>
+    <row r="49" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K43" s="10">
-        <f t="shared" ref="K43" si="91">K25/K12</f>
+      <c r="K49" s="10">
+        <f t="shared" ref="K49" si="91">K31/K18</f>
         <v>5.4308194204567263E-2</v>
       </c>
-      <c r="L43" s="10">
-        <f t="shared" ref="L43:M43" si="92">L25/L12</f>
+      <c r="L49" s="10">
+        <f t="shared" ref="L49:M49" si="92">L31/L18</f>
         <v>6.9069635780335911E-2</v>
       </c>
-      <c r="M43" s="10">
+      <c r="M49" s="10">
         <f t="shared" si="92"/>
         <v>7.5585789871504161E-2</v>
       </c>
-      <c r="N43" s="10">
-        <f t="shared" ref="N43" si="93">N25/N12</f>
+      <c r="N49" s="10">
+        <f t="shared" ref="N49" si="93">N31/N18</f>
         <v>8.2020640956002172E-2</v>
       </c>
-      <c r="O43" s="10">
-        <f t="shared" ref="O43:P43" si="94">O25/O12</f>
+      <c r="O49" s="10">
+        <f t="shared" ref="O49:P49" si="94">O31/O18</f>
         <v>7.5214341387373346E-2</v>
       </c>
-      <c r="P43" s="10">
+      <c r="P49" s="10">
         <f t="shared" si="94"/>
         <v>8.4408403980833033E-2</v>
       </c>
-      <c r="Q43" s="10">
-        <f t="shared" ref="Q43:R43" si="95">Q25/Q12</f>
+      <c r="Q49" s="10">
+        <f t="shared" ref="Q49:R49" si="95">Q31/Q18</f>
         <v>8.1639865700653833E-2</v>
       </c>
-      <c r="R43" s="10">
+      <c r="R49" s="10">
         <f t="shared" si="95"/>
         <v>9.9946760748298669E-2</v>
       </c>
-      <c r="T43" s="10">
-        <f t="shared" ref="T43:W43" si="96">T25/T12</f>
+      <c r="T49" s="10">
+        <f t="shared" ref="T49:W49" si="96">T31/T18</f>
         <v>6.1503792459052437E-2</v>
       </c>
-      <c r="U43" s="10">
+      <c r="U49" s="10">
         <f t="shared" si="96"/>
         <v>0.10362636128887392</v>
       </c>
-      <c r="V43" s="10">
+      <c r="V49" s="10">
         <f t="shared" si="96"/>
         <v>6.2243582229515884E-2</v>
       </c>
-      <c r="W43" s="10">
+      <c r="W49" s="10">
         <f t="shared" si="96"/>
         <v>6.3185539935115095E-2</v>
       </c>
-      <c r="X43" s="10">
-        <f>X25/X12</f>
+      <c r="X49" s="10">
+        <f>X31/X18</f>
         <v>7.0433763188745599E-2</v>
       </c>
-      <c r="Y43" s="10">
-        <f t="shared" ref="Y43:AI43" si="97">Y25/Y12</f>
+      <c r="Y49" s="10">
+        <f t="shared" ref="Y49:AI49" si="97">Y31/Y18</f>
         <v>8.5815739085863388E-2</v>
       </c>
-      <c r="Z43" s="10">
+      <c r="Z49" s="10">
         <f t="shared" si="97"/>
         <v>8.920633204875944E-2</v>
       </c>
-      <c r="AA43" s="10">
+      <c r="AA49" s="10">
         <f t="shared" si="97"/>
         <v>9.061484937516491E-2</v>
       </c>
-      <c r="AB43" s="10">
+      <c r="AB49" s="10">
         <f t="shared" si="97"/>
         <v>9.1943805948498658E-2</v>
       </c>
-      <c r="AC43" s="10">
+      <c r="AC49" s="10">
         <f t="shared" si="97"/>
         <v>9.3483381221456385E-2</v>
       </c>
-      <c r="AD43" s="10">
+      <c r="AD49" s="10">
         <f t="shared" si="97"/>
         <v>9.5004892924147974E-2</v>
       </c>
-      <c r="AE43" s="10">
+      <c r="AE49" s="10">
         <f t="shared" si="97"/>
         <v>9.6508514741448087E-2</v>
       </c>
-      <c r="AF43" s="10">
+      <c r="AF49" s="10">
         <f t="shared" si="97"/>
         <v>9.7994418824196738E-2</v>
       </c>
-      <c r="AG43" s="10">
+      <c r="AG49" s="10">
         <f t="shared" si="97"/>
         <v>9.9462775805533865E-2</v>
       </c>
-      <c r="AH43" s="10">
+      <c r="AH49" s="10">
         <f t="shared" si="97"/>
         <v>0.10091375481704352</v>
       </c>
-      <c r="AI43" s="10">
+      <c r="AI49" s="10">
         <f t="shared" si="97"/>
         <v>0.10234752350470923</v>
       </c>
-      <c r="AK43" s="1" t="s">
+      <c r="AK49" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AL43" s="7" t="s">
+      <c r="AL49" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="2:38" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B46" s="12" t="s">
+    <row r="52" spans="2:38" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="P46" s="17">
+      <c r="P52" s="17">
         <v>41240</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q52" s="17">
         <v>41014</v>
       </c>
-      <c r="Y46" s="17">
+      <c r="Y52" s="17">
         <v>41014</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.3">
-      <c r="B48" s="1" t="s">
+    <row r="54" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B54" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P48" s="13"/>
-      <c r="Y48" s="13">
-        <f>Main!$D$9/Model!Y46</f>
-        <v>1.626328570731945</v>
-      </c>
-    </row>
-    <row r="49" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B49" s="1" t="s">
+      <c r="P54" s="13"/>
+      <c r="Y54" s="13">
+        <f>Main!$D$9/Model!Y52</f>
+        <v>1.5505105086068169</v>
+      </c>
+    </row>
+    <row r="55" spans="2:38" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="P49" s="10"/>
-      <c r="Y49" s="10">
-        <f>Y46/Main!$D$9-1</f>
-        <v>-0.38511810098131627</v>
+      <c r="P55" s="10"/>
+      <c r="Y55" s="10">
+        <f>Y52/Main!$D$9-1</f>
+        <v>-0.3550511302896413</v>
       </c>
     </row>
   </sheetData>
